--- a/GBDS JULY FILES 2026/CSR MONTH OF JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/CSR MONTH OF JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E58B4085-C1E0-43FC-94F8-BD9DA8439EFA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3FEE021-DC58-4406-975C-B0B8BD65F1E2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="16" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | JULY" sheetId="902" r:id="rId1"/>

--- a/GBDS JULY FILES 2026/CSR MONTH OF JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/CSR MONTH OF JULY 2026.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3FEE021-DC58-4406-975C-B0B8BD65F1E2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42594E29-CCA8-4A57-996B-0C2D8CBB9B34}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | JULY" sheetId="902" r:id="rId1"/>
     <sheet name="(1)" sheetId="1790" r:id="rId2"/>
-    <sheet name="07-01 R1" sheetId="1791" r:id="rId3"/>
+    <sheet name="07-01 R1 NO TRIP" sheetId="1791" r:id="rId3"/>
     <sheet name="07-01 R2" sheetId="1792" r:id="rId4"/>
     <sheet name="07-01 R3" sheetId="1793" r:id="rId5"/>
     <sheet name="(2)" sheetId="1794" r:id="rId6"/>
@@ -39,7 +39,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="5">'(2)'!$A$1:$Z$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'(3)'!$A$1:$Z$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'(4)'!$A$1:$Z$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'07-01 R1'!$A$1:$Z$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'07-01 R1 NO TRIP'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'07-01 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'07-01 R3'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'07-02 R1'!$A$1:$Z$43</definedName>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1374" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1385" uniqueCount="81">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -290,6 +290,27 @@
   </si>
   <si>
     <t>DATE ___________07/04/2026___________</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>10/12B</t>
+  </si>
+  <si>
+    <t>11/12B</t>
+  </si>
+  <si>
+    <t>1/12B</t>
+  </si>
+  <si>
+    <t>9/4B</t>
+  </si>
+  <si>
+    <t>12/12B</t>
+  </si>
+  <si>
+    <t>3/3B</t>
   </si>
 </sst>
 </file>
@@ -18220,12 +18241,20 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
+      <c r="C8" s="77" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="14">
+        <v>1</v>
+      </c>
+      <c r="E8" s="14">
+        <v>1</v>
+      </c>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>76</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -18236,12 +18265,18 @@
       <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
-      <c r="S8" s="14"/>
+      <c r="S8" s="14">
+        <v>1</v>
+      </c>
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
+      <c r="W8" s="14">
+        <v>5</v>
+      </c>
+      <c r="X8" s="59">
+        <v>1</v>
+      </c>
       <c r="Y8" s="15"/>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -18408,12 +18443,20 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
+      <c r="D15" s="23">
+        <v>1</v>
+      </c>
+      <c r="E15" s="23">
+        <v>1</v>
+      </c>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>1</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -18424,24 +18467,38 @@
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
-      <c r="S15" s="23"/>
+      <c r="S15" s="23">
+        <v>1</v>
+      </c>
       <c r="T15" s="23"/>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
+      <c r="W15" s="23">
+        <v>0</v>
+      </c>
+      <c r="X15" s="61">
+        <v>0</v>
+      </c>
       <c r="Y15" s="24"/>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="27"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
+      <c r="E16" s="27">
+        <v>0</v>
+      </c>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>75</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -18452,12 +18509,18 @@
       <c r="P16" s="28"/>
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
-      <c r="S16" s="28"/>
+      <c r="S16" s="28">
+        <v>0</v>
+      </c>
       <c r="T16" s="28"/>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
+      <c r="W16" s="56">
+        <v>5</v>
+      </c>
+      <c r="X16" s="62">
+        <v>1</v>
+      </c>
       <c r="Y16" s="29"/>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -18860,17 +18923,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="79"/>
+      <c r="F24" s="79" t="s">
+        <v>77</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>55</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14">
+        <v>10</v>
+      </c>
+      <c r="M24" s="14">
+        <v>366</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>78</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -19046,17 +19121,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23" t="s">
+        <v>77</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>1</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>2</v>
+      </c>
+      <c r="L31" s="23">
+        <v>2</v>
+      </c>
+      <c r="M31" s="23">
+        <v>110</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>78</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -19074,17 +19161,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>54</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>8</v>
+      </c>
+      <c r="M32" s="28">
+        <v>256</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -19221,21 +19320,39 @@
       <c r="B36" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="46"/>
+      <c r="C36" s="46">
+        <v>1</v>
+      </c>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
+      <c r="F36" s="42">
+        <v>316</v>
+      </c>
+      <c r="G36" s="42">
+        <v>1</v>
+      </c>
+      <c r="H36" s="42">
+        <v>5</v>
+      </c>
+      <c r="I36" s="42">
+        <v>3</v>
+      </c>
       <c r="J36" s="42"/>
       <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
+      <c r="L36" s="42">
+        <v>4</v>
+      </c>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="O36" s="42">
+        <v>5</v>
+      </c>
+      <c r="P36" s="42">
+        <v>6</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>9</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -19379,21 +19496,39 @@
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
+      <c r="C42" s="46">
+        <v>1</v>
+      </c>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
+      <c r="F42" s="42">
+        <v>316</v>
+      </c>
+      <c r="G42" s="42">
+        <v>1</v>
+      </c>
+      <c r="H42" s="42">
+        <v>5</v>
+      </c>
+      <c r="I42" s="42">
+        <v>3</v>
+      </c>
       <c r="J42" s="42"/>
       <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
+      <c r="L42" s="42">
+        <v>4</v>
+      </c>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="O42" s="42">
+        <v>5</v>
+      </c>
+      <c r="P42" s="42">
+        <v>6</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>9</v>
+      </c>
       <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
@@ -19435,7 +19570,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
+      <c r="C44" s="92">
+        <f>10+5+1+54+8+256</f>
+        <v>334</v>
+      </c>
       <c r="D44" s="92"/>
       <c r="E44" s="92"/>
     </row>
@@ -19443,7 +19581,9 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
+      <c r="C45" s="92">
+        <v>12</v>
+      </c>
       <c r="D45" s="92"/>
       <c r="E45" s="92"/>
     </row>
@@ -19844,11 +19984,17 @@
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
       <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
+      <c r="D8" s="14">
+        <v>2</v>
+      </c>
+      <c r="E8" s="14">
+        <v>2</v>
+      </c>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>24</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -19860,12 +20006,20 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>2</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="W8" s="14">
+        <v>5</v>
+      </c>
+      <c r="X8" s="59">
+        <v>2</v>
+      </c>
+      <c r="Y8" s="15">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -20032,11 +20186,17 @@
         <v>25</v>
       </c>
       <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
+      <c r="D15" s="23">
+        <v>2</v>
+      </c>
+      <c r="E15" s="23">
+        <v>2</v>
+      </c>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>76</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -20048,23 +20208,37 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>2</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="W15" s="23">
+        <v>0</v>
+      </c>
+      <c r="X15" s="61">
+        <v>2</v>
+      </c>
+      <c r="Y15" s="24">
+        <v>2</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
       <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="27"/>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
+      <c r="E16" s="27">
+        <v>0</v>
+      </c>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>79</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -20076,12 +20250,20 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="29"/>
+      <c r="W16" s="56">
+        <v>5</v>
+      </c>
+      <c r="X16" s="62">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -20483,17 +20665,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>55</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14">
+        <v>21</v>
+      </c>
+      <c r="M24" s="14">
+        <v>507</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>80</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -20669,17 +20863,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>2</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>55</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>2</v>
+      </c>
+      <c r="L31" s="23">
+        <v>19</v>
+      </c>
+      <c r="M31" s="23">
+        <v>129</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>80</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -20697,17 +20903,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>0</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>2</v>
+      </c>
+      <c r="M32" s="28">
+        <v>378</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -20847,18 +21065,34 @@
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
+      <c r="F36" s="42">
+        <v>502</v>
+      </c>
+      <c r="G36" s="42">
+        <v>8</v>
+      </c>
+      <c r="H36" s="42">
+        <v>1</v>
+      </c>
       <c r="I36" s="42"/>
       <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
+      <c r="K36" s="42">
+        <v>2</v>
+      </c>
+      <c r="L36" s="42">
+        <v>4</v>
+      </c>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="O36" s="42">
+        <v>9</v>
+      </c>
+      <c r="P36" s="42">
+        <v>4</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>1</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -21005,18 +21239,34 @@
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
+      <c r="F42" s="42">
+        <v>502</v>
+      </c>
+      <c r="G42" s="42">
+        <v>8</v>
+      </c>
+      <c r="H42" s="42">
+        <v>1</v>
+      </c>
       <c r="I42" s="42"/>
       <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
+      <c r="K42" s="42">
+        <v>2</v>
+      </c>
+      <c r="L42" s="42">
+        <v>4</v>
+      </c>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="O42" s="42">
+        <v>9</v>
+      </c>
+      <c r="P42" s="42">
+        <v>4</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>1</v>
+      </c>
       <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
@@ -21058,7 +21308,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
+      <c r="C44" s="92">
+        <f>12+5+2+378</f>
+        <v>397</v>
+      </c>
       <c r="D44" s="92"/>
       <c r="E44" s="92"/>
     </row>
@@ -21066,7 +21319,9 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
+      <c r="C45" s="92">
+        <v>12</v>
+      </c>
       <c r="D45" s="92"/>
       <c r="E45" s="92"/>
     </row>

--- a/GBDS JULY FILES 2026/CSR MONTH OF JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/CSR MONTH OF JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42594E29-CCA8-4A57-996B-0C2D8CBB9B34}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D8FE987-DE0E-4F58-A232-C37288CC7FD9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | JULY" sheetId="902" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="07-01 R2" sheetId="1792" r:id="rId4"/>
     <sheet name="07-01 R3" sheetId="1793" r:id="rId5"/>
     <sheet name="(2)" sheetId="1794" r:id="rId6"/>
-    <sheet name="07-02 R1" sheetId="1796" r:id="rId7"/>
+    <sheet name="07-02 R1 NO TRIP" sheetId="1796" r:id="rId7"/>
     <sheet name="07-02 R2" sheetId="1797" r:id="rId8"/>
     <sheet name="07-02 R3" sheetId="1798" r:id="rId9"/>
     <sheet name="(3)" sheetId="1799" r:id="rId10"/>
@@ -42,7 +42,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="2">'07-01 R1 NO TRIP'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'07-01 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'07-01 R3'!$A$1:$V$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'07-02 R1'!$A$1:$Z$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'07-02 R1 NO TRIP'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'07-02 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'07-02 R3'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="10">'07-03 R1'!$A$1:$Z$43</definedName>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1385" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="84">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -311,6 +311,15 @@
   </si>
   <si>
     <t>3/3B</t>
+  </si>
+  <si>
+    <t>3/12B</t>
+  </si>
+  <si>
+    <t>8/12B</t>
+  </si>
+  <si>
+    <t>16/12B</t>
   </si>
 </sst>
 </file>
@@ -931,7 +940,7 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1218,6 +1227,10 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -24948,12 +24961,20 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="77" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="14">
+        <v>1</v>
+      </c>
       <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="F8" s="14">
+        <v>2</v>
+      </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>82</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -24965,10 +24986,14 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>3</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>2</v>
+      </c>
       <c r="X8" s="59"/>
       <c r="Y8" s="15"/>
     </row>
@@ -25136,12 +25161,20 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
+      <c r="D15" s="23">
+        <v>1</v>
+      </c>
       <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="F15" s="23">
+        <v>0</v>
+      </c>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>81</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -25153,10 +25186,14 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>2</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>0</v>
+      </c>
       <c r="X15" s="61"/>
       <c r="Y15" s="24"/>
     </row>
@@ -25164,12 +25201,20 @@
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
       <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="F16" s="27">
+        <v>2</v>
+      </c>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28">
+        <v>5</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -25181,10 +25226,14 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>1</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56">
+        <v>2</v>
+      </c>
       <c r="X16" s="62"/>
       <c r="Y16" s="29"/>
     </row>
@@ -25588,14 +25637,24 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="79"/>
+      <c r="F24" s="93">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>47</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>47</v>
+      </c>
+      <c r="L24" s="14">
+        <v>10</v>
+      </c>
+      <c r="M24" s="14">
+        <v>324</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
       <c r="P24" s="14"/>
@@ -25774,14 +25833,24 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>1</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>22</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>1</v>
+      </c>
+      <c r="L31" s="23">
+        <v>0</v>
+      </c>
+      <c r="M31" s="23">
+        <v>42</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
       <c r="P31" s="23"/>
@@ -25802,14 +25871,24 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>1</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>25</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>46</v>
+      </c>
+      <c r="L32" s="28">
+        <v>10</v>
+      </c>
+      <c r="M32" s="28">
+        <v>282</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
       <c r="P32" s="28"/>
@@ -25950,20 +26029,44 @@
         <v>52</v>
       </c>
       <c r="C36" s="46"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
+      <c r="D36" s="41">
+        <v>1</v>
+      </c>
+      <c r="E36" s="42">
+        <v>18</v>
+      </c>
+      <c r="F36" s="42">
+        <v>348</v>
+      </c>
+      <c r="G36" s="42">
+        <v>13</v>
+      </c>
+      <c r="H36" s="42">
+        <v>2</v>
+      </c>
+      <c r="I36" s="42">
+        <v>9</v>
+      </c>
+      <c r="J36" s="42">
+        <v>3</v>
+      </c>
+      <c r="K36" s="42">
+        <v>11</v>
+      </c>
+      <c r="L36" s="42">
+        <v>48</v>
+      </c>
+      <c r="M36" s="42">
+        <v>2</v>
+      </c>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
+      <c r="O36" s="42">
+        <v>4</v>
+      </c>
       <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="Q36" s="43">
+        <v>16</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -26108,20 +26211,44 @@
         <v>53</v>
       </c>
       <c r="C42" s="46"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
-      <c r="M42" s="42"/>
+      <c r="D42" s="41">
+        <v>1</v>
+      </c>
+      <c r="E42" s="42">
+        <v>18</v>
+      </c>
+      <c r="F42" s="42">
+        <v>348</v>
+      </c>
+      <c r="G42" s="42">
+        <v>13</v>
+      </c>
+      <c r="H42" s="42">
+        <v>2</v>
+      </c>
+      <c r="I42" s="42">
+        <v>9</v>
+      </c>
+      <c r="J42" s="42">
+        <v>3</v>
+      </c>
+      <c r="K42" s="42">
+        <v>11</v>
+      </c>
+      <c r="L42" s="42">
+        <v>48</v>
+      </c>
+      <c r="M42" s="42">
+        <v>2</v>
+      </c>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
+      <c r="O42" s="42">
+        <v>4</v>
+      </c>
       <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="Q42" s="43">
+        <v>16</v>
+      </c>
       <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
@@ -26163,7 +26290,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
+      <c r="C44" s="92">
+        <f>2+5+1+2+1+25+46+10+282</f>
+        <v>374</v>
+      </c>
       <c r="D44" s="92"/>
       <c r="E44" s="92"/>
     </row>
@@ -26572,11 +26702,17 @@
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
       <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
+      <c r="D8" s="14">
+        <v>2</v>
+      </c>
+      <c r="E8" s="14">
+        <v>2</v>
+      </c>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>83</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -26588,12 +26724,18 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>2</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
       <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="X8" s="59">
+        <v>2</v>
+      </c>
+      <c r="Y8" s="15">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -26760,11 +26902,17 @@
         <v>25</v>
       </c>
       <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
+      <c r="D15" s="23">
+        <v>2</v>
+      </c>
+      <c r="E15" s="23">
+        <v>2</v>
+      </c>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>8</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -26776,23 +26924,35 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>2</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
       <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="X15" s="61">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="24">
+        <v>2</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
       <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="27"/>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
+      <c r="E16" s="27">
+        <v>0</v>
+      </c>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>82</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -26804,12 +26964,18 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
       <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="29"/>
+      <c r="X16" s="62">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -27211,17 +27377,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>55</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14">
+        <v>19</v>
+      </c>
+      <c r="M24" s="14">
+        <v>453</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>80</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -27397,17 +27575,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>2</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>2</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>2</v>
+      </c>
+      <c r="L31" s="23">
+        <v>13</v>
+      </c>
+      <c r="M31" s="23">
+        <v>182</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>80</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -27425,17 +27615,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>53</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>6</v>
+      </c>
+      <c r="M32" s="28">
+        <v>271</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -27572,21 +27774,33 @@
       <c r="B36" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="46"/>
+      <c r="C36" s="46">
+        <v>1</v>
+      </c>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
+      <c r="F36" s="42">
+        <v>323</v>
+      </c>
       <c r="G36" s="42"/>
       <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
+      <c r="I36" s="42">
+        <v>16</v>
+      </c>
       <c r="J36" s="42"/>
       <c r="K36" s="42"/>
       <c r="L36" s="42"/>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="O36" s="42">
+        <v>6</v>
+      </c>
+      <c r="P36" s="42">
+        <v>4</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>17</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -27730,21 +27944,33 @@
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
+      <c r="C42" s="46">
+        <v>1</v>
+      </c>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
+      <c r="F42" s="42">
+        <v>323</v>
+      </c>
       <c r="G42" s="42"/>
       <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
+      <c r="I42" s="42">
+        <v>16</v>
+      </c>
       <c r="J42" s="42"/>
       <c r="K42" s="42"/>
       <c r="L42" s="42"/>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="O42" s="42">
+        <v>6</v>
+      </c>
+      <c r="P42" s="42">
+        <v>4</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>17</v>
+      </c>
       <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
@@ -27786,7 +28012,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
+      <c r="C44" s="92">
+        <f>8+1+53+6+271</f>
+        <v>339</v>
+      </c>
       <c r="D44" s="92"/>
       <c r="E44" s="92"/>
     </row>

--- a/GBDS JULY FILES 2026/CSR MONTH OF JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/CSR MONTH OF JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D8FE987-DE0E-4F58-A232-C37288CC7FD9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08666EC-4187-4BB8-9C7C-2D4C69884757}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="12" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | JULY" sheetId="902" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="86">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -320,6 +320,12 @@
   </si>
   <si>
     <t>16/12B</t>
+  </si>
+  <si>
+    <t>6/12B</t>
+  </si>
+  <si>
+    <t>5/12B</t>
   </si>
 </sst>
 </file>
@@ -1192,6 +1198,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1227,10 +1237,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3056,47 +3062,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90" t="s">
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="91" t="s">
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="81" t="s">
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -3328,12 +3334,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="84" t="s">
+      <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -3689,25 +3695,63 @@
       <c r="B7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="10"/>
-      <c r="S7" s="10"/>
-      <c r="T7" s="10"/>
-      <c r="U7" s="11"/>
+      <c r="C7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="R7" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="S7" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="T7" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>14</v>
+      </c>
       <c r="V7" s="10" t="s">
         <v>65</v>
       </c>
@@ -3723,12 +3767,18 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="13">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14">
+        <v>1</v>
+      </c>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="81" t="s">
+        <v>82</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -3740,7 +3790,9 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>2</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
       <c r="W8" s="14"/>
@@ -3911,12 +3963,18 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
+      <c r="C15" s="22">
+        <v>0</v>
+      </c>
+      <c r="D15" s="23">
+        <v>0</v>
+      </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>2</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -3928,7 +3986,9 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>1</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
       <c r="W15" s="23"/>
@@ -3939,12 +3999,18 @@
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="C16" s="57">
+        <v>1</v>
+      </c>
+      <c r="D16" s="58">
+        <v>1</v>
+      </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>84</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -3956,7 +4022,9 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>1</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
       <c r="W16" s="56"/>
@@ -4363,14 +4431,24 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>1</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>22</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>1</v>
+      </c>
+      <c r="L24" s="14">
+        <v>16</v>
+      </c>
+      <c r="M24" s="14">
+        <v>474</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
       <c r="P24" s="14"/>
@@ -4549,14 +4627,24 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>1</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>14</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>0</v>
+      </c>
+      <c r="L31" s="23">
+        <v>0</v>
+      </c>
+      <c r="M31" s="23">
+        <v>70</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
       <c r="P31" s="23"/>
@@ -4577,14 +4665,24 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>8</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>1</v>
+      </c>
+      <c r="L32" s="28">
+        <v>16</v>
+      </c>
+      <c r="M32" s="28">
+        <v>404</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
       <c r="P32" s="28"/>
@@ -4625,47 +4723,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90" t="s">
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="91" t="s">
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="81" t="s">
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -4724,21 +4822,41 @@
       <c r="B36" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="46"/>
-      <c r="D36" s="41"/>
+      <c r="C36" s="46">
+        <v>2</v>
+      </c>
+      <c r="D36" s="41">
+        <v>1</v>
+      </c>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
+      <c r="F36" s="42">
+        <v>460</v>
+      </c>
+      <c r="G36" s="42">
+        <v>27</v>
+      </c>
+      <c r="H36" s="42">
+        <v>1</v>
+      </c>
+      <c r="I36" s="42">
+        <v>1</v>
+      </c>
+      <c r="J36" s="42">
+        <v>14</v>
+      </c>
       <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
+      <c r="L36" s="42">
+        <v>4</v>
+      </c>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
+      <c r="O36" s="42">
+        <v>3</v>
+      </c>
       <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="Q36" s="43">
+        <v>3</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -4882,27 +5000,47 @@
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
-      <c r="D42" s="41"/>
+      <c r="C42" s="46">
+        <v>2</v>
+      </c>
+      <c r="D42" s="41">
+        <v>1</v>
+      </c>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
+      <c r="F42" s="42">
+        <v>460</v>
+      </c>
+      <c r="G42" s="42">
+        <v>27</v>
+      </c>
+      <c r="H42" s="42">
+        <v>1</v>
+      </c>
+      <c r="I42" s="42">
+        <v>1</v>
+      </c>
+      <c r="J42" s="42">
+        <v>14</v>
+      </c>
       <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
+      <c r="L42" s="42">
+        <v>4</v>
+      </c>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
+      <c r="O42" s="42">
+        <v>3</v>
+      </c>
       <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
-      <c r="R42" s="84" t="s">
+      <c r="Q42" s="43">
+        <v>3</v>
+      </c>
+      <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -4938,17 +5076,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="93">
+        <f>1+1+6+1+8+1+16+404</f>
+        <v>438</v>
+      </c>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="93">
+        <v>12</v>
+      </c>
+      <c r="D45" s="93"/>
+      <c r="E45" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -5346,12 +5489,20 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
+      <c r="C8" s="77" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="14">
+        <v>1</v>
+      </c>
+      <c r="E8" s="14">
+        <v>1</v>
+      </c>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>14</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -5363,10 +5514,14 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>1</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>1</v>
+      </c>
       <c r="X8" s="59"/>
       <c r="Y8" s="15"/>
     </row>
@@ -5534,12 +5689,20 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
+      <c r="D15" s="23">
+        <v>1</v>
+      </c>
+      <c r="E15" s="23">
+        <v>1</v>
+      </c>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>85</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -5551,10 +5714,14 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>1</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>0</v>
+      </c>
       <c r="X15" s="61"/>
       <c r="Y15" s="24"/>
     </row>
@@ -5562,12 +5729,20 @@
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="27"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
+      <c r="E16" s="27">
+        <v>0</v>
+      </c>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>82</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -5579,10 +5754,14 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56">
+        <v>1</v>
+      </c>
       <c r="X16" s="62"/>
       <c r="Y16" s="29"/>
     </row>
@@ -5986,17 +6165,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="79"/>
+      <c r="F24" s="79" t="s">
+        <v>77</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>40</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14">
+        <v>2</v>
+      </c>
+      <c r="M24" s="14">
+        <v>434</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>78</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -6172,17 +6363,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23" t="s">
+        <v>77</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>10</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>2</v>
+      </c>
+      <c r="L31" s="23">
+        <v>0</v>
+      </c>
+      <c r="M31" s="23">
+        <v>112</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>78</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -6200,17 +6403,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>30</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>2</v>
+      </c>
+      <c r="M32" s="28">
+        <v>322</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -6248,47 +6463,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90" t="s">
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="91" t="s">
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="81" t="s">
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -6350,18 +6565,26 @@
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
+      <c r="F36" s="42">
+        <v>353</v>
+      </c>
       <c r="G36" s="42"/>
       <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
+      <c r="I36" s="42">
+        <v>4</v>
+      </c>
       <c r="J36" s="42"/>
       <c r="K36" s="42"/>
       <c r="L36" s="42"/>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
+      <c r="O36" s="42">
+        <v>2</v>
+      </c>
       <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="Q36" s="43">
+        <v>11</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -6508,24 +6731,32 @@
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
+      <c r="F42" s="42">
+        <v>353</v>
+      </c>
       <c r="G42" s="42"/>
       <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
+      <c r="I42" s="42">
+        <v>4</v>
+      </c>
       <c r="J42" s="42"/>
       <c r="K42" s="42"/>
       <c r="L42" s="42"/>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
+      <c r="O42" s="42">
+        <v>2</v>
+      </c>
       <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
-      <c r="R42" s="84" t="s">
+      <c r="Q42" s="43">
+        <v>11</v>
+      </c>
+      <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -6561,17 +6792,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="93">
+        <f>8+1+30+2+322</f>
+        <v>363</v>
+      </c>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="93">
+        <v>12</v>
+      </c>
+      <c r="D45" s="93"/>
+      <c r="E45" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -6970,11 +7206,17 @@
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
       <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
+      <c r="D8" s="14">
+        <v>2</v>
+      </c>
+      <c r="E8" s="14">
+        <v>2</v>
+      </c>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>18</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -6986,12 +7228,20 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>2</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="W8" s="14">
+        <v>10</v>
+      </c>
+      <c r="X8" s="59">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="15">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -7158,11 +7408,17 @@
         <v>25</v>
       </c>
       <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
+      <c r="D15" s="23">
+        <v>2</v>
+      </c>
+      <c r="E15" s="23">
+        <v>2</v>
+      </c>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>5</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -7174,23 +7430,37 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>0</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="W15" s="23">
+        <v>0</v>
+      </c>
+      <c r="X15" s="61">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
       <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="27"/>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
+      <c r="E16" s="27">
+        <v>0</v>
+      </c>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28">
+        <v>13</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -7202,12 +7472,20 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>2</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="29"/>
+      <c r="W16" s="56">
+        <v>10</v>
+      </c>
+      <c r="X16" s="62">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="29">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -7609,17 +7887,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>56</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14">
+        <v>31</v>
+      </c>
+      <c r="M24" s="14">
+        <v>505</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>80</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -7795,17 +8085,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>2</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>2</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>0</v>
+      </c>
+      <c r="L31" s="23">
+        <v>1</v>
+      </c>
+      <c r="M31" s="23">
+        <v>39</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>80</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -7823,17 +8125,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>54</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>2</v>
+      </c>
+      <c r="L32" s="28">
+        <v>30</v>
+      </c>
+      <c r="M32" s="28">
+        <v>466</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -7871,47 +8185,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90" t="s">
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="91" t="s">
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="81" t="s">
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -8128,27 +8442,53 @@
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
+      <c r="C42" s="46">
+        <v>3</v>
+      </c>
+      <c r="D42" s="41">
+        <v>2</v>
+      </c>
+      <c r="E42" s="42">
+        <v>23</v>
+      </c>
+      <c r="F42" s="42">
+        <v>244</v>
+      </c>
+      <c r="G42" s="42">
+        <v>28</v>
+      </c>
       <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
-      <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
+      <c r="I42" s="42">
+        <v>8</v>
+      </c>
+      <c r="J42" s="42">
+        <v>8</v>
+      </c>
+      <c r="K42" s="42">
+        <v>3</v>
+      </c>
+      <c r="L42" s="42">
+        <v>25</v>
+      </c>
+      <c r="M42" s="42">
+        <v>6</v>
+      </c>
+      <c r="N42" s="42">
+        <v>10</v>
+      </c>
+      <c r="O42" s="42">
+        <v>2</v>
+      </c>
       <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
-      <c r="R42" s="84" t="s">
+      <c r="Q42" s="43">
+        <v>16</v>
+      </c>
+      <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -8184,17 +8524,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="93"/>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="93"/>
+      <c r="D45" s="93"/>
+      <c r="E45" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -9491,47 +9831,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90" t="s">
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="91" t="s">
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="81" t="s">
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -9763,12 +10103,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="84" t="s">
+      <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -11060,47 +11400,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90" t="s">
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="91" t="s">
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="81" t="s">
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -11332,12 +11672,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="84" t="s">
+      <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -11373,17 +11713,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="93"/>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="93"/>
+      <c r="D45" s="93"/>
+      <c r="E45" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -12683,47 +13023,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90" t="s">
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="91" t="s">
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="81" t="s">
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -12955,12 +13295,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="84" t="s">
+      <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -12996,17 +13336,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="93"/>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="93"/>
+      <c r="D45" s="93"/>
+      <c r="E45" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -14306,47 +14646,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90" t="s">
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="91" t="s">
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="81" t="s">
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -14578,12 +14918,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="84" t="s">
+      <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -14619,17 +14959,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="93"/>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="93"/>
+      <c r="D45" s="93"/>
+      <c r="E45" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -15926,47 +16266,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90" t="s">
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="91" t="s">
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="81" t="s">
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -16198,12 +16538,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="84" t="s">
+      <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -17533,47 +17873,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90" t="s">
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="91" t="s">
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="81" t="s">
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -17805,12 +18145,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="84" t="s">
+      <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -17846,17 +18186,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="93"/>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="93"/>
+      <c r="D45" s="93"/>
+      <c r="E45" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -19234,47 +19574,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90" t="s">
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="91" t="s">
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="81" t="s">
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -19542,12 +19882,12 @@
       <c r="Q42" s="43">
         <v>9</v>
       </c>
-      <c r="R42" s="84" t="s">
+      <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -19583,22 +19923,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92">
+      <c r="C44" s="93">
         <f>10+5+1+54+8+256</f>
         <v>334</v>
       </c>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92">
+      <c r="C45" s="93">
         <v>12</v>
       </c>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="D45" s="93"/>
+      <c r="E45" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -20976,47 +21316,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90" t="s">
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="91" t="s">
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="81" t="s">
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -21280,12 +21620,12 @@
       <c r="Q42" s="43">
         <v>1</v>
       </c>
-      <c r="R42" s="84" t="s">
+      <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -21321,22 +21661,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92">
+      <c r="C44" s="93">
         <f>12+5+2+378</f>
         <v>397</v>
       </c>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92">
+      <c r="C45" s="93">
         <v>12</v>
       </c>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="D45" s="93"/>
+      <c r="E45" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -22633,47 +22973,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90" t="s">
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="91" t="s">
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="81" t="s">
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -22905,12 +23245,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="84" t="s">
+      <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -24240,47 +24580,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90" t="s">
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="91" t="s">
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="81" t="s">
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -24512,12 +24852,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="84" t="s">
+      <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -24553,17 +24893,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="93"/>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="93"/>
+      <c r="D45" s="93"/>
+      <c r="E45" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -25637,7 +25977,7 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="93">
+      <c r="F24" s="81">
         <v>2</v>
       </c>
       <c r="G24" s="14"/>
@@ -25929,47 +26269,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90" t="s">
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="91" t="s">
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="81" t="s">
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -26249,12 +26589,12 @@
       <c r="Q42" s="43">
         <v>16</v>
       </c>
-      <c r="R42" s="84" t="s">
+      <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -26290,20 +26630,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92">
+      <c r="C44" s="93">
         <f>2+5+1+2+1+25+46+10+282</f>
         <v>374</v>
       </c>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="93"/>
+      <c r="D45" s="93"/>
+      <c r="E45" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -27675,47 +28015,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90" t="s">
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="91" t="s">
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="81" t="s">
+      <c r="P34" s="92"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="84"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -27971,12 +28311,12 @@
       <c r="Q42" s="43">
         <v>17</v>
       </c>
-      <c r="R42" s="84" t="s">
+      <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -28012,20 +28352,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92">
+      <c r="C44" s="93">
         <f>8+1+53+6+271</f>
         <v>339</v>
       </c>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="93"/>
+      <c r="D45" s="93"/>
+      <c r="E45" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/GBDS JULY FILES 2026/CSR MONTH OF JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/CSR MONTH OF JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08666EC-4187-4BB8-9C7C-2D4C69884757}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B4E2E6-8779-4ADD-83DB-55FA7D86680C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="12" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="14" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | JULY" sheetId="902" r:id="rId1"/>

--- a/GBDS JULY FILES 2026/CSR MONTH OF JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/CSR MONTH OF JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B4E2E6-8779-4ADD-83DB-55FA7D86680C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260D1000-3052-417C-B8EA-1247463EFBB1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="14" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="15" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | JULY" sheetId="902" r:id="rId1"/>
@@ -26,10 +26,10 @@
     <sheet name="07-03 R1" sheetId="1800" r:id="rId11"/>
     <sheet name="07-03 R2" sheetId="1801" r:id="rId12"/>
     <sheet name="07-03 R3" sheetId="1802" r:id="rId13"/>
-    <sheet name="(4)" sheetId="1803" r:id="rId14"/>
-    <sheet name="07-04 R1" sheetId="1804" r:id="rId15"/>
-    <sheet name="07-04 R2" sheetId="1805" r:id="rId16"/>
-    <sheet name="07-04 R3" sheetId="1806" r:id="rId17"/>
+    <sheet name="(6)" sheetId="1803" r:id="rId14"/>
+    <sheet name="07-06 R1" sheetId="1804" r:id="rId15"/>
+    <sheet name="07-06 R2" sheetId="1805" r:id="rId16"/>
+    <sheet name="07-06 R3" sheetId="1806" r:id="rId17"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId18"/>
@@ -38,7 +38,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">'(1)'!$A$1:$Z$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'(2)'!$A$1:$Z$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'(3)'!$A$1:$Z$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="13">'(4)'!$A$1:$Z$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'(6)'!$A$1:$Z$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'07-01 R1 NO TRIP'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'07-01 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'07-01 R3'!$A$1:$V$44</definedName>
@@ -48,9 +48,9 @@
     <definedName name="_xlnm.Print_Area" localSheetId="10">'07-03 R1'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'07-03 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">'07-03 R3'!$A$1:$V$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="14">'07-04 R1'!$A$1:$Z$43</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="15">'07-04 R2'!$A$1:$V$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="16">'07-04 R3'!$A$1:$V$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'07-06 R1'!$A$1:$Z$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'07-06 R2'!$A$1:$V$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">'07-06 R3'!$A$1:$V$44</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="86">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -289,9 +289,6 @@
     <t>DATE ___________07/03/2026___________</t>
   </si>
   <si>
-    <t>DATE ___________07/04/2026___________</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
@@ -326,6 +323,9 @@
   </si>
   <si>
     <t>5/12B</t>
+  </si>
+  <si>
+    <t>DATE ___________07/06/2026___________</t>
   </si>
 </sst>
 </file>
@@ -3777,7 +3777,7 @@
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
       <c r="H8" s="81" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
@@ -4009,7 +4009,7 @@
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
       <c r="H16" s="28" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
@@ -5490,7 +5490,7 @@
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
       <c r="C8" s="77" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D8" s="14">
         <v>1</v>
@@ -5701,7 +5701,7 @@
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
       <c r="H15" s="23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
@@ -5741,7 +5741,7 @@
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
       <c r="H16" s="28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
@@ -6166,7 +6166,7 @@
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="79" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G24" s="14"/>
       <c r="H24" s="14">
@@ -6186,7 +6186,7 @@
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
       <c r="P24" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
@@ -6364,7 +6364,7 @@
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
       <c r="F31" s="23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G31" s="23"/>
       <c r="H31" s="23">
@@ -6384,7 +6384,7 @@
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
       <c r="P31" s="23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
@@ -7908,7 +7908,7 @@
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
       <c r="P24" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
@@ -8106,7 +8106,7 @@
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
       <c r="P31" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
@@ -10191,7 +10191,7 @@
     </row>
     <row r="2" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -10464,25 +10464,63 @@
       <c r="B7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="10"/>
-      <c r="S7" s="10"/>
-      <c r="T7" s="10"/>
-      <c r="U7" s="11"/>
+      <c r="C7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="R7" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="S7" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="T7" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>14</v>
+      </c>
       <c r="V7" s="10" t="s">
         <v>65</v>
       </c>
@@ -11776,7 +11814,7 @@
     </row>
     <row r="2" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -12121,12 +12159,20 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
+      <c r="C8" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="14">
+        <v>1</v>
+      </c>
+      <c r="E8" s="14">
+        <v>1</v>
+      </c>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>74</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -12138,10 +12184,14 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>1</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>3</v>
+      </c>
       <c r="X8" s="59"/>
       <c r="Y8" s="15"/>
     </row>
@@ -12309,12 +12359,20 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
+      <c r="D15" s="23">
+        <v>0</v>
+      </c>
+      <c r="E15" s="23">
+        <v>1</v>
+      </c>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>0</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -12326,10 +12384,14 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>1</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>3</v>
+      </c>
       <c r="X15" s="61"/>
       <c r="Y15" s="24"/>
     </row>
@@ -12337,12 +12399,18 @@
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+      <c r="D16" s="58">
+        <v>1</v>
+      </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>74</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -12354,10 +12422,14 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56">
+        <v>0</v>
+      </c>
       <c r="X16" s="62"/>
       <c r="Y16" s="29"/>
     </row>
@@ -12761,17 +12833,27 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="79"/>
+      <c r="F24" s="79" t="s">
+        <v>76</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>25</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
       <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="M24" s="14">
+        <v>436</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>77</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -12947,17 +13029,27 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23" t="s">
+        <v>76</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>0</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
+      <c r="K31" s="23">
+        <v>2</v>
+      </c>
       <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="M31" s="23">
+        <v>130</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>77</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -12975,17 +13067,27 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>25</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
       <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="M32" s="28">
+        <v>306</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -13122,20 +13224,32 @@
       <c r="B36" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="46"/>
+      <c r="C36" s="46">
+        <v>3</v>
+      </c>
       <c r="D36" s="41"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
+      <c r="E36" s="42">
+        <v>6</v>
+      </c>
+      <c r="F36" s="42">
+        <v>360</v>
+      </c>
       <c r="G36" s="42"/>
       <c r="H36" s="42"/>
       <c r="I36" s="42"/>
       <c r="J36" s="42"/>
       <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
+      <c r="L36" s="42">
+        <v>2</v>
+      </c>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
+      <c r="O36" s="42">
+        <v>9</v>
+      </c>
+      <c r="P36" s="42">
+        <v>8</v>
+      </c>
       <c r="Q36" s="43"/>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
@@ -13280,20 +13394,32 @@
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
+      <c r="C42" s="46">
+        <v>3</v>
+      </c>
       <c r="D42" s="41"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
+      <c r="E42" s="42">
+        <v>6</v>
+      </c>
+      <c r="F42" s="42">
+        <v>360</v>
+      </c>
       <c r="G42" s="42"/>
       <c r="H42" s="42"/>
       <c r="I42" s="42"/>
       <c r="J42" s="42"/>
       <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
+      <c r="L42" s="42">
+        <v>2</v>
+      </c>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
+      <c r="O42" s="42">
+        <v>9</v>
+      </c>
+      <c r="P42" s="42">
+        <v>8</v>
+      </c>
       <c r="Q42" s="43"/>
       <c r="R42" s="85" t="s">
         <v>54</v>
@@ -13336,7 +13462,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="93"/>
+      <c r="C44" s="93">
+        <f>1+10+25+306</f>
+        <v>342</v>
+      </c>
       <c r="D44" s="93"/>
       <c r="E44" s="93"/>
     </row>
@@ -13344,7 +13473,9 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="93"/>
+      <c r="C45" s="93">
+        <v>12</v>
+      </c>
       <c r="D45" s="93"/>
       <c r="E45" s="93"/>
     </row>
@@ -13399,7 +13530,7 @@
     </row>
     <row r="2" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -18595,7 +18726,7 @@
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
       <c r="C8" s="77" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D8" s="14">
         <v>1</v>
@@ -18606,7 +18737,7 @@
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
       <c r="H8" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
@@ -18850,7 +18981,7 @@
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
       <c r="H16" s="28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
@@ -19277,7 +19408,7 @@
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="79" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G24" s="14"/>
       <c r="H24" s="14">
@@ -19297,7 +19428,7 @@
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
       <c r="P24" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
@@ -19475,7 +19606,7 @@
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
       <c r="F31" s="23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G31" s="23"/>
       <c r="H31" s="23">
@@ -19495,7 +19626,7 @@
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
       <c r="P31" s="23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
@@ -20548,7 +20679,7 @@
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
       <c r="H15" s="23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
@@ -20590,7 +20721,7 @@
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
       <c r="H16" s="28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
@@ -21039,7 +21170,7 @@
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
       <c r="P24" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
@@ -21237,7 +21368,7 @@
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
       <c r="P31" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
@@ -25302,7 +25433,7 @@
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
       <c r="C8" s="77" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D8" s="14">
         <v>1</v>
@@ -25313,7 +25444,7 @@
       </c>
       <c r="G8" s="14"/>
       <c r="H8" s="14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
@@ -25513,7 +25644,7 @@
       </c>
       <c r="G15" s="23"/>
       <c r="H15" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
@@ -27051,7 +27182,7 @@
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
       <c r="H8" s="14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
@@ -27291,7 +27422,7 @@
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
       <c r="H16" s="28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
@@ -27738,7 +27869,7 @@
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
       <c r="P24" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
@@ -27936,7 +28067,7 @@
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
       <c r="P31" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>

--- a/GBDS JULY FILES 2026/CSR MONTH OF JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/CSR MONTH OF JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260D1000-3052-417C-B8EA-1247463EFBB1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B767777-EAD6-4C2F-B4C7-1D374172464F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="15" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="16" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | JULY" sheetId="902" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="86">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -10537,11 +10537,19 @@
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
       <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="D8" s="14">
+        <v>1</v>
+      </c>
+      <c r="E8" s="14">
+        <v>1</v>
+      </c>
+      <c r="F8" s="14">
+        <v>1</v>
+      </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>7</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -10552,7 +10560,9 @@
       <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
-      <c r="S8" s="14"/>
+      <c r="S8" s="14">
+        <v>6</v>
+      </c>
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
@@ -10725,11 +10735,19 @@
         <v>25</v>
       </c>
       <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="D15" s="23">
+        <v>1</v>
+      </c>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
+      <c r="F15" s="23">
+        <v>0</v>
+      </c>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>2</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -10740,7 +10758,9 @@
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
-      <c r="S15" s="23"/>
+      <c r="S15" s="23">
+        <v>1</v>
+      </c>
       <c r="T15" s="23"/>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
@@ -10753,11 +10773,19 @@
         <v>26</v>
       </c>
       <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
+      <c r="E16" s="27">
+        <v>1</v>
+      </c>
+      <c r="F16" s="27">
+        <v>1</v>
+      </c>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28">
+        <v>5</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -10768,7 +10796,9 @@
       <c r="P16" s="28"/>
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
-      <c r="S16" s="28"/>
+      <c r="S16" s="28">
+        <v>5</v>
+      </c>
       <c r="T16" s="28"/>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
@@ -11176,14 +11206,20 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>1</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>14</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
       <c r="K24" s="14"/>
       <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="M24" s="14">
+        <v>340</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
       <c r="P24" s="14"/>
@@ -11362,14 +11398,20 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>1</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>11</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
       <c r="K31" s="23"/>
       <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="M31" s="23">
+        <v>47</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
       <c r="P31" s="23"/>
@@ -11390,14 +11432,20 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>3</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
       <c r="K32" s="28"/>
       <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="M32" s="28">
+        <v>293</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
       <c r="P32" s="28"/>
@@ -11537,21 +11585,47 @@
       <c r="B36" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="46"/>
+      <c r="C36" s="46">
+        <v>6</v>
+      </c>
       <c r="D36" s="41"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
+      <c r="E36" s="42">
+        <v>1</v>
+      </c>
+      <c r="F36" s="42">
+        <v>299</v>
+      </c>
+      <c r="G36" s="42">
+        <v>4</v>
+      </c>
+      <c r="H36" s="42">
+        <v>6</v>
+      </c>
+      <c r="I36" s="42">
+        <v>9</v>
+      </c>
       <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="K36" s="42">
+        <v>6</v>
+      </c>
+      <c r="L36" s="42">
+        <v>3</v>
+      </c>
+      <c r="M36" s="42">
+        <v>2</v>
+      </c>
+      <c r="N36" s="42">
+        <v>33</v>
+      </c>
+      <c r="O36" s="42">
+        <v>7</v>
+      </c>
+      <c r="P36" s="42">
+        <v>10</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>19</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -11695,21 +11769,47 @@
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
+      <c r="C42" s="46">
+        <v>6</v>
+      </c>
       <c r="D42" s="41"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
+      <c r="E42" s="42">
+        <v>1</v>
+      </c>
+      <c r="F42" s="42">
+        <v>299</v>
+      </c>
+      <c r="G42" s="42">
+        <v>4</v>
+      </c>
+      <c r="H42" s="42">
+        <v>6</v>
+      </c>
+      <c r="I42" s="42">
+        <v>9</v>
+      </c>
       <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
-      <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="K42" s="42">
+        <v>6</v>
+      </c>
+      <c r="L42" s="42">
+        <v>3</v>
+      </c>
+      <c r="M42" s="42">
+        <v>2</v>
+      </c>
+      <c r="N42" s="42">
+        <v>33</v>
+      </c>
+      <c r="O42" s="42">
+        <v>7</v>
+      </c>
+      <c r="P42" s="42">
+        <v>10</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>19</v>
+      </c>
       <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
@@ -11751,7 +11851,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="93"/>
+      <c r="C44" s="93">
+        <f>1+1+5+5+3+293</f>
+        <v>308</v>
+      </c>
       <c r="D44" s="93"/>
       <c r="E44" s="93"/>
     </row>
@@ -13876,11 +13979,17 @@
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
       <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
+      <c r="D8" s="14">
+        <v>2</v>
+      </c>
+      <c r="E8" s="14">
+        <v>2</v>
+      </c>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>20</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -13891,13 +14000,19 @@
       <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
-      <c r="S8" s="14"/>
+      <c r="S8" s="14">
+        <v>2</v>
+      </c>
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>4</v>
+      </c>
       <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="Y8" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -14064,11 +14179,17 @@
         <v>25</v>
       </c>
       <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
+      <c r="D15" s="23">
+        <v>2</v>
+      </c>
+      <c r="E15" s="23">
+        <v>2</v>
+      </c>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>6</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -14079,24 +14200,36 @@
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
-      <c r="S15" s="23"/>
+      <c r="S15" s="23">
+        <v>0</v>
+      </c>
       <c r="T15" s="23"/>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>4</v>
+      </c>
       <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="Y15" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
       <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="27"/>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
+      <c r="E16" s="27">
+        <v>0</v>
+      </c>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28">
+        <v>14</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -14107,13 +14240,19 @@
       <c r="P16" s="28"/>
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
-      <c r="S16" s="28"/>
+      <c r="S16" s="28">
+        <v>2</v>
+      </c>
       <c r="T16" s="28"/>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56">
+        <v>0</v>
+      </c>
       <c r="X16" s="62"/>
-      <c r="Y16" s="29"/>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -14515,17 +14654,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>110</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14">
+        <v>1</v>
+      </c>
+      <c r="M24" s="14">
+        <v>470</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -14701,17 +14852,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>2</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>90</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>2</v>
+      </c>
+      <c r="L31" s="23">
+        <v>1</v>
+      </c>
+      <c r="M31" s="23">
+        <v>104</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>79</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -14729,17 +14892,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>20</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>0</v>
+      </c>
+      <c r="M32" s="28">
+        <v>266</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -14879,18 +15054,28 @@
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
+      <c r="F36" s="42">
+        <v>437</v>
+      </c>
       <c r="G36" s="42"/>
       <c r="H36" s="42"/>
       <c r="I36" s="42"/>
       <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
+      <c r="K36" s="42">
+        <v>4</v>
+      </c>
+      <c r="L36" s="42">
+        <v>1</v>
+      </c>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
+      <c r="O36" s="42">
+        <v>14</v>
+      </c>
       <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="Q36" s="43">
+        <v>3</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -15037,18 +15222,28 @@
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
+      <c r="F42" s="42">
+        <v>437</v>
+      </c>
       <c r="G42" s="42"/>
       <c r="H42" s="42"/>
       <c r="I42" s="42"/>
       <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
+      <c r="K42" s="42">
+        <v>4</v>
+      </c>
+      <c r="L42" s="42">
+        <v>1</v>
+      </c>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
+      <c r="O42" s="42">
+        <v>14</v>
+      </c>
       <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="Q42" s="43">
+        <v>3</v>
+      </c>
       <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
@@ -15090,7 +15285,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="93"/>
+      <c r="C44" s="93">
+        <f>14+2+20+266</f>
+        <v>302</v>
+      </c>
       <c r="D44" s="93"/>
       <c r="E44" s="93"/>
     </row>

--- a/GBDS JULY FILES 2026/CSR MONTH OF JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/CSR MONTH OF JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B767777-EAD6-4C2F-B4C7-1D374172464F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B8A8AC-5014-4641-8C6A-CF8F4C9C3FC2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="16" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="8" activeTab="20" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | JULY" sheetId="902" r:id="rId1"/>
@@ -30,15 +30,20 @@
     <sheet name="07-06 R1" sheetId="1804" r:id="rId15"/>
     <sheet name="07-06 R2" sheetId="1805" r:id="rId16"/>
     <sheet name="07-06 R3" sheetId="1806" r:id="rId17"/>
+    <sheet name="(7)" sheetId="1807" r:id="rId18"/>
+    <sheet name="07-07 R1" sheetId="1808" r:id="rId19"/>
+    <sheet name="07-07 R2" sheetId="1809" r:id="rId20"/>
+    <sheet name="07-07 R3" sheetId="1810" r:id="rId21"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId18"/>
+    <externalReference r:id="rId22"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'(1)'!$A$1:$Z$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'(2)'!$A$1:$Z$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'(3)'!$A$1:$Z$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'(6)'!$A$1:$Z$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="17">'(7)'!$A$1:$Z$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'07-01 R1 NO TRIP'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'07-01 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'07-01 R3'!$A$1:$V$44</definedName>
@@ -51,6 +56,9 @@
     <definedName name="_xlnm.Print_Area" localSheetId="14">'07-06 R1'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="15">'07-06 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="16">'07-06 R3'!$A$1:$V$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="18">'07-07 R1'!$A$1:$Z$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="19">'07-07 R2'!$A$1:$V$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="20">'07-07 R3'!$A$1:$V$44</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -68,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="87">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -326,6 +334,9 @@
   </si>
   <si>
     <t>DATE ___________07/06/2026___________</t>
+  </si>
+  <si>
+    <t>DATE ___________07/07/2026___________</t>
   </si>
 </sst>
 </file>
@@ -946,7 +957,7 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1201,6 +1212,9 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3062,47 +3076,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="87" t="s">
+      <c r="B34" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="89" t="s">
+      <c r="C34" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="89"/>
-      <c r="E34" s="90"/>
-      <c r="F34" s="91" t="s">
+      <c r="D34" s="90"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="89"/>
-      <c r="H34" s="90"/>
-      <c r="I34" s="91" t="s">
+      <c r="G34" s="90"/>
+      <c r="H34" s="91"/>
+      <c r="I34" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="89"/>
-      <c r="K34" s="90"/>
-      <c r="L34" s="91" t="s">
+      <c r="J34" s="90"/>
+      <c r="K34" s="91"/>
+      <c r="L34" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="89"/>
-      <c r="N34" s="90"/>
-      <c r="O34" s="92" t="s">
+      <c r="M34" s="90"/>
+      <c r="N34" s="91"/>
+      <c r="O34" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="92"/>
-      <c r="Q34" s="92"/>
-      <c r="R34" s="82" t="s">
+      <c r="P34" s="93"/>
+      <c r="Q34" s="93"/>
+      <c r="R34" s="83" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="83"/>
-      <c r="T34" s="83"/>
-      <c r="U34" s="84"/>
+      <c r="S34" s="84"/>
+      <c r="T34" s="84"/>
+      <c r="U34" s="85"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="88"/>
+      <c r="B35" s="89"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -3334,12 +3348,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="85" t="s">
+      <c r="R42" s="86" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="86"/>
-      <c r="T42" s="86"/>
-      <c r="U42" s="86"/>
+      <c r="S42" s="87"/>
+      <c r="T42" s="87"/>
+      <c r="U42" s="87"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -4723,47 +4737,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="87" t="s">
+      <c r="B34" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="89" t="s">
+      <c r="C34" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="89"/>
-      <c r="E34" s="90"/>
-      <c r="F34" s="91" t="s">
+      <c r="D34" s="90"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="89"/>
-      <c r="H34" s="90"/>
-      <c r="I34" s="91" t="s">
+      <c r="G34" s="90"/>
+      <c r="H34" s="91"/>
+      <c r="I34" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="89"/>
-      <c r="K34" s="90"/>
-      <c r="L34" s="91" t="s">
+      <c r="J34" s="90"/>
+      <c r="K34" s="91"/>
+      <c r="L34" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="89"/>
-      <c r="N34" s="90"/>
-      <c r="O34" s="92" t="s">
+      <c r="M34" s="90"/>
+      <c r="N34" s="91"/>
+      <c r="O34" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="92"/>
-      <c r="Q34" s="92"/>
-      <c r="R34" s="82" t="s">
+      <c r="P34" s="93"/>
+      <c r="Q34" s="93"/>
+      <c r="R34" s="83" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="83"/>
-      <c r="T34" s="83"/>
-      <c r="U34" s="84"/>
+      <c r="S34" s="84"/>
+      <c r="T34" s="84"/>
+      <c r="U34" s="85"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="88"/>
+      <c r="B35" s="89"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -5035,12 +5049,12 @@
       <c r="Q42" s="43">
         <v>3</v>
       </c>
-      <c r="R42" s="85" t="s">
+      <c r="R42" s="86" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="86"/>
-      <c r="T42" s="86"/>
-      <c r="U42" s="86"/>
+      <c r="S42" s="87"/>
+      <c r="T42" s="87"/>
+      <c r="U42" s="87"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -5076,22 +5090,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="93">
+      <c r="C44" s="94">
         <f>1+1+6+1+8+1+16+404</f>
         <v>438</v>
       </c>
-      <c r="D44" s="93"/>
-      <c r="E44" s="93"/>
+      <c r="D44" s="94"/>
+      <c r="E44" s="94"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="93">
+      <c r="C45" s="94">
         <v>12</v>
       </c>
-      <c r="D45" s="93"/>
-      <c r="E45" s="93"/>
+      <c r="D45" s="94"/>
+      <c r="E45" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -6463,47 +6477,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="87" t="s">
+      <c r="B34" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="89" t="s">
+      <c r="C34" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="89"/>
-      <c r="E34" s="90"/>
-      <c r="F34" s="91" t="s">
+      <c r="D34" s="90"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="89"/>
-      <c r="H34" s="90"/>
-      <c r="I34" s="91" t="s">
+      <c r="G34" s="90"/>
+      <c r="H34" s="91"/>
+      <c r="I34" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="89"/>
-      <c r="K34" s="90"/>
-      <c r="L34" s="91" t="s">
+      <c r="J34" s="90"/>
+      <c r="K34" s="91"/>
+      <c r="L34" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="89"/>
-      <c r="N34" s="90"/>
-      <c r="O34" s="92" t="s">
+      <c r="M34" s="90"/>
+      <c r="N34" s="91"/>
+      <c r="O34" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="92"/>
-      <c r="Q34" s="92"/>
-      <c r="R34" s="82" t="s">
+      <c r="P34" s="93"/>
+      <c r="Q34" s="93"/>
+      <c r="R34" s="83" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="83"/>
-      <c r="T34" s="83"/>
-      <c r="U34" s="84"/>
+      <c r="S34" s="84"/>
+      <c r="T34" s="84"/>
+      <c r="U34" s="85"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="88"/>
+      <c r="B35" s="89"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -6751,12 +6765,12 @@
       <c r="Q42" s="43">
         <v>11</v>
       </c>
-      <c r="R42" s="85" t="s">
+      <c r="R42" s="86" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="86"/>
-      <c r="T42" s="86"/>
-      <c r="U42" s="86"/>
+      <c r="S42" s="87"/>
+      <c r="T42" s="87"/>
+      <c r="U42" s="87"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -6792,22 +6806,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="93">
+      <c r="C44" s="94">
         <f>8+1+30+2+322</f>
         <v>363</v>
       </c>
-      <c r="D44" s="93"/>
-      <c r="E44" s="93"/>
+      <c r="D44" s="94"/>
+      <c r="E44" s="94"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="93">
+      <c r="C45" s="94">
         <v>12</v>
       </c>
-      <c r="D45" s="93"/>
-      <c r="E45" s="93"/>
+      <c r="D45" s="94"/>
+      <c r="E45" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -8185,47 +8199,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="87" t="s">
+      <c r="B34" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="89" t="s">
+      <c r="C34" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="89"/>
-      <c r="E34" s="90"/>
-      <c r="F34" s="91" t="s">
+      <c r="D34" s="90"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="89"/>
-      <c r="H34" s="90"/>
-      <c r="I34" s="91" t="s">
+      <c r="G34" s="90"/>
+      <c r="H34" s="91"/>
+      <c r="I34" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="89"/>
-      <c r="K34" s="90"/>
-      <c r="L34" s="91" t="s">
+      <c r="J34" s="90"/>
+      <c r="K34" s="91"/>
+      <c r="L34" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="89"/>
-      <c r="N34" s="90"/>
-      <c r="O34" s="92" t="s">
+      <c r="M34" s="90"/>
+      <c r="N34" s="91"/>
+      <c r="O34" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="92"/>
-      <c r="Q34" s="92"/>
-      <c r="R34" s="82" t="s">
+      <c r="P34" s="93"/>
+      <c r="Q34" s="93"/>
+      <c r="R34" s="83" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="83"/>
-      <c r="T34" s="83"/>
-      <c r="U34" s="84"/>
+      <c r="S34" s="84"/>
+      <c r="T34" s="84"/>
+      <c r="U34" s="85"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="88"/>
+      <c r="B35" s="89"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -8483,12 +8497,12 @@
       <c r="Q42" s="43">
         <v>16</v>
       </c>
-      <c r="R42" s="85" t="s">
+      <c r="R42" s="86" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="86"/>
-      <c r="T42" s="86"/>
-      <c r="U42" s="86"/>
+      <c r="S42" s="87"/>
+      <c r="T42" s="87"/>
+      <c r="U42" s="87"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -8524,17 +8538,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="93"/>
-      <c r="D44" s="93"/>
-      <c r="E44" s="93"/>
+      <c r="C44" s="94"/>
+      <c r="D44" s="94"/>
+      <c r="E44" s="94"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="93"/>
-      <c r="D45" s="93"/>
-      <c r="E45" s="93"/>
+      <c r="C45" s="94"/>
+      <c r="D45" s="94"/>
+      <c r="E45" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -9831,47 +9845,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="87" t="s">
+      <c r="B34" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="89" t="s">
+      <c r="C34" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="89"/>
-      <c r="E34" s="90"/>
-      <c r="F34" s="91" t="s">
+      <c r="D34" s="90"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="89"/>
-      <c r="H34" s="90"/>
-      <c r="I34" s="91" t="s">
+      <c r="G34" s="90"/>
+      <c r="H34" s="91"/>
+      <c r="I34" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="89"/>
-      <c r="K34" s="90"/>
-      <c r="L34" s="91" t="s">
+      <c r="J34" s="90"/>
+      <c r="K34" s="91"/>
+      <c r="L34" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="89"/>
-      <c r="N34" s="90"/>
-      <c r="O34" s="92" t="s">
+      <c r="M34" s="90"/>
+      <c r="N34" s="91"/>
+      <c r="O34" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="92"/>
-      <c r="Q34" s="92"/>
-      <c r="R34" s="82" t="s">
+      <c r="P34" s="93"/>
+      <c r="Q34" s="93"/>
+      <c r="R34" s="83" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="83"/>
-      <c r="T34" s="83"/>
-      <c r="U34" s="84"/>
+      <c r="S34" s="84"/>
+      <c r="T34" s="84"/>
+      <c r="U34" s="85"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="88"/>
+      <c r="B35" s="89"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -10103,12 +10117,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="85" t="s">
+      <c r="R42" s="86" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="86"/>
-      <c r="T42" s="86"/>
-      <c r="U42" s="86"/>
+      <c r="S42" s="87"/>
+      <c r="T42" s="87"/>
+      <c r="U42" s="87"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -11486,47 +11500,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="87" t="s">
+      <c r="B34" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="89" t="s">
+      <c r="C34" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="89"/>
-      <c r="E34" s="90"/>
-      <c r="F34" s="91" t="s">
+      <c r="D34" s="90"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="89"/>
-      <c r="H34" s="90"/>
-      <c r="I34" s="91" t="s">
+      <c r="G34" s="90"/>
+      <c r="H34" s="91"/>
+      <c r="I34" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="89"/>
-      <c r="K34" s="90"/>
-      <c r="L34" s="91" t="s">
+      <c r="J34" s="90"/>
+      <c r="K34" s="91"/>
+      <c r="L34" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="89"/>
-      <c r="N34" s="90"/>
-      <c r="O34" s="92" t="s">
+      <c r="M34" s="90"/>
+      <c r="N34" s="91"/>
+      <c r="O34" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="92"/>
-      <c r="Q34" s="92"/>
-      <c r="R34" s="82" t="s">
+      <c r="P34" s="93"/>
+      <c r="Q34" s="93"/>
+      <c r="R34" s="83" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="83"/>
-      <c r="T34" s="83"/>
-      <c r="U34" s="84"/>
+      <c r="S34" s="84"/>
+      <c r="T34" s="84"/>
+      <c r="U34" s="85"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="88"/>
+      <c r="B35" s="89"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -11810,12 +11824,12 @@
       <c r="Q42" s="43">
         <v>19</v>
       </c>
-      <c r="R42" s="85" t="s">
+      <c r="R42" s="86" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="86"/>
-      <c r="T42" s="86"/>
-      <c r="U42" s="86"/>
+      <c r="S42" s="87"/>
+      <c r="T42" s="87"/>
+      <c r="U42" s="87"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -11851,20 +11865,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="93">
+      <c r="C44" s="94">
         <f>1+1+5+5+3+293</f>
         <v>308</v>
       </c>
-      <c r="D44" s="93"/>
-      <c r="E44" s="93"/>
+      <c r="D44" s="94"/>
+      <c r="E44" s="94"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="93"/>
-      <c r="D45" s="93"/>
-      <c r="E45" s="93"/>
+      <c r="C45" s="94"/>
+      <c r="D45" s="94"/>
+      <c r="E45" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -13228,47 +13242,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="87" t="s">
+      <c r="B34" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="89" t="s">
+      <c r="C34" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="89"/>
-      <c r="E34" s="90"/>
-      <c r="F34" s="91" t="s">
+      <c r="D34" s="90"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="89"/>
-      <c r="H34" s="90"/>
-      <c r="I34" s="91" t="s">
+      <c r="G34" s="90"/>
+      <c r="H34" s="91"/>
+      <c r="I34" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="89"/>
-      <c r="K34" s="90"/>
-      <c r="L34" s="91" t="s">
+      <c r="J34" s="90"/>
+      <c r="K34" s="91"/>
+      <c r="L34" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="89"/>
-      <c r="N34" s="90"/>
-      <c r="O34" s="92" t="s">
+      <c r="M34" s="90"/>
+      <c r="N34" s="91"/>
+      <c r="O34" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="92"/>
-      <c r="Q34" s="92"/>
-      <c r="R34" s="82" t="s">
+      <c r="P34" s="93"/>
+      <c r="Q34" s="93"/>
+      <c r="R34" s="83" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="83"/>
-      <c r="T34" s="83"/>
-      <c r="U34" s="84"/>
+      <c r="S34" s="84"/>
+      <c r="T34" s="84"/>
+      <c r="U34" s="85"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="88"/>
+      <c r="B35" s="89"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -13524,12 +13538,12 @@
         <v>8</v>
       </c>
       <c r="Q42" s="43"/>
-      <c r="R42" s="85" t="s">
+      <c r="R42" s="86" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="86"/>
-      <c r="T42" s="86"/>
-      <c r="U42" s="86"/>
+      <c r="S42" s="87"/>
+      <c r="T42" s="87"/>
+      <c r="U42" s="87"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -13565,22 +13579,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="93">
+      <c r="C44" s="94">
         <f>1+10+25+306</f>
         <v>342</v>
       </c>
-      <c r="D44" s="93"/>
-      <c r="E44" s="93"/>
+      <c r="D44" s="94"/>
+      <c r="E44" s="94"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="93">
+      <c r="C45" s="94">
         <v>12</v>
       </c>
-      <c r="D45" s="93"/>
-      <c r="E45" s="93"/>
+      <c r="D45" s="94"/>
+      <c r="E45" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -14952,47 +14966,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="87" t="s">
+      <c r="B34" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="89" t="s">
+      <c r="C34" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="89"/>
-      <c r="E34" s="90"/>
-      <c r="F34" s="91" t="s">
+      <c r="D34" s="90"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="89"/>
-      <c r="H34" s="90"/>
-      <c r="I34" s="91" t="s">
+      <c r="G34" s="90"/>
+      <c r="H34" s="91"/>
+      <c r="I34" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="89"/>
-      <c r="K34" s="90"/>
-      <c r="L34" s="91" t="s">
+      <c r="J34" s="90"/>
+      <c r="K34" s="91"/>
+      <c r="L34" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="89"/>
-      <c r="N34" s="90"/>
-      <c r="O34" s="92" t="s">
+      <c r="M34" s="90"/>
+      <c r="N34" s="91"/>
+      <c r="O34" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="92"/>
-      <c r="Q34" s="92"/>
-      <c r="R34" s="82" t="s">
+      <c r="P34" s="93"/>
+      <c r="Q34" s="93"/>
+      <c r="R34" s="83" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="83"/>
-      <c r="T34" s="83"/>
-      <c r="U34" s="84"/>
+      <c r="S34" s="84"/>
+      <c r="T34" s="84"/>
+      <c r="U34" s="85"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="88"/>
+      <c r="B35" s="89"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -15244,12 +15258,12 @@
       <c r="Q42" s="43">
         <v>3</v>
       </c>
-      <c r="R42" s="85" t="s">
+      <c r="R42" s="86" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="86"/>
-      <c r="T42" s="86"/>
-      <c r="U42" s="86"/>
+      <c r="S42" s="87"/>
+      <c r="T42" s="87"/>
+      <c r="U42" s="87"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -15285,20 +15299,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="93">
+      <c r="C44" s="94">
         <f>14+2+20+266</f>
         <v>302</v>
       </c>
-      <c r="D44" s="93"/>
-      <c r="E44" s="93"/>
+      <c r="D44" s="94"/>
+      <c r="E44" s="94"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="93"/>
-      <c r="D45" s="93"/>
-      <c r="E45" s="93"/>
+      <c r="C45" s="94"/>
+      <c r="D45" s="94"/>
+      <c r="E45" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -15316,6 +15330,3296 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="90" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F140EC48-F116-412C-876B-BD25C51A6FB3}">
+  <dimension ref="B1:AA43"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
+    <col min="3" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.140625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.140625" style="2" customWidth="1"/>
+    <col min="20" max="21" width="5.7109375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="29" width="5.7109375" style="2" customWidth="1"/>
+    <col min="30" max="16384" width="8.7109375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="3"/>
+    </row>
+    <row r="2" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6">
+        <f>[1]DSSR!B4</f>
+        <v>1300</v>
+      </c>
+      <c r="D3" s="6">
+        <f>[1]DSSR!C4</f>
+        <v>1534</v>
+      </c>
+      <c r="E3" s="6">
+        <f>[1]DSSR!D4</f>
+        <v>1728</v>
+      </c>
+      <c r="F3" s="6">
+        <f>[1]DSSR!E4</f>
+        <v>1728</v>
+      </c>
+      <c r="G3" s="6">
+        <f>[1]DSSR!F4</f>
+        <v>1452</v>
+      </c>
+      <c r="H3" s="6">
+        <f>[1]DSSR!G4</f>
+        <v>1240</v>
+      </c>
+      <c r="I3" s="6">
+        <f>[1]DSSR!H4</f>
+        <v>1520</v>
+      </c>
+      <c r="J3" s="6">
+        <f>[1]DSSR!I4</f>
+        <v>978</v>
+      </c>
+      <c r="K3" s="6">
+        <f>[1]DSSR!J4</f>
+        <v>945</v>
+      </c>
+      <c r="L3" s="6">
+        <f>[1]DSSR!K4</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="6">
+        <f>[1]DSSR!L4</f>
+        <v>1127</v>
+      </c>
+      <c r="N3" s="6">
+        <f>[1]DSSR!M4</f>
+        <v>773</v>
+      </c>
+      <c r="O3" s="6">
+        <f>[1]DSSR!N4</f>
+        <v>1038</v>
+      </c>
+      <c r="P3" s="6">
+        <f>[1]DSSR!O4</f>
+        <v>773</v>
+      </c>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6">
+        <f>[1]DSSR!P4</f>
+        <v>1038</v>
+      </c>
+      <c r="U3" s="6">
+        <f>[1]DSSR!Q4</f>
+        <v>773</v>
+      </c>
+      <c r="V3" s="6">
+        <f>[1]DSSR!R4</f>
+        <v>1038</v>
+      </c>
+      <c r="W3" s="6">
+        <f>[1]DSSR!S4</f>
+        <v>792</v>
+      </c>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6">
+        <f>[1]DSSR!T4</f>
+        <v>948</v>
+      </c>
+    </row>
+    <row r="4" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6">
+        <f>[1]DSSR!B5</f>
+        <v>120</v>
+      </c>
+      <c r="D4" s="6">
+        <f>[1]DSSR!C5</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="6">
+        <f>[1]DSSR!D5</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <f>[1]DSSR!E5</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="6">
+        <f>[1]DSSR!F5</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
+        <f>[1]DSSR!G5</f>
+        <v>120</v>
+      </c>
+      <c r="I4" s="6">
+        <f>[1]DSSR!H5</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <f>[1]DSSR!I5</f>
+        <v>120</v>
+      </c>
+      <c r="K4" s="6">
+        <f>[1]DSSR!J5</f>
+        <v>120</v>
+      </c>
+      <c r="L4" s="6">
+        <f>[1]DSSR!K5</f>
+        <v>111</v>
+      </c>
+      <c r="M4" s="6">
+        <f>[1]DSSR!L5</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="6">
+        <f>[1]DSSR!M5</f>
+        <v>120</v>
+      </c>
+      <c r="O4" s="6">
+        <f>[1]DSSR!N5</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="6">
+        <f>[1]DSSR!O5</f>
+        <v>120</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6">
+        <f>[1]DSSR!P5</f>
+        <v>0</v>
+      </c>
+      <c r="U4" s="6">
+        <f>[1]DSSR!Q5</f>
+        <v>120</v>
+      </c>
+      <c r="V4" s="6">
+        <f>[1]DSSR!R5</f>
+        <v>0</v>
+      </c>
+      <c r="W4" s="6">
+        <f>[1]DSSR!S5</f>
+        <v>120</v>
+      </c>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6">
+        <f>[1]DSSR!T5</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="7">
+        <v>84</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7">
+        <v>84</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7">
+        <v>84</v>
+      </c>
+      <c r="K5" s="7">
+        <v>84</v>
+      </c>
+      <c r="L5" s="7">
+        <v>84</v>
+      </c>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7">
+        <v>84</v>
+      </c>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7">
+        <v>84</v>
+      </c>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7">
+        <v>84</v>
+      </c>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7">
+        <v>84</v>
+      </c>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="L6" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="8"/>
+      <c r="C7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="R7" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="S7" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="T7" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="V7" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y7" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="12"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="14"/>
+      <c r="X8" s="59"/>
+      <c r="Y8" s="15"/>
+    </row>
+    <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="60"/>
+      <c r="Y9" s="20"/>
+    </row>
+    <row r="10" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="60"/>
+      <c r="Y10" s="20"/>
+    </row>
+    <row r="11" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="16"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="60"/>
+      <c r="Y11" s="20"/>
+    </row>
+    <row r="12" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="60"/>
+      <c r="Y12" s="20"/>
+    </row>
+    <row r="13" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="60"/>
+      <c r="Y13" s="20"/>
+    </row>
+    <row r="14" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="16"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="19"/>
+      <c r="V14" s="19"/>
+      <c r="W14" s="19"/>
+      <c r="X14" s="60"/>
+      <c r="Y14" s="20"/>
+    </row>
+    <row r="15" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="T15" s="23"/>
+      <c r="U15" s="23"/>
+      <c r="V15" s="23"/>
+      <c r="W15" s="23"/>
+      <c r="X15" s="61"/>
+      <c r="Y15" s="24"/>
+    </row>
+    <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="57"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28"/>
+      <c r="U16" s="28"/>
+      <c r="V16" s="28"/>
+      <c r="W16" s="56"/>
+      <c r="X16" s="62"/>
+      <c r="Y16" s="29"/>
+    </row>
+    <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="32"/>
+    </row>
+    <row r="18" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="34">
+        <f>[1]DSSR!B24</f>
+        <v>544</v>
+      </c>
+      <c r="D18" s="34">
+        <f>[1]DSSR!C24</f>
+        <v>1127</v>
+      </c>
+      <c r="E18" s="34">
+        <f>[1]DSSR!D24</f>
+        <v>853</v>
+      </c>
+      <c r="F18" s="34">
+        <f>[1]DSSR!E24</f>
+        <v>563</v>
+      </c>
+      <c r="G18" s="34">
+        <f>[1]DSSR!F24</f>
+        <v>575</v>
+      </c>
+      <c r="H18" s="34">
+        <f>[1]DSSR!G24</f>
+        <v>1175</v>
+      </c>
+      <c r="I18" s="34">
+        <f>[1]DSSR!H24</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="34">
+        <f>[1]DSSR!I24</f>
+        <v>791</v>
+      </c>
+      <c r="K18" s="34">
+        <f>[1]DSSR!J24</f>
+        <v>1102</v>
+      </c>
+      <c r="L18" s="34">
+        <f>[1]DSSR!K24</f>
+        <v>520</v>
+      </c>
+      <c r="M18" s="34">
+        <f>[1]DSSR!L24</f>
+        <v>1142</v>
+      </c>
+      <c r="N18" s="34">
+        <f>[1]DSSR!M24</f>
+        <v>205</v>
+      </c>
+      <c r="O18" s="34">
+        <f>[1]DSSR!N24</f>
+        <v>205</v>
+      </c>
+      <c r="P18" s="34">
+        <f>[1]DSSR!O24</f>
+        <v>205</v>
+      </c>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="34"/>
+      <c r="S18" s="34"/>
+      <c r="T18" s="34">
+        <f>[1]DSSR!P24</f>
+        <v>500</v>
+      </c>
+      <c r="U18" s="34">
+        <f>[1]DSSR!Q24</f>
+        <v>650</v>
+      </c>
+      <c r="V18" s="34">
+        <f>[1]DSSR!R24</f>
+        <v>650</v>
+      </c>
+      <c r="W18" s="34">
+        <f>[1]DSSR!S24</f>
+        <v>500</v>
+      </c>
+      <c r="X18" s="34"/>
+      <c r="Y18" s="35">
+        <f>[1]DSSR!T24</f>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="34">
+        <f>[1]DSSR!B25</f>
+        <v>111</v>
+      </c>
+      <c r="D19" s="34">
+        <f>[1]DSSR!C25</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="34">
+        <f>[1]DSSR!D25</f>
+        <v>120</v>
+      </c>
+      <c r="F19" s="34">
+        <f>[1]DSSR!E25</f>
+        <v>111</v>
+      </c>
+      <c r="G19" s="34">
+        <f>[1]DSSR!F25</f>
+        <v>111</v>
+      </c>
+      <c r="H19" s="34">
+        <f>[1]DSSR!G25</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="34">
+        <f>[1]DSSR!H25</f>
+        <v>111</v>
+      </c>
+      <c r="J19" s="34">
+        <f>[1]DSSR!I25</f>
+        <v>120</v>
+      </c>
+      <c r="K19" s="34">
+        <f>[1]DSSR!J25</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="34">
+        <f>[1]DSSR!K25</f>
+        <v>111</v>
+      </c>
+      <c r="M19" s="34">
+        <f>[1]DSSR!L25</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="34">
+        <f>[1]DSSR!M25</f>
+        <v>78</v>
+      </c>
+      <c r="O19" s="34">
+        <f>[1]DSSR!N25</f>
+        <v>78</v>
+      </c>
+      <c r="P19" s="34">
+        <f>[1]DSSR!O25</f>
+        <v>78</v>
+      </c>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+      <c r="S19" s="34"/>
+      <c r="T19" s="34">
+        <f>[1]DSSR!P25</f>
+        <v>120</v>
+      </c>
+      <c r="U19" s="34">
+        <f>[1]DSSR!Q25</f>
+        <v>0</v>
+      </c>
+      <c r="V19" s="34">
+        <f>[1]DSSR!R25</f>
+        <v>0</v>
+      </c>
+      <c r="W19" s="34">
+        <f>[1]DSSR!S25</f>
+        <v>120</v>
+      </c>
+      <c r="X19" s="34"/>
+      <c r="Y19" s="35">
+        <f>[1]DSSR!T25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="34">
+        <v>84</v>
+      </c>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34">
+        <v>84</v>
+      </c>
+      <c r="F20" s="34">
+        <v>84</v>
+      </c>
+      <c r="G20" s="34">
+        <v>84</v>
+      </c>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34">
+        <v>84</v>
+      </c>
+      <c r="J20" s="34">
+        <v>84</v>
+      </c>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34">
+        <v>84</v>
+      </c>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34">
+        <v>42</v>
+      </c>
+      <c r="O20" s="34">
+        <v>42</v>
+      </c>
+      <c r="P20" s="34">
+        <v>42</v>
+      </c>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="34"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="34">
+        <v>84</v>
+      </c>
+      <c r="U20" s="34"/>
+      <c r="V20" s="34"/>
+      <c r="W20" s="34">
+        <v>84</v>
+      </c>
+      <c r="X20" s="34"/>
+      <c r="Y20" s="35"/>
+    </row>
+    <row r="21" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="F21" s="36">
+        <f>4.5/2</f>
+        <v>2.25</v>
+      </c>
+      <c r="G21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="J21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="O21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="P21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+      <c r="S21" s="34"/>
+      <c r="T21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="U21" s="34"/>
+      <c r="V21" s="34"/>
+      <c r="W21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="X21" s="34"/>
+      <c r="Y21" s="35"/>
+    </row>
+    <row r="22" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="33"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="34"/>
+      <c r="S22" s="34"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="34"/>
+      <c r="V22" s="34"/>
+      <c r="W22" s="34"/>
+      <c r="X22" s="34"/>
+      <c r="Y22" s="35"/>
+    </row>
+    <row r="23" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="37"/>
+      <c r="C23" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O23" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P23" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q23" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="R23" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="V23" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="11"/>
+    </row>
+    <row r="24" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="14"/>
+      <c r="Y24" s="15"/>
+    </row>
+    <row r="25" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="17"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="19"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="19"/>
+      <c r="X25" s="60"/>
+      <c r="Y25" s="20"/>
+    </row>
+    <row r="26" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="16"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="19"/>
+      <c r="U26" s="19"/>
+      <c r="V26" s="19"/>
+      <c r="W26" s="19"/>
+      <c r="X26" s="60"/>
+      <c r="Y26" s="20"/>
+    </row>
+    <row r="27" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="16"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="19"/>
+      <c r="U27" s="19"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="19"/>
+      <c r="X27" s="60"/>
+      <c r="Y27" s="20"/>
+    </row>
+    <row r="28" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="16"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="19"/>
+      <c r="X28" s="60"/>
+      <c r="Y28" s="20"/>
+    </row>
+    <row r="29" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="16"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="19"/>
+      <c r="W29" s="19"/>
+      <c r="X29" s="60"/>
+      <c r="Y29" s="20"/>
+    </row>
+    <row r="30" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="16"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="19"/>
+      <c r="U30" s="19"/>
+      <c r="V30" s="19"/>
+      <c r="W30" s="19"/>
+      <c r="X30" s="60"/>
+      <c r="Y30" s="20"/>
+    </row>
+    <row r="31" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
+      <c r="M31" s="23"/>
+      <c r="N31" s="23"/>
+      <c r="O31" s="23"/>
+      <c r="P31" s="23"/>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="23"/>
+      <c r="S31" s="23"/>
+      <c r="T31" s="23"/>
+      <c r="U31" s="23"/>
+      <c r="V31" s="23"/>
+      <c r="W31" s="23"/>
+      <c r="X31" s="61"/>
+      <c r="Y31" s="24"/>
+    </row>
+    <row r="32" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="26"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="23"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="28"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="63"/>
+      <c r="Y32" s="29"/>
+    </row>
+    <row r="33" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="30"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="68"/>
+      <c r="S33" s="68"/>
+      <c r="T33" s="68"/>
+      <c r="U33" s="68"/>
+      <c r="V33" s="31"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="31"/>
+      <c r="Y33" s="31"/>
+    </row>
+    <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="88" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="90"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="92" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="90"/>
+      <c r="H34" s="91"/>
+      <c r="I34" s="92" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34" s="90"/>
+      <c r="K34" s="91"/>
+      <c r="L34" s="92" t="s">
+        <v>46</v>
+      </c>
+      <c r="M34" s="90"/>
+      <c r="N34" s="91"/>
+      <c r="O34" s="93" t="s">
+        <v>47</v>
+      </c>
+      <c r="P34" s="93"/>
+      <c r="Q34" s="93"/>
+      <c r="R34" s="83" t="s">
+        <v>48</v>
+      </c>
+      <c r="S34" s="84"/>
+      <c r="T34" s="84"/>
+      <c r="U34" s="85"/>
+      <c r="V34" s="66"/>
+      <c r="W34" s="3"/>
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
+    </row>
+    <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="89"/>
+      <c r="C35" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="G35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="J35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="K35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="L35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="M35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="N35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="O35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="P35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q35" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="R35" s="69"/>
+      <c r="S35" s="70"/>
+      <c r="T35" s="70"/>
+      <c r="U35" s="71"/>
+      <c r="V35" s="82"/>
+      <c r="W35" s="82"/>
+      <c r="X35" s="82"/>
+      <c r="Y35" s="82"/>
+    </row>
+    <row r="36" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="46"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="42"/>
+      <c r="L36" s="42"/>
+      <c r="M36" s="42"/>
+      <c r="N36" s="42"/>
+      <c r="O36" s="42"/>
+      <c r="P36" s="42"/>
+      <c r="Q36" s="43"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="44"/>
+      <c r="T36" s="44"/>
+      <c r="U36" s="82"/>
+      <c r="V36" s="82"/>
+      <c r="W36" s="82"/>
+      <c r="X36" s="82"/>
+      <c r="Y36" s="82"/>
+    </row>
+    <row r="37" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="53"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="48"/>
+      <c r="M37" s="48"/>
+      <c r="N37" s="48"/>
+      <c r="O37" s="48"/>
+      <c r="P37" s="48"/>
+      <c r="Q37" s="64"/>
+      <c r="R37" s="72"/>
+      <c r="S37" s="44"/>
+      <c r="T37" s="44"/>
+      <c r="U37" s="82"/>
+      <c r="V37" s="82"/>
+      <c r="W37" s="82"/>
+      <c r="X37" s="82"/>
+      <c r="Y37" s="82"/>
+    </row>
+    <row r="38" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="53"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="19"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="20"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="44"/>
+      <c r="T38" s="44"/>
+      <c r="U38" s="82"/>
+      <c r="V38" s="82"/>
+      <c r="W38" s="82"/>
+      <c r="X38" s="82"/>
+      <c r="Y38" s="82"/>
+    </row>
+    <row r="39" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="53"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="44"/>
+      <c r="T39" s="44"/>
+      <c r="U39" s="82"/>
+      <c r="V39" s="82"/>
+      <c r="W39" s="82"/>
+      <c r="X39" s="82"/>
+      <c r="Y39" s="82"/>
+    </row>
+    <row r="40" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="53"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="72"/>
+      <c r="S40" s="44"/>
+      <c r="T40" s="44"/>
+      <c r="U40" s="82"/>
+      <c r="V40" s="82"/>
+      <c r="W40" s="82"/>
+      <c r="X40" s="82"/>
+      <c r="Y40" s="82"/>
+    </row>
+    <row r="41" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="54"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="40"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="40"/>
+      <c r="M41" s="40"/>
+      <c r="N41" s="40"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="65"/>
+      <c r="R41" s="73"/>
+      <c r="S41" s="74"/>
+      <c r="T41" s="74"/>
+      <c r="U41" s="75"/>
+      <c r="V41" s="82"/>
+      <c r="W41" s="82"/>
+      <c r="X41" s="82"/>
+      <c r="Y41" s="82"/>
+    </row>
+    <row r="42" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="46"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="42"/>
+      <c r="I42" s="42"/>
+      <c r="J42" s="42"/>
+      <c r="K42" s="42"/>
+      <c r="L42" s="42"/>
+      <c r="M42" s="42"/>
+      <c r="N42" s="42"/>
+      <c r="O42" s="42"/>
+      <c r="P42" s="42"/>
+      <c r="Q42" s="43"/>
+      <c r="R42" s="86" t="s">
+        <v>54</v>
+      </c>
+      <c r="S42" s="87"/>
+      <c r="T42" s="87"/>
+      <c r="U42" s="87"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3"/>
+    </row>
+    <row r="43" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="3"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+      <c r="L43" s="44"/>
+      <c r="M43" s="44"/>
+      <c r="N43" s="44"/>
+      <c r="O43" s="44"/>
+      <c r="P43" s="44"/>
+      <c r="Q43" s="44"/>
+      <c r="R43" s="44"/>
+      <c r="S43" s="44"/>
+      <c r="T43" s="44"/>
+      <c r="U43" s="82"/>
+      <c r="V43" s="82"/>
+      <c r="W43" s="82"/>
+      <c r="X43" s="82"/>
+      <c r="Y43" s="82"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="R34:U34"/>
+    <mergeCell ref="R42:U42"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="O34:Q34"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="83" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{595EDB8E-3648-4F46-B81D-2258A72BA680}">
+  <dimension ref="B1:AA45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
+    <col min="3" max="5" width="5.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.140625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.140625" style="2" customWidth="1"/>
+    <col min="20" max="21" width="5.7109375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="29" width="5.7109375" style="2" customWidth="1"/>
+    <col min="30" max="16384" width="8.7109375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="3"/>
+    </row>
+    <row r="2" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6">
+        <f>[1]DSSR!B4</f>
+        <v>1300</v>
+      </c>
+      <c r="D3" s="6">
+        <f>[1]DSSR!C4</f>
+        <v>1534</v>
+      </c>
+      <c r="E3" s="6">
+        <f>[1]DSSR!D4</f>
+        <v>1728</v>
+      </c>
+      <c r="F3" s="6">
+        <f>[1]DSSR!E4</f>
+        <v>1728</v>
+      </c>
+      <c r="G3" s="6">
+        <f>[1]DSSR!F4</f>
+        <v>1452</v>
+      </c>
+      <c r="H3" s="6">
+        <f>[1]DSSR!G4</f>
+        <v>1240</v>
+      </c>
+      <c r="I3" s="6">
+        <f>[1]DSSR!H4</f>
+        <v>1520</v>
+      </c>
+      <c r="J3" s="6">
+        <f>[1]DSSR!I4</f>
+        <v>978</v>
+      </c>
+      <c r="K3" s="6">
+        <f>[1]DSSR!J4</f>
+        <v>945</v>
+      </c>
+      <c r="L3" s="6">
+        <f>[1]DSSR!K4</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="6">
+        <f>[1]DSSR!L4</f>
+        <v>1127</v>
+      </c>
+      <c r="N3" s="6">
+        <f>[1]DSSR!M4</f>
+        <v>773</v>
+      </c>
+      <c r="O3" s="6">
+        <f>[1]DSSR!N4</f>
+        <v>1038</v>
+      </c>
+      <c r="P3" s="6">
+        <f>[1]DSSR!O4</f>
+        <v>773</v>
+      </c>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6">
+        <f>[1]DSSR!P4</f>
+        <v>1038</v>
+      </c>
+      <c r="U3" s="6">
+        <f>[1]DSSR!Q4</f>
+        <v>773</v>
+      </c>
+      <c r="V3" s="6">
+        <f>[1]DSSR!R4</f>
+        <v>1038</v>
+      </c>
+      <c r="W3" s="6">
+        <f>[1]DSSR!S4</f>
+        <v>792</v>
+      </c>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6">
+        <f>[1]DSSR!T4</f>
+        <v>948</v>
+      </c>
+    </row>
+    <row r="4" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6">
+        <f>[1]DSSR!B5</f>
+        <v>120</v>
+      </c>
+      <c r="D4" s="6">
+        <f>[1]DSSR!C5</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="6">
+        <f>[1]DSSR!D5</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <f>[1]DSSR!E5</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="6">
+        <f>[1]DSSR!F5</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
+        <f>[1]DSSR!G5</f>
+        <v>120</v>
+      </c>
+      <c r="I4" s="6">
+        <f>[1]DSSR!H5</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <f>[1]DSSR!I5</f>
+        <v>120</v>
+      </c>
+      <c r="K4" s="6">
+        <f>[1]DSSR!J5</f>
+        <v>120</v>
+      </c>
+      <c r="L4" s="6">
+        <f>[1]DSSR!K5</f>
+        <v>111</v>
+      </c>
+      <c r="M4" s="6">
+        <f>[1]DSSR!L5</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="6">
+        <f>[1]DSSR!M5</f>
+        <v>120</v>
+      </c>
+      <c r="O4" s="6">
+        <f>[1]DSSR!N5</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="6">
+        <f>[1]DSSR!O5</f>
+        <v>120</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6">
+        <f>[1]DSSR!P5</f>
+        <v>0</v>
+      </c>
+      <c r="U4" s="6">
+        <f>[1]DSSR!Q5</f>
+        <v>120</v>
+      </c>
+      <c r="V4" s="6">
+        <f>[1]DSSR!R5</f>
+        <v>0</v>
+      </c>
+      <c r="W4" s="6">
+        <f>[1]DSSR!S5</f>
+        <v>120</v>
+      </c>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6">
+        <f>[1]DSSR!T5</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="7">
+        <v>84</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7">
+        <v>84</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7">
+        <v>84</v>
+      </c>
+      <c r="K5" s="7">
+        <v>84</v>
+      </c>
+      <c r="L5" s="7">
+        <v>84</v>
+      </c>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7">
+        <v>84</v>
+      </c>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7">
+        <v>84</v>
+      </c>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7">
+        <v>84</v>
+      </c>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7">
+        <v>84</v>
+      </c>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="L6" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="R7" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="S7" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="T7" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="V7" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y7" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="12"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14">
+        <v>1</v>
+      </c>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14">
+        <v>12</v>
+      </c>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14">
+        <v>1</v>
+      </c>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="14"/>
+      <c r="X8" s="59"/>
+      <c r="Y8" s="15"/>
+    </row>
+    <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="60"/>
+      <c r="Y9" s="20"/>
+    </row>
+    <row r="10" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="60"/>
+      <c r="Y10" s="20"/>
+    </row>
+    <row r="11" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="16"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="60"/>
+      <c r="Y11" s="20"/>
+    </row>
+    <row r="12" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="60"/>
+      <c r="Y12" s="20"/>
+    </row>
+    <row r="13" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="60"/>
+      <c r="Y13" s="20"/>
+    </row>
+    <row r="14" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="16"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="19"/>
+      <c r="V14" s="19"/>
+      <c r="W14" s="19"/>
+      <c r="X14" s="60"/>
+      <c r="Y14" s="20"/>
+    </row>
+    <row r="15" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23">
+        <v>1</v>
+      </c>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23">
+        <v>0</v>
+      </c>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="T15" s="23">
+        <v>1</v>
+      </c>
+      <c r="U15" s="23"/>
+      <c r="V15" s="23"/>
+      <c r="W15" s="23"/>
+      <c r="X15" s="61"/>
+      <c r="Y15" s="24"/>
+    </row>
+    <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="57"/>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28">
+        <v>12</v>
+      </c>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
+      <c r="U16" s="28"/>
+      <c r="V16" s="28"/>
+      <c r="W16" s="56"/>
+      <c r="X16" s="62"/>
+      <c r="Y16" s="29"/>
+    </row>
+    <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="32"/>
+    </row>
+    <row r="18" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="34">
+        <f>[1]DSSR!B24</f>
+        <v>544</v>
+      </c>
+      <c r="D18" s="34">
+        <f>[1]DSSR!C24</f>
+        <v>1127</v>
+      </c>
+      <c r="E18" s="34">
+        <f>[1]DSSR!D24</f>
+        <v>853</v>
+      </c>
+      <c r="F18" s="34">
+        <f>[1]DSSR!E24</f>
+        <v>563</v>
+      </c>
+      <c r="G18" s="34">
+        <f>[1]DSSR!F24</f>
+        <v>575</v>
+      </c>
+      <c r="H18" s="34">
+        <f>[1]DSSR!G24</f>
+        <v>1175</v>
+      </c>
+      <c r="I18" s="34">
+        <f>[1]DSSR!H24</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="34">
+        <f>[1]DSSR!I24</f>
+        <v>791</v>
+      </c>
+      <c r="K18" s="34">
+        <f>[1]DSSR!J24</f>
+        <v>1102</v>
+      </c>
+      <c r="L18" s="34">
+        <f>[1]DSSR!K24</f>
+        <v>520</v>
+      </c>
+      <c r="M18" s="34">
+        <f>[1]DSSR!L24</f>
+        <v>1142</v>
+      </c>
+      <c r="N18" s="34">
+        <f>[1]DSSR!M24</f>
+        <v>205</v>
+      </c>
+      <c r="O18" s="34">
+        <f>[1]DSSR!N24</f>
+        <v>205</v>
+      </c>
+      <c r="P18" s="34">
+        <f>[1]DSSR!O24</f>
+        <v>205</v>
+      </c>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="34"/>
+      <c r="S18" s="34"/>
+      <c r="T18" s="34">
+        <f>[1]DSSR!P24</f>
+        <v>500</v>
+      </c>
+      <c r="U18" s="34">
+        <f>[1]DSSR!Q24</f>
+        <v>650</v>
+      </c>
+      <c r="V18" s="34">
+        <f>[1]DSSR!R24</f>
+        <v>650</v>
+      </c>
+      <c r="W18" s="34">
+        <f>[1]DSSR!S24</f>
+        <v>500</v>
+      </c>
+      <c r="X18" s="34"/>
+      <c r="Y18" s="35">
+        <f>[1]DSSR!T24</f>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="34">
+        <f>[1]DSSR!B25</f>
+        <v>111</v>
+      </c>
+      <c r="D19" s="34">
+        <f>[1]DSSR!C25</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="34">
+        <f>[1]DSSR!D25</f>
+        <v>120</v>
+      </c>
+      <c r="F19" s="34">
+        <f>[1]DSSR!E25</f>
+        <v>111</v>
+      </c>
+      <c r="G19" s="34">
+        <f>[1]DSSR!F25</f>
+        <v>111</v>
+      </c>
+      <c r="H19" s="34">
+        <f>[1]DSSR!G25</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="34">
+        <f>[1]DSSR!H25</f>
+        <v>111</v>
+      </c>
+      <c r="J19" s="34">
+        <f>[1]DSSR!I25</f>
+        <v>120</v>
+      </c>
+      <c r="K19" s="34">
+        <f>[1]DSSR!J25</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="34">
+        <f>[1]DSSR!K25</f>
+        <v>111</v>
+      </c>
+      <c r="M19" s="34">
+        <f>[1]DSSR!L25</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="34">
+        <f>[1]DSSR!M25</f>
+        <v>78</v>
+      </c>
+      <c r="O19" s="34">
+        <f>[1]DSSR!N25</f>
+        <v>78</v>
+      </c>
+      <c r="P19" s="34">
+        <f>[1]DSSR!O25</f>
+        <v>78</v>
+      </c>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+      <c r="S19" s="34"/>
+      <c r="T19" s="34">
+        <f>[1]DSSR!P25</f>
+        <v>120</v>
+      </c>
+      <c r="U19" s="34">
+        <f>[1]DSSR!Q25</f>
+        <v>0</v>
+      </c>
+      <c r="V19" s="34">
+        <f>[1]DSSR!R25</f>
+        <v>0</v>
+      </c>
+      <c r="W19" s="34">
+        <f>[1]DSSR!S25</f>
+        <v>120</v>
+      </c>
+      <c r="X19" s="34"/>
+      <c r="Y19" s="35">
+        <f>[1]DSSR!T25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="34">
+        <v>84</v>
+      </c>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34">
+        <v>84</v>
+      </c>
+      <c r="F20" s="34">
+        <v>84</v>
+      </c>
+      <c r="G20" s="34">
+        <v>84</v>
+      </c>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34">
+        <v>84</v>
+      </c>
+      <c r="J20" s="34">
+        <v>84</v>
+      </c>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34">
+        <v>84</v>
+      </c>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34">
+        <v>42</v>
+      </c>
+      <c r="O20" s="34">
+        <v>42</v>
+      </c>
+      <c r="P20" s="34">
+        <v>42</v>
+      </c>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="34"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="34">
+        <v>84</v>
+      </c>
+      <c r="U20" s="34"/>
+      <c r="V20" s="34"/>
+      <c r="W20" s="34">
+        <v>84</v>
+      </c>
+      <c r="X20" s="34"/>
+      <c r="Y20" s="35"/>
+    </row>
+    <row r="21" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="F21" s="36">
+        <f>4.5/2</f>
+        <v>2.25</v>
+      </c>
+      <c r="G21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="J21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="O21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="P21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+      <c r="S21" s="34"/>
+      <c r="T21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="U21" s="34"/>
+      <c r="V21" s="34"/>
+      <c r="W21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="X21" s="34"/>
+      <c r="Y21" s="35"/>
+    </row>
+    <row r="22" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="33"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="34"/>
+      <c r="S22" s="34"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="34"/>
+      <c r="V22" s="34"/>
+      <c r="W22" s="34"/>
+      <c r="X22" s="34"/>
+      <c r="Y22" s="35"/>
+    </row>
+    <row r="23" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="37"/>
+      <c r="C23" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O23" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P23" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q23" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="R23" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="V23" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="11"/>
+    </row>
+    <row r="24" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14">
+        <v>1</v>
+      </c>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14">
+        <v>11</v>
+      </c>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14">
+        <v>329</v>
+      </c>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="14"/>
+      <c r="Y24" s="15"/>
+    </row>
+    <row r="25" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="17"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="19"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="19"/>
+      <c r="X25" s="60"/>
+      <c r="Y25" s="20"/>
+    </row>
+    <row r="26" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="16"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="19"/>
+      <c r="U26" s="19"/>
+      <c r="V26" s="19"/>
+      <c r="W26" s="19"/>
+      <c r="X26" s="60"/>
+      <c r="Y26" s="20"/>
+    </row>
+    <row r="27" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="16"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="19"/>
+      <c r="U27" s="19"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="19"/>
+      <c r="X27" s="60"/>
+      <c r="Y27" s="20"/>
+    </row>
+    <row r="28" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="16"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="19"/>
+      <c r="X28" s="60"/>
+      <c r="Y28" s="20"/>
+    </row>
+    <row r="29" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="16"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="19"/>
+      <c r="W29" s="19"/>
+      <c r="X29" s="60"/>
+      <c r="Y29" s="20"/>
+    </row>
+    <row r="30" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="16"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="19"/>
+      <c r="U30" s="19"/>
+      <c r="V30" s="19"/>
+      <c r="W30" s="19"/>
+      <c r="X30" s="60"/>
+      <c r="Y30" s="20"/>
+    </row>
+    <row r="31" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23">
+        <v>1</v>
+      </c>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23">
+        <v>0</v>
+      </c>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
+      <c r="M31" s="23">
+        <v>5</v>
+      </c>
+      <c r="N31" s="23"/>
+      <c r="O31" s="23"/>
+      <c r="P31" s="23"/>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="23"/>
+      <c r="S31" s="23"/>
+      <c r="T31" s="23"/>
+      <c r="U31" s="23"/>
+      <c r="V31" s="23"/>
+      <c r="W31" s="23"/>
+      <c r="X31" s="61"/>
+      <c r="Y31" s="24"/>
+    </row>
+    <row r="32" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="26"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28">
+        <v>11</v>
+      </c>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28">
+        <v>324</v>
+      </c>
+      <c r="N32" s="28"/>
+      <c r="O32" s="23"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="28"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="63"/>
+      <c r="Y32" s="29"/>
+    </row>
+    <row r="33" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="30"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="68"/>
+      <c r="S33" s="68"/>
+      <c r="T33" s="68"/>
+      <c r="U33" s="68"/>
+      <c r="V33" s="31"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="31"/>
+      <c r="Y33" s="31"/>
+    </row>
+    <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="88" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="90"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="92" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="90"/>
+      <c r="H34" s="91"/>
+      <c r="I34" s="92" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34" s="90"/>
+      <c r="K34" s="91"/>
+      <c r="L34" s="92" t="s">
+        <v>46</v>
+      </c>
+      <c r="M34" s="90"/>
+      <c r="N34" s="91"/>
+      <c r="O34" s="93" t="s">
+        <v>47</v>
+      </c>
+      <c r="P34" s="93"/>
+      <c r="Q34" s="93"/>
+      <c r="R34" s="83" t="s">
+        <v>48</v>
+      </c>
+      <c r="S34" s="84"/>
+      <c r="T34" s="84"/>
+      <c r="U34" s="85"/>
+      <c r="V34" s="66"/>
+      <c r="W34" s="3"/>
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
+    </row>
+    <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="89"/>
+      <c r="C35" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="G35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="J35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="K35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="L35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="M35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="N35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="O35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="P35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q35" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="R35" s="69"/>
+      <c r="S35" s="70"/>
+      <c r="T35" s="70"/>
+      <c r="U35" s="71"/>
+      <c r="V35" s="82"/>
+      <c r="W35" s="82"/>
+      <c r="X35" s="82"/>
+      <c r="Y35" s="82"/>
+    </row>
+    <row r="36" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="46"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42">
+        <v>332</v>
+      </c>
+      <c r="G36" s="42">
+        <v>3</v>
+      </c>
+      <c r="H36" s="42">
+        <v>1</v>
+      </c>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="42"/>
+      <c r="L36" s="42"/>
+      <c r="M36" s="42"/>
+      <c r="N36" s="42"/>
+      <c r="O36" s="42">
+        <v>9</v>
+      </c>
+      <c r="P36" s="42">
+        <v>3</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>21</v>
+      </c>
+      <c r="R36" s="72"/>
+      <c r="S36" s="44"/>
+      <c r="T36" s="44"/>
+      <c r="U36" s="82"/>
+      <c r="V36" s="82"/>
+      <c r="W36" s="82"/>
+      <c r="X36" s="82"/>
+      <c r="Y36" s="82"/>
+    </row>
+    <row r="37" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="53"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="48"/>
+      <c r="M37" s="48"/>
+      <c r="N37" s="48"/>
+      <c r="O37" s="48"/>
+      <c r="P37" s="48"/>
+      <c r="Q37" s="64"/>
+      <c r="R37" s="72"/>
+      <c r="S37" s="44"/>
+      <c r="T37" s="44"/>
+      <c r="U37" s="82"/>
+      <c r="V37" s="82"/>
+      <c r="W37" s="82"/>
+      <c r="X37" s="82"/>
+      <c r="Y37" s="82"/>
+    </row>
+    <row r="38" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="53"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="19"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="20"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="44"/>
+      <c r="T38" s="44"/>
+      <c r="U38" s="82"/>
+      <c r="V38" s="82"/>
+      <c r="W38" s="82"/>
+      <c r="X38" s="82"/>
+      <c r="Y38" s="82"/>
+    </row>
+    <row r="39" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="53"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="44"/>
+      <c r="T39" s="44"/>
+      <c r="U39" s="82"/>
+      <c r="V39" s="82"/>
+      <c r="W39" s="82"/>
+      <c r="X39" s="82"/>
+      <c r="Y39" s="82"/>
+    </row>
+    <row r="40" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="53"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="72"/>
+      <c r="S40" s="44"/>
+      <c r="T40" s="44"/>
+      <c r="U40" s="82"/>
+      <c r="V40" s="82"/>
+      <c r="W40" s="82"/>
+      <c r="X40" s="82"/>
+      <c r="Y40" s="82"/>
+    </row>
+    <row r="41" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="54"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="40"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="40"/>
+      <c r="M41" s="40"/>
+      <c r="N41" s="40"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="65"/>
+      <c r="R41" s="73"/>
+      <c r="S41" s="74"/>
+      <c r="T41" s="74"/>
+      <c r="U41" s="75"/>
+      <c r="V41" s="82"/>
+      <c r="W41" s="82"/>
+      <c r="X41" s="82"/>
+      <c r="Y41" s="82"/>
+    </row>
+    <row r="42" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="46"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42">
+        <v>332</v>
+      </c>
+      <c r="G42" s="42">
+        <v>3</v>
+      </c>
+      <c r="H42" s="42">
+        <v>1</v>
+      </c>
+      <c r="I42" s="42"/>
+      <c r="J42" s="42"/>
+      <c r="K42" s="42"/>
+      <c r="L42" s="42"/>
+      <c r="M42" s="42"/>
+      <c r="N42" s="42"/>
+      <c r="O42" s="42">
+        <v>9</v>
+      </c>
+      <c r="P42" s="42">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>21</v>
+      </c>
+      <c r="R42" s="86" t="s">
+        <v>54</v>
+      </c>
+      <c r="S42" s="87"/>
+      <c r="T42" s="87"/>
+      <c r="U42" s="87"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3"/>
+    </row>
+    <row r="43" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="3"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+      <c r="L43" s="44"/>
+      <c r="M43" s="44"/>
+      <c r="N43" s="44"/>
+      <c r="O43" s="44"/>
+      <c r="P43" s="44"/>
+      <c r="Q43" s="44"/>
+      <c r="R43" s="44"/>
+      <c r="S43" s="44"/>
+      <c r="T43" s="44"/>
+      <c r="U43" s="82"/>
+      <c r="V43" s="82"/>
+      <c r="W43" s="82"/>
+      <c r="X43" s="82"/>
+      <c r="Y43" s="82"/>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B44" s="76" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" s="94">
+        <f>12+11+324</f>
+        <v>347</v>
+      </c>
+      <c r="D44" s="94"/>
+      <c r="E44" s="94"/>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B45" s="76" t="s">
+        <v>69</v>
+      </c>
+      <c r="C45" s="94"/>
+      <c r="D45" s="94"/>
+      <c r="E45" s="94"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="R34:U34"/>
+    <mergeCell ref="R42:U42"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="O34:Q34"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="83" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -16595,47 +19899,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="87" t="s">
+      <c r="B34" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="89" t="s">
+      <c r="C34" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="89"/>
-      <c r="E34" s="90"/>
-      <c r="F34" s="91" t="s">
+      <c r="D34" s="90"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="89"/>
-      <c r="H34" s="90"/>
-      <c r="I34" s="91" t="s">
+      <c r="G34" s="90"/>
+      <c r="H34" s="91"/>
+      <c r="I34" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="89"/>
-      <c r="K34" s="90"/>
-      <c r="L34" s="91" t="s">
+      <c r="J34" s="90"/>
+      <c r="K34" s="91"/>
+      <c r="L34" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="89"/>
-      <c r="N34" s="90"/>
-      <c r="O34" s="92" t="s">
+      <c r="M34" s="90"/>
+      <c r="N34" s="91"/>
+      <c r="O34" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="92"/>
-      <c r="Q34" s="92"/>
-      <c r="R34" s="82" t="s">
+      <c r="P34" s="93"/>
+      <c r="Q34" s="93"/>
+      <c r="R34" s="83" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="83"/>
-      <c r="T34" s="83"/>
-      <c r="U34" s="84"/>
+      <c r="S34" s="84"/>
+      <c r="T34" s="84"/>
+      <c r="U34" s="85"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="88"/>
+      <c r="B35" s="89"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -16867,12 +20171,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="85" t="s">
+      <c r="R42" s="86" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="86"/>
-      <c r="T42" s="86"/>
-      <c r="U42" s="86"/>
+      <c r="S42" s="87"/>
+      <c r="T42" s="87"/>
+      <c r="U42" s="87"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -16918,6 +20222,3470 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="83" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14B56F3B-4942-4C08-A83E-9F505115220B}">
+  <dimension ref="B1:AA45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.140625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.140625" style="2" customWidth="1"/>
+    <col min="20" max="21" width="5.7109375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="29" width="5.7109375" style="2" customWidth="1"/>
+    <col min="30" max="16384" width="8.7109375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="3"/>
+    </row>
+    <row r="2" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6">
+        <f>[1]DSSR!B4</f>
+        <v>1300</v>
+      </c>
+      <c r="D3" s="6">
+        <f>[1]DSSR!C4</f>
+        <v>1534</v>
+      </c>
+      <c r="E3" s="6">
+        <f>[1]DSSR!D4</f>
+        <v>1728</v>
+      </c>
+      <c r="F3" s="6">
+        <f>[1]DSSR!E4</f>
+        <v>1728</v>
+      </c>
+      <c r="G3" s="6">
+        <f>[1]DSSR!F4</f>
+        <v>1452</v>
+      </c>
+      <c r="H3" s="6">
+        <f>[1]DSSR!G4</f>
+        <v>1240</v>
+      </c>
+      <c r="I3" s="6">
+        <f>[1]DSSR!H4</f>
+        <v>1520</v>
+      </c>
+      <c r="J3" s="6">
+        <f>[1]DSSR!I4</f>
+        <v>978</v>
+      </c>
+      <c r="K3" s="6">
+        <f>[1]DSSR!J4</f>
+        <v>945</v>
+      </c>
+      <c r="L3" s="6">
+        <f>[1]DSSR!K4</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="6">
+        <f>[1]DSSR!L4</f>
+        <v>1127</v>
+      </c>
+      <c r="N3" s="6">
+        <f>[1]DSSR!M4</f>
+        <v>773</v>
+      </c>
+      <c r="O3" s="6">
+        <f>[1]DSSR!N4</f>
+        <v>1038</v>
+      </c>
+      <c r="P3" s="6">
+        <f>[1]DSSR!O4</f>
+        <v>773</v>
+      </c>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6">
+        <f>[1]DSSR!P4</f>
+        <v>1038</v>
+      </c>
+      <c r="U3" s="6">
+        <f>[1]DSSR!Q4</f>
+        <v>773</v>
+      </c>
+      <c r="V3" s="6">
+        <f>[1]DSSR!R4</f>
+        <v>1038</v>
+      </c>
+      <c r="W3" s="6">
+        <f>[1]DSSR!S4</f>
+        <v>792</v>
+      </c>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6">
+        <f>[1]DSSR!T4</f>
+        <v>948</v>
+      </c>
+    </row>
+    <row r="4" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6">
+        <f>[1]DSSR!B5</f>
+        <v>120</v>
+      </c>
+      <c r="D4" s="6">
+        <f>[1]DSSR!C5</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="6">
+        <f>[1]DSSR!D5</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <f>[1]DSSR!E5</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="6">
+        <f>[1]DSSR!F5</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
+        <f>[1]DSSR!G5</f>
+        <v>120</v>
+      </c>
+      <c r="I4" s="6">
+        <f>[1]DSSR!H5</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <f>[1]DSSR!I5</f>
+        <v>120</v>
+      </c>
+      <c r="K4" s="6">
+        <f>[1]DSSR!J5</f>
+        <v>120</v>
+      </c>
+      <c r="L4" s="6">
+        <f>[1]DSSR!K5</f>
+        <v>111</v>
+      </c>
+      <c r="M4" s="6">
+        <f>[1]DSSR!L5</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="6">
+        <f>[1]DSSR!M5</f>
+        <v>120</v>
+      </c>
+      <c r="O4" s="6">
+        <f>[1]DSSR!N5</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="6">
+        <f>[1]DSSR!O5</f>
+        <v>120</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6">
+        <f>[1]DSSR!P5</f>
+        <v>0</v>
+      </c>
+      <c r="U4" s="6">
+        <f>[1]DSSR!Q5</f>
+        <v>120</v>
+      </c>
+      <c r="V4" s="6">
+        <f>[1]DSSR!R5</f>
+        <v>0</v>
+      </c>
+      <c r="W4" s="6">
+        <f>[1]DSSR!S5</f>
+        <v>120</v>
+      </c>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6">
+        <f>[1]DSSR!T5</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="7">
+        <v>84</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7">
+        <v>84</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7">
+        <v>84</v>
+      </c>
+      <c r="K5" s="7">
+        <v>84</v>
+      </c>
+      <c r="L5" s="7">
+        <v>84</v>
+      </c>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7">
+        <v>84</v>
+      </c>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7">
+        <v>84</v>
+      </c>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7">
+        <v>84</v>
+      </c>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7">
+        <v>84</v>
+      </c>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="L6" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="R7" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="S7" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="T7" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="V7" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y7" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="12"/>
+      <c r="C8" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14">
+        <v>1</v>
+      </c>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14">
+        <v>15</v>
+      </c>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14">
+        <v>1</v>
+      </c>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="14">
+        <v>3</v>
+      </c>
+      <c r="X8" s="59"/>
+      <c r="Y8" s="15"/>
+    </row>
+    <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="60"/>
+      <c r="Y9" s="20"/>
+    </row>
+    <row r="10" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="60"/>
+      <c r="Y10" s="20"/>
+    </row>
+    <row r="11" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="16"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="60"/>
+      <c r="Y11" s="20"/>
+    </row>
+    <row r="12" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="60"/>
+      <c r="Y12" s="20"/>
+    </row>
+    <row r="13" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="60"/>
+      <c r="Y13" s="20"/>
+    </row>
+    <row r="14" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="16"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="19"/>
+      <c r="V14" s="19"/>
+      <c r="W14" s="19"/>
+      <c r="X14" s="60"/>
+      <c r="Y14" s="20"/>
+    </row>
+    <row r="15" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23">
+        <v>1</v>
+      </c>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23">
+        <v>3</v>
+      </c>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="T15" s="23">
+        <v>1</v>
+      </c>
+      <c r="U15" s="23"/>
+      <c r="V15" s="23"/>
+      <c r="W15" s="23">
+        <v>3</v>
+      </c>
+      <c r="X15" s="61"/>
+      <c r="Y15" s="24"/>
+    </row>
+    <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+      <c r="D16" s="58"/>
+      <c r="E16" s="27">
+        <v>0</v>
+      </c>
+      <c r="F16" s="27"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28">
+        <v>12</v>
+      </c>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
+      <c r="U16" s="28"/>
+      <c r="V16" s="28"/>
+      <c r="W16" s="56">
+        <v>0</v>
+      </c>
+      <c r="X16" s="62"/>
+      <c r="Y16" s="29"/>
+    </row>
+    <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="32"/>
+    </row>
+    <row r="18" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="34">
+        <f>[1]DSSR!B24</f>
+        <v>544</v>
+      </c>
+      <c r="D18" s="34">
+        <f>[1]DSSR!C24</f>
+        <v>1127</v>
+      </c>
+      <c r="E18" s="34">
+        <f>[1]DSSR!D24</f>
+        <v>853</v>
+      </c>
+      <c r="F18" s="34">
+        <f>[1]DSSR!E24</f>
+        <v>563</v>
+      </c>
+      <c r="G18" s="34">
+        <f>[1]DSSR!F24</f>
+        <v>575</v>
+      </c>
+      <c r="H18" s="34">
+        <f>[1]DSSR!G24</f>
+        <v>1175</v>
+      </c>
+      <c r="I18" s="34">
+        <f>[1]DSSR!H24</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="34">
+        <f>[1]DSSR!I24</f>
+        <v>791</v>
+      </c>
+      <c r="K18" s="34">
+        <f>[1]DSSR!J24</f>
+        <v>1102</v>
+      </c>
+      <c r="L18" s="34">
+        <f>[1]DSSR!K24</f>
+        <v>520</v>
+      </c>
+      <c r="M18" s="34">
+        <f>[1]DSSR!L24</f>
+        <v>1142</v>
+      </c>
+      <c r="N18" s="34">
+        <f>[1]DSSR!M24</f>
+        <v>205</v>
+      </c>
+      <c r="O18" s="34">
+        <f>[1]DSSR!N24</f>
+        <v>205</v>
+      </c>
+      <c r="P18" s="34">
+        <f>[1]DSSR!O24</f>
+        <v>205</v>
+      </c>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="34"/>
+      <c r="S18" s="34"/>
+      <c r="T18" s="34">
+        <f>[1]DSSR!P24</f>
+        <v>500</v>
+      </c>
+      <c r="U18" s="34">
+        <f>[1]DSSR!Q24</f>
+        <v>650</v>
+      </c>
+      <c r="V18" s="34">
+        <f>[1]DSSR!R24</f>
+        <v>650</v>
+      </c>
+      <c r="W18" s="34">
+        <f>[1]DSSR!S24</f>
+        <v>500</v>
+      </c>
+      <c r="X18" s="34"/>
+      <c r="Y18" s="35">
+        <f>[1]DSSR!T24</f>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="34">
+        <f>[1]DSSR!B25</f>
+        <v>111</v>
+      </c>
+      <c r="D19" s="34">
+        <f>[1]DSSR!C25</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="34">
+        <f>[1]DSSR!D25</f>
+        <v>120</v>
+      </c>
+      <c r="F19" s="34">
+        <f>[1]DSSR!E25</f>
+        <v>111</v>
+      </c>
+      <c r="G19" s="34">
+        <f>[1]DSSR!F25</f>
+        <v>111</v>
+      </c>
+      <c r="H19" s="34">
+        <f>[1]DSSR!G25</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="34">
+        <f>[1]DSSR!H25</f>
+        <v>111</v>
+      </c>
+      <c r="J19" s="34">
+        <f>[1]DSSR!I25</f>
+        <v>120</v>
+      </c>
+      <c r="K19" s="34">
+        <f>[1]DSSR!J25</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="34">
+        <f>[1]DSSR!K25</f>
+        <v>111</v>
+      </c>
+      <c r="M19" s="34">
+        <f>[1]DSSR!L25</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="34">
+        <f>[1]DSSR!M25</f>
+        <v>78</v>
+      </c>
+      <c r="O19" s="34">
+        <f>[1]DSSR!N25</f>
+        <v>78</v>
+      </c>
+      <c r="P19" s="34">
+        <f>[1]DSSR!O25</f>
+        <v>78</v>
+      </c>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+      <c r="S19" s="34"/>
+      <c r="T19" s="34">
+        <f>[1]DSSR!P25</f>
+        <v>120</v>
+      </c>
+      <c r="U19" s="34">
+        <f>[1]DSSR!Q25</f>
+        <v>0</v>
+      </c>
+      <c r="V19" s="34">
+        <f>[1]DSSR!R25</f>
+        <v>0</v>
+      </c>
+      <c r="W19" s="34">
+        <f>[1]DSSR!S25</f>
+        <v>120</v>
+      </c>
+      <c r="X19" s="34"/>
+      <c r="Y19" s="35">
+        <f>[1]DSSR!T25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="34">
+        <v>84</v>
+      </c>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34">
+        <v>84</v>
+      </c>
+      <c r="F20" s="34">
+        <v>84</v>
+      </c>
+      <c r="G20" s="34">
+        <v>84</v>
+      </c>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34">
+        <v>84</v>
+      </c>
+      <c r="J20" s="34">
+        <v>84</v>
+      </c>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34">
+        <v>84</v>
+      </c>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34">
+        <v>42</v>
+      </c>
+      <c r="O20" s="34">
+        <v>42</v>
+      </c>
+      <c r="P20" s="34">
+        <v>42</v>
+      </c>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="34"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="34">
+        <v>84</v>
+      </c>
+      <c r="U20" s="34"/>
+      <c r="V20" s="34"/>
+      <c r="W20" s="34">
+        <v>84</v>
+      </c>
+      <c r="X20" s="34"/>
+      <c r="Y20" s="35"/>
+    </row>
+    <row r="21" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="F21" s="36">
+        <f>4.5/2</f>
+        <v>2.25</v>
+      </c>
+      <c r="G21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="J21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="O21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="P21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+      <c r="S21" s="34"/>
+      <c r="T21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="U21" s="34"/>
+      <c r="V21" s="34"/>
+      <c r="W21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="X21" s="34"/>
+      <c r="Y21" s="35"/>
+    </row>
+    <row r="22" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="33"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="34"/>
+      <c r="S22" s="34"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="34"/>
+      <c r="V22" s="34"/>
+      <c r="W22" s="34"/>
+      <c r="X22" s="34"/>
+      <c r="Y22" s="35"/>
+    </row>
+    <row r="23" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="37"/>
+      <c r="C23" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O23" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P23" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q23" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="R23" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="V23" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="11"/>
+    </row>
+    <row r="24" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="79" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14">
+        <v>108</v>
+      </c>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14">
+        <v>395</v>
+      </c>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="14"/>
+      <c r="Y24" s="15"/>
+    </row>
+    <row r="25" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="17"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="19"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="19"/>
+      <c r="X25" s="60"/>
+      <c r="Y25" s="20"/>
+    </row>
+    <row r="26" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="16"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="19"/>
+      <c r="U26" s="19"/>
+      <c r="V26" s="19"/>
+      <c r="W26" s="19"/>
+      <c r="X26" s="60"/>
+      <c r="Y26" s="20"/>
+    </row>
+    <row r="27" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="16"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="19"/>
+      <c r="U27" s="19"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="19"/>
+      <c r="X27" s="60"/>
+      <c r="Y27" s="20"/>
+    </row>
+    <row r="28" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="16"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="19"/>
+      <c r="X28" s="60"/>
+      <c r="Y28" s="20"/>
+    </row>
+    <row r="29" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="16"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="19"/>
+      <c r="W29" s="19"/>
+      <c r="X29" s="60"/>
+      <c r="Y29" s="20"/>
+    </row>
+    <row r="30" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="16"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="19"/>
+      <c r="U30" s="19"/>
+      <c r="V30" s="19"/>
+      <c r="W30" s="19"/>
+      <c r="X30" s="60"/>
+      <c r="Y30" s="20"/>
+    </row>
+    <row r="31" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23">
+        <v>38</v>
+      </c>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="23">
+        <v>2</v>
+      </c>
+      <c r="L31" s="23"/>
+      <c r="M31" s="23">
+        <v>39</v>
+      </c>
+      <c r="N31" s="23"/>
+      <c r="O31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="23"/>
+      <c r="S31" s="23"/>
+      <c r="T31" s="23"/>
+      <c r="U31" s="23"/>
+      <c r="V31" s="23"/>
+      <c r="W31" s="23"/>
+      <c r="X31" s="61"/>
+      <c r="Y31" s="24"/>
+    </row>
+    <row r="32" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="26"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28">
+        <v>70</v>
+      </c>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28">
+        <v>356</v>
+      </c>
+      <c r="N32" s="28"/>
+      <c r="O32" s="23"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="28"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="63"/>
+      <c r="Y32" s="29"/>
+    </row>
+    <row r="33" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="30"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="68"/>
+      <c r="S33" s="68"/>
+      <c r="T33" s="68"/>
+      <c r="U33" s="68"/>
+      <c r="V33" s="31"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="31"/>
+      <c r="Y33" s="31"/>
+    </row>
+    <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="88" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="90"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="92" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="90"/>
+      <c r="H34" s="91"/>
+      <c r="I34" s="92" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34" s="90"/>
+      <c r="K34" s="91"/>
+      <c r="L34" s="92" t="s">
+        <v>46</v>
+      </c>
+      <c r="M34" s="90"/>
+      <c r="N34" s="91"/>
+      <c r="O34" s="93" t="s">
+        <v>47</v>
+      </c>
+      <c r="P34" s="93"/>
+      <c r="Q34" s="93"/>
+      <c r="R34" s="83" t="s">
+        <v>48</v>
+      </c>
+      <c r="S34" s="84"/>
+      <c r="T34" s="84"/>
+      <c r="U34" s="85"/>
+      <c r="V34" s="66"/>
+      <c r="W34" s="3"/>
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
+    </row>
+    <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="89"/>
+      <c r="C35" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="G35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="J35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="K35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="L35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="M35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="N35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="O35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="P35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q35" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="R35" s="69"/>
+      <c r="S35" s="70"/>
+      <c r="T35" s="70"/>
+      <c r="U35" s="71"/>
+      <c r="V35" s="82"/>
+      <c r="W35" s="82"/>
+      <c r="X35" s="82"/>
+      <c r="Y35" s="82"/>
+    </row>
+    <row r="36" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="46"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42">
+        <v>431</v>
+      </c>
+      <c r="G36" s="42">
+        <v>3</v>
+      </c>
+      <c r="H36" s="42">
+        <v>1</v>
+      </c>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="42"/>
+      <c r="L36" s="42"/>
+      <c r="M36" s="42"/>
+      <c r="N36" s="42"/>
+      <c r="O36" s="42">
+        <v>2</v>
+      </c>
+      <c r="P36" s="42">
+        <v>16</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>2</v>
+      </c>
+      <c r="R36" s="72"/>
+      <c r="S36" s="44"/>
+      <c r="T36" s="44"/>
+      <c r="U36" s="82"/>
+      <c r="V36" s="82"/>
+      <c r="W36" s="82"/>
+      <c r="X36" s="82"/>
+      <c r="Y36" s="82"/>
+    </row>
+    <row r="37" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="53"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="48"/>
+      <c r="M37" s="48"/>
+      <c r="N37" s="48"/>
+      <c r="O37" s="48"/>
+      <c r="P37" s="48"/>
+      <c r="Q37" s="64"/>
+      <c r="R37" s="72"/>
+      <c r="S37" s="44"/>
+      <c r="T37" s="44"/>
+      <c r="U37" s="82"/>
+      <c r="V37" s="82"/>
+      <c r="W37" s="82"/>
+      <c r="X37" s="82"/>
+      <c r="Y37" s="82"/>
+    </row>
+    <row r="38" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="53"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="19"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="20"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="44"/>
+      <c r="T38" s="44"/>
+      <c r="U38" s="82"/>
+      <c r="V38" s="82"/>
+      <c r="W38" s="82"/>
+      <c r="X38" s="82"/>
+      <c r="Y38" s="82"/>
+    </row>
+    <row r="39" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="53"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="44"/>
+      <c r="T39" s="44"/>
+      <c r="U39" s="82"/>
+      <c r="V39" s="82"/>
+      <c r="W39" s="82"/>
+      <c r="X39" s="82"/>
+      <c r="Y39" s="82"/>
+    </row>
+    <row r="40" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="53"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="72"/>
+      <c r="S40" s="44"/>
+      <c r="T40" s="44"/>
+      <c r="U40" s="82"/>
+      <c r="V40" s="82"/>
+      <c r="W40" s="82"/>
+      <c r="X40" s="82"/>
+      <c r="Y40" s="82"/>
+    </row>
+    <row r="41" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="54"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="40"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="40"/>
+      <c r="M41" s="40"/>
+      <c r="N41" s="40"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="65"/>
+      <c r="R41" s="73"/>
+      <c r="S41" s="74"/>
+      <c r="T41" s="74"/>
+      <c r="U41" s="75"/>
+      <c r="V41" s="82"/>
+      <c r="W41" s="82"/>
+      <c r="X41" s="82"/>
+      <c r="Y41" s="82"/>
+    </row>
+    <row r="42" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="46"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42">
+        <v>431</v>
+      </c>
+      <c r="G42" s="42">
+        <v>3</v>
+      </c>
+      <c r="H42" s="42">
+        <v>1</v>
+      </c>
+      <c r="I42" s="42"/>
+      <c r="J42" s="42"/>
+      <c r="K42" s="42"/>
+      <c r="L42" s="42"/>
+      <c r="M42" s="42"/>
+      <c r="N42" s="42"/>
+      <c r="O42" s="42">
+        <v>2</v>
+      </c>
+      <c r="P42" s="42">
+        <v>16</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>2</v>
+      </c>
+      <c r="R42" s="86" t="s">
+        <v>54</v>
+      </c>
+      <c r="S42" s="87"/>
+      <c r="T42" s="87"/>
+      <c r="U42" s="87"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3"/>
+    </row>
+    <row r="43" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="3"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+      <c r="L43" s="44"/>
+      <c r="M43" s="44"/>
+      <c r="N43" s="44"/>
+      <c r="O43" s="44"/>
+      <c r="P43" s="44"/>
+      <c r="Q43" s="44"/>
+      <c r="R43" s="44"/>
+      <c r="S43" s="44"/>
+      <c r="T43" s="44"/>
+      <c r="U43" s="82"/>
+      <c r="V43" s="82"/>
+      <c r="W43" s="82"/>
+      <c r="X43" s="82"/>
+      <c r="Y43" s="82"/>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B44" s="76" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" s="94">
+        <f>12+70+356</f>
+        <v>438</v>
+      </c>
+      <c r="D44" s="94"/>
+      <c r="E44" s="94"/>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B45" s="76" t="s">
+        <v>69</v>
+      </c>
+      <c r="C45" s="94"/>
+      <c r="D45" s="94"/>
+      <c r="E45" s="94"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="R34:U34"/>
+    <mergeCell ref="R42:U42"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="O34:Q34"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="90" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00C7745F-FED7-4415-9492-E74DC3086A90}">
+  <dimension ref="B1:AA45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.140625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.140625" style="2" customWidth="1"/>
+    <col min="20" max="21" width="5.7109375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="29" width="5.7109375" style="2" customWidth="1"/>
+    <col min="30" max="16384" width="8.7109375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="3"/>
+    </row>
+    <row r="2" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6">
+        <f>[1]DSSR!B4</f>
+        <v>1300</v>
+      </c>
+      <c r="D3" s="6">
+        <f>[1]DSSR!C4</f>
+        <v>1534</v>
+      </c>
+      <c r="E3" s="6">
+        <f>[1]DSSR!D4</f>
+        <v>1728</v>
+      </c>
+      <c r="F3" s="6">
+        <f>[1]DSSR!E4</f>
+        <v>1728</v>
+      </c>
+      <c r="G3" s="6">
+        <f>[1]DSSR!F4</f>
+        <v>1452</v>
+      </c>
+      <c r="H3" s="6">
+        <f>[1]DSSR!G4</f>
+        <v>1240</v>
+      </c>
+      <c r="I3" s="6">
+        <f>[1]DSSR!H4</f>
+        <v>1520</v>
+      </c>
+      <c r="J3" s="6">
+        <f>[1]DSSR!I4</f>
+        <v>978</v>
+      </c>
+      <c r="K3" s="6">
+        <f>[1]DSSR!J4</f>
+        <v>945</v>
+      </c>
+      <c r="L3" s="6">
+        <f>[1]DSSR!K4</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="6">
+        <f>[1]DSSR!L4</f>
+        <v>1127</v>
+      </c>
+      <c r="N3" s="6">
+        <f>[1]DSSR!M4</f>
+        <v>773</v>
+      </c>
+      <c r="O3" s="6">
+        <f>[1]DSSR!N4</f>
+        <v>1038</v>
+      </c>
+      <c r="P3" s="6">
+        <f>[1]DSSR!O4</f>
+        <v>773</v>
+      </c>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6">
+        <f>[1]DSSR!P4</f>
+        <v>1038</v>
+      </c>
+      <c r="U3" s="6">
+        <f>[1]DSSR!Q4</f>
+        <v>773</v>
+      </c>
+      <c r="V3" s="6">
+        <f>[1]DSSR!R4</f>
+        <v>1038</v>
+      </c>
+      <c r="W3" s="6">
+        <f>[1]DSSR!S4</f>
+        <v>792</v>
+      </c>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6">
+        <f>[1]DSSR!T4</f>
+        <v>948</v>
+      </c>
+    </row>
+    <row r="4" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6">
+        <f>[1]DSSR!B5</f>
+        <v>120</v>
+      </c>
+      <c r="D4" s="6">
+        <f>[1]DSSR!C5</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="6">
+        <f>[1]DSSR!D5</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <f>[1]DSSR!E5</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="6">
+        <f>[1]DSSR!F5</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
+        <f>[1]DSSR!G5</f>
+        <v>120</v>
+      </c>
+      <c r="I4" s="6">
+        <f>[1]DSSR!H5</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <f>[1]DSSR!I5</f>
+        <v>120</v>
+      </c>
+      <c r="K4" s="6">
+        <f>[1]DSSR!J5</f>
+        <v>120</v>
+      </c>
+      <c r="L4" s="6">
+        <f>[1]DSSR!K5</f>
+        <v>111</v>
+      </c>
+      <c r="M4" s="6">
+        <f>[1]DSSR!L5</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="6">
+        <f>[1]DSSR!M5</f>
+        <v>120</v>
+      </c>
+      <c r="O4" s="6">
+        <f>[1]DSSR!N5</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="6">
+        <f>[1]DSSR!O5</f>
+        <v>120</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6">
+        <f>[1]DSSR!P5</f>
+        <v>0</v>
+      </c>
+      <c r="U4" s="6">
+        <f>[1]DSSR!Q5</f>
+        <v>120</v>
+      </c>
+      <c r="V4" s="6">
+        <f>[1]DSSR!R5</f>
+        <v>0</v>
+      </c>
+      <c r="W4" s="6">
+        <f>[1]DSSR!S5</f>
+        <v>120</v>
+      </c>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6">
+        <f>[1]DSSR!T5</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="7">
+        <v>84</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7">
+        <v>84</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7">
+        <v>84</v>
+      </c>
+      <c r="K5" s="7">
+        <v>84</v>
+      </c>
+      <c r="L5" s="7">
+        <v>84</v>
+      </c>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7">
+        <v>84</v>
+      </c>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7">
+        <v>84</v>
+      </c>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7">
+        <v>84</v>
+      </c>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7">
+        <v>84</v>
+      </c>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="L6" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="R7" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="S7" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="T7" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="V7" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y7" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="12"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14">
+        <v>2</v>
+      </c>
+      <c r="E8" s="14">
+        <v>2</v>
+      </c>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14">
+        <v>16</v>
+      </c>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14">
+        <v>2</v>
+      </c>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="14">
+        <v>2</v>
+      </c>
+      <c r="X8" s="59"/>
+      <c r="Y8" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="60"/>
+      <c r="Y9" s="20"/>
+    </row>
+    <row r="10" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="60"/>
+      <c r="Y10" s="20"/>
+    </row>
+    <row r="11" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="16"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="60"/>
+      <c r="Y11" s="20"/>
+    </row>
+    <row r="12" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="60"/>
+      <c r="Y12" s="20"/>
+    </row>
+    <row r="13" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="60"/>
+      <c r="Y13" s="20"/>
+    </row>
+    <row r="14" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="16"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="19"/>
+      <c r="V14" s="19"/>
+      <c r="W14" s="19"/>
+      <c r="X14" s="60"/>
+      <c r="Y14" s="20"/>
+    </row>
+    <row r="15" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23">
+        <v>2</v>
+      </c>
+      <c r="E15" s="23">
+        <v>2</v>
+      </c>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23">
+        <v>7</v>
+      </c>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="T15" s="23">
+        <v>2</v>
+      </c>
+      <c r="U15" s="23"/>
+      <c r="V15" s="23"/>
+      <c r="W15" s="23">
+        <v>0</v>
+      </c>
+      <c r="X15" s="61"/>
+      <c r="Y15" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="57"/>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
+      <c r="E16" s="27">
+        <v>0</v>
+      </c>
+      <c r="F16" s="27"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28">
+        <v>9</v>
+      </c>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
+      <c r="U16" s="28"/>
+      <c r="V16" s="28"/>
+      <c r="W16" s="56">
+        <v>4</v>
+      </c>
+      <c r="X16" s="62"/>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="32"/>
+    </row>
+    <row r="18" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="34">
+        <f>[1]DSSR!B24</f>
+        <v>544</v>
+      </c>
+      <c r="D18" s="34">
+        <f>[1]DSSR!C24</f>
+        <v>1127</v>
+      </c>
+      <c r="E18" s="34">
+        <f>[1]DSSR!D24</f>
+        <v>853</v>
+      </c>
+      <c r="F18" s="34">
+        <f>[1]DSSR!E24</f>
+        <v>563</v>
+      </c>
+      <c r="G18" s="34">
+        <f>[1]DSSR!F24</f>
+        <v>575</v>
+      </c>
+      <c r="H18" s="34">
+        <f>[1]DSSR!G24</f>
+        <v>1175</v>
+      </c>
+      <c r="I18" s="34">
+        <f>[1]DSSR!H24</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="34">
+        <f>[1]DSSR!I24</f>
+        <v>791</v>
+      </c>
+      <c r="K18" s="34">
+        <f>[1]DSSR!J24</f>
+        <v>1102</v>
+      </c>
+      <c r="L18" s="34">
+        <f>[1]DSSR!K24</f>
+        <v>520</v>
+      </c>
+      <c r="M18" s="34">
+        <f>[1]DSSR!L24</f>
+        <v>1142</v>
+      </c>
+      <c r="N18" s="34">
+        <f>[1]DSSR!M24</f>
+        <v>205</v>
+      </c>
+      <c r="O18" s="34">
+        <f>[1]DSSR!N24</f>
+        <v>205</v>
+      </c>
+      <c r="P18" s="34">
+        <f>[1]DSSR!O24</f>
+        <v>205</v>
+      </c>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="34"/>
+      <c r="S18" s="34"/>
+      <c r="T18" s="34">
+        <f>[1]DSSR!P24</f>
+        <v>500</v>
+      </c>
+      <c r="U18" s="34">
+        <f>[1]DSSR!Q24</f>
+        <v>650</v>
+      </c>
+      <c r="V18" s="34">
+        <f>[1]DSSR!R24</f>
+        <v>650</v>
+      </c>
+      <c r="W18" s="34">
+        <f>[1]DSSR!S24</f>
+        <v>500</v>
+      </c>
+      <c r="X18" s="34"/>
+      <c r="Y18" s="35">
+        <f>[1]DSSR!T24</f>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="34">
+        <f>[1]DSSR!B25</f>
+        <v>111</v>
+      </c>
+      <c r="D19" s="34">
+        <f>[1]DSSR!C25</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="34">
+        <f>[1]DSSR!D25</f>
+        <v>120</v>
+      </c>
+      <c r="F19" s="34">
+        <f>[1]DSSR!E25</f>
+        <v>111</v>
+      </c>
+      <c r="G19" s="34">
+        <f>[1]DSSR!F25</f>
+        <v>111</v>
+      </c>
+      <c r="H19" s="34">
+        <f>[1]DSSR!G25</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="34">
+        <f>[1]DSSR!H25</f>
+        <v>111</v>
+      </c>
+      <c r="J19" s="34">
+        <f>[1]DSSR!I25</f>
+        <v>120</v>
+      </c>
+      <c r="K19" s="34">
+        <f>[1]DSSR!J25</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="34">
+        <f>[1]DSSR!K25</f>
+        <v>111</v>
+      </c>
+      <c r="M19" s="34">
+        <f>[1]DSSR!L25</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="34">
+        <f>[1]DSSR!M25</f>
+        <v>78</v>
+      </c>
+      <c r="O19" s="34">
+        <f>[1]DSSR!N25</f>
+        <v>78</v>
+      </c>
+      <c r="P19" s="34">
+        <f>[1]DSSR!O25</f>
+        <v>78</v>
+      </c>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+      <c r="S19" s="34"/>
+      <c r="T19" s="34">
+        <f>[1]DSSR!P25</f>
+        <v>120</v>
+      </c>
+      <c r="U19" s="34">
+        <f>[1]DSSR!Q25</f>
+        <v>0</v>
+      </c>
+      <c r="V19" s="34">
+        <f>[1]DSSR!R25</f>
+        <v>0</v>
+      </c>
+      <c r="W19" s="34">
+        <f>[1]DSSR!S25</f>
+        <v>120</v>
+      </c>
+      <c r="X19" s="34"/>
+      <c r="Y19" s="35">
+        <f>[1]DSSR!T25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="34">
+        <v>84</v>
+      </c>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34">
+        <v>84</v>
+      </c>
+      <c r="F20" s="34">
+        <v>84</v>
+      </c>
+      <c r="G20" s="34">
+        <v>84</v>
+      </c>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34">
+        <v>84</v>
+      </c>
+      <c r="J20" s="34">
+        <v>84</v>
+      </c>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34">
+        <v>84</v>
+      </c>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34">
+        <v>42</v>
+      </c>
+      <c r="O20" s="34">
+        <v>42</v>
+      </c>
+      <c r="P20" s="34">
+        <v>42</v>
+      </c>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="34"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="34">
+        <v>84</v>
+      </c>
+      <c r="U20" s="34"/>
+      <c r="V20" s="34"/>
+      <c r="W20" s="34">
+        <v>84</v>
+      </c>
+      <c r="X20" s="34"/>
+      <c r="Y20" s="35"/>
+    </row>
+    <row r="21" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="F21" s="36">
+        <f>4.5/2</f>
+        <v>2.25</v>
+      </c>
+      <c r="G21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="J21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="O21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="P21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+      <c r="S21" s="34"/>
+      <c r="T21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="U21" s="34"/>
+      <c r="V21" s="34"/>
+      <c r="W21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="X21" s="34"/>
+      <c r="Y21" s="35"/>
+    </row>
+    <row r="22" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="33"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="34"/>
+      <c r="S22" s="34"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="34"/>
+      <c r="V22" s="34"/>
+      <c r="W22" s="34"/>
+      <c r="X22" s="34"/>
+      <c r="Y22" s="35"/>
+    </row>
+    <row r="23" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="37"/>
+      <c r="C23" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O23" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P23" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q23" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="R23" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="V23" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="11"/>
+    </row>
+    <row r="24" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14">
+        <v>30</v>
+      </c>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14">
+        <v>1</v>
+      </c>
+      <c r="M24" s="14">
+        <v>426</v>
+      </c>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="14"/>
+      <c r="Y24" s="15"/>
+    </row>
+    <row r="25" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="17"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="19"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="19"/>
+      <c r="X25" s="60"/>
+      <c r="Y25" s="20"/>
+    </row>
+    <row r="26" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="16"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="19"/>
+      <c r="U26" s="19"/>
+      <c r="V26" s="19"/>
+      <c r="W26" s="19"/>
+      <c r="X26" s="60"/>
+      <c r="Y26" s="20"/>
+    </row>
+    <row r="27" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="16"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="19"/>
+      <c r="U27" s="19"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="19"/>
+      <c r="X27" s="60"/>
+      <c r="Y27" s="20"/>
+    </row>
+    <row r="28" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="16"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="19"/>
+      <c r="X28" s="60"/>
+      <c r="Y28" s="20"/>
+    </row>
+    <row r="29" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="16"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="19"/>
+      <c r="W29" s="19"/>
+      <c r="X29" s="60"/>
+      <c r="Y29" s="20"/>
+    </row>
+    <row r="30" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="16"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="19"/>
+      <c r="U30" s="19"/>
+      <c r="V30" s="19"/>
+      <c r="W30" s="19"/>
+      <c r="X30" s="60"/>
+      <c r="Y30" s="20"/>
+    </row>
+    <row r="31" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23">
+        <v>0</v>
+      </c>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23">
+        <v>1</v>
+      </c>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="23">
+        <v>2</v>
+      </c>
+      <c r="L31" s="23">
+        <v>0</v>
+      </c>
+      <c r="M31" s="23">
+        <v>147</v>
+      </c>
+      <c r="N31" s="23"/>
+      <c r="O31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="23"/>
+      <c r="S31" s="23"/>
+      <c r="T31" s="23"/>
+      <c r="U31" s="23"/>
+      <c r="V31" s="23"/>
+      <c r="W31" s="23"/>
+      <c r="X31" s="61"/>
+      <c r="Y31" s="24"/>
+    </row>
+    <row r="32" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="26"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27">
+        <v>2</v>
+      </c>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28">
+        <v>89</v>
+      </c>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>1</v>
+      </c>
+      <c r="M32" s="28">
+        <v>279</v>
+      </c>
+      <c r="N32" s="28"/>
+      <c r="O32" s="23"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="28"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="63"/>
+      <c r="Y32" s="29"/>
+    </row>
+    <row r="33" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="30"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="68"/>
+      <c r="S33" s="68"/>
+      <c r="T33" s="68"/>
+      <c r="U33" s="68"/>
+      <c r="V33" s="31"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="31"/>
+      <c r="Y33" s="31"/>
+    </row>
+    <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="88" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="90"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="92" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="90"/>
+      <c r="H34" s="91"/>
+      <c r="I34" s="92" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34" s="90"/>
+      <c r="K34" s="91"/>
+      <c r="L34" s="92" t="s">
+        <v>46</v>
+      </c>
+      <c r="M34" s="90"/>
+      <c r="N34" s="91"/>
+      <c r="O34" s="93" t="s">
+        <v>47</v>
+      </c>
+      <c r="P34" s="93"/>
+      <c r="Q34" s="93"/>
+      <c r="R34" s="83" t="s">
+        <v>48</v>
+      </c>
+      <c r="S34" s="84"/>
+      <c r="T34" s="84"/>
+      <c r="U34" s="85"/>
+      <c r="V34" s="66"/>
+      <c r="W34" s="3"/>
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
+    </row>
+    <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="89"/>
+      <c r="C35" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="G35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="J35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="K35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="L35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="M35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="N35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="O35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="P35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q35" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="R35" s="69"/>
+      <c r="S35" s="70"/>
+      <c r="T35" s="70"/>
+      <c r="U35" s="71"/>
+      <c r="V35" s="82"/>
+      <c r="W35" s="82"/>
+      <c r="X35" s="82"/>
+      <c r="Y35" s="82"/>
+    </row>
+    <row r="36" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="46">
+        <v>2</v>
+      </c>
+      <c r="D36" s="41">
+        <v>1</v>
+      </c>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42">
+        <v>347</v>
+      </c>
+      <c r="G36" s="42">
+        <v>9</v>
+      </c>
+      <c r="H36" s="42">
+        <v>3</v>
+      </c>
+      <c r="I36" s="42">
+        <v>9</v>
+      </c>
+      <c r="J36" s="42">
+        <v>2</v>
+      </c>
+      <c r="K36" s="42">
+        <v>11</v>
+      </c>
+      <c r="L36" s="42">
+        <v>2</v>
+      </c>
+      <c r="M36" s="42">
+        <v>1</v>
+      </c>
+      <c r="N36" s="42">
+        <v>19</v>
+      </c>
+      <c r="O36" s="42">
+        <v>7</v>
+      </c>
+      <c r="P36" s="42">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>11</v>
+      </c>
+      <c r="R36" s="72"/>
+      <c r="S36" s="44"/>
+      <c r="T36" s="44"/>
+      <c r="U36" s="82"/>
+      <c r="V36" s="82"/>
+      <c r="W36" s="82"/>
+      <c r="X36" s="82"/>
+      <c r="Y36" s="82"/>
+    </row>
+    <row r="37" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="53"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="48"/>
+      <c r="M37" s="48"/>
+      <c r="N37" s="48"/>
+      <c r="O37" s="48"/>
+      <c r="P37" s="48"/>
+      <c r="Q37" s="64"/>
+      <c r="R37" s="72"/>
+      <c r="S37" s="44"/>
+      <c r="T37" s="44"/>
+      <c r="U37" s="82"/>
+      <c r="V37" s="82"/>
+      <c r="W37" s="82"/>
+      <c r="X37" s="82"/>
+      <c r="Y37" s="82"/>
+    </row>
+    <row r="38" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="53"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="19"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="20"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="44"/>
+      <c r="T38" s="44"/>
+      <c r="U38" s="82"/>
+      <c r="V38" s="82"/>
+      <c r="W38" s="82"/>
+      <c r="X38" s="82"/>
+      <c r="Y38" s="82"/>
+    </row>
+    <row r="39" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="53"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="44"/>
+      <c r="T39" s="44"/>
+      <c r="U39" s="82"/>
+      <c r="V39" s="82"/>
+      <c r="W39" s="82"/>
+      <c r="X39" s="82"/>
+      <c r="Y39" s="82"/>
+    </row>
+    <row r="40" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="53"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="72"/>
+      <c r="S40" s="44"/>
+      <c r="T40" s="44"/>
+      <c r="U40" s="82"/>
+      <c r="V40" s="82"/>
+      <c r="W40" s="82"/>
+      <c r="X40" s="82"/>
+      <c r="Y40" s="82"/>
+    </row>
+    <row r="41" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="54"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="40"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="40"/>
+      <c r="M41" s="40"/>
+      <c r="N41" s="40"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="65"/>
+      <c r="R41" s="73"/>
+      <c r="S41" s="74"/>
+      <c r="T41" s="74"/>
+      <c r="U41" s="75"/>
+      <c r="V41" s="82"/>
+      <c r="W41" s="82"/>
+      <c r="X41" s="82"/>
+      <c r="Y41" s="82"/>
+    </row>
+    <row r="42" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="46">
+        <v>2</v>
+      </c>
+      <c r="D42" s="41">
+        <v>1</v>
+      </c>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42">
+        <v>347</v>
+      </c>
+      <c r="G42" s="42">
+        <v>9</v>
+      </c>
+      <c r="H42" s="42">
+        <v>3</v>
+      </c>
+      <c r="I42" s="42">
+        <v>9</v>
+      </c>
+      <c r="J42" s="42">
+        <v>2</v>
+      </c>
+      <c r="K42" s="42">
+        <v>11</v>
+      </c>
+      <c r="L42" s="42">
+        <v>2</v>
+      </c>
+      <c r="M42" s="42">
+        <v>1</v>
+      </c>
+      <c r="N42" s="42">
+        <v>19</v>
+      </c>
+      <c r="O42" s="42">
+        <v>7</v>
+      </c>
+      <c r="P42" s="42">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>11</v>
+      </c>
+      <c r="R42" s="86" t="s">
+        <v>54</v>
+      </c>
+      <c r="S42" s="87"/>
+      <c r="T42" s="87"/>
+      <c r="U42" s="87"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3"/>
+    </row>
+    <row r="43" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="3"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+      <c r="L43" s="44"/>
+      <c r="M43" s="44"/>
+      <c r="N43" s="44"/>
+      <c r="O43" s="44"/>
+      <c r="P43" s="44"/>
+      <c r="Q43" s="44"/>
+      <c r="R43" s="44"/>
+      <c r="S43" s="44"/>
+      <c r="T43" s="44"/>
+      <c r="U43" s="82"/>
+      <c r="V43" s="82"/>
+      <c r="W43" s="82"/>
+      <c r="X43" s="82"/>
+      <c r="Y43" s="82"/>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B44" s="76" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" s="94">
+        <f>9+4+2+89+1+279</f>
+        <v>384</v>
+      </c>
+      <c r="D44" s="94"/>
+      <c r="E44" s="94"/>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B45" s="76" t="s">
+        <v>69</v>
+      </c>
+      <c r="C45" s="94"/>
+      <c r="D45" s="94"/>
+      <c r="E45" s="94"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="R34:U34"/>
+    <mergeCell ref="R42:U42"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="O34:Q34"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="90" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -18202,47 +24970,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="87" t="s">
+      <c r="B34" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="89" t="s">
+      <c r="C34" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="89"/>
-      <c r="E34" s="90"/>
-      <c r="F34" s="91" t="s">
+      <c r="D34" s="90"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="89"/>
-      <c r="H34" s="90"/>
-      <c r="I34" s="91" t="s">
+      <c r="G34" s="90"/>
+      <c r="H34" s="91"/>
+      <c r="I34" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="89"/>
-      <c r="K34" s="90"/>
-      <c r="L34" s="91" t="s">
+      <c r="J34" s="90"/>
+      <c r="K34" s="91"/>
+      <c r="L34" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="89"/>
-      <c r="N34" s="90"/>
-      <c r="O34" s="92" t="s">
+      <c r="M34" s="90"/>
+      <c r="N34" s="91"/>
+      <c r="O34" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="92"/>
-      <c r="Q34" s="92"/>
-      <c r="R34" s="82" t="s">
+      <c r="P34" s="93"/>
+      <c r="Q34" s="93"/>
+      <c r="R34" s="83" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="83"/>
-      <c r="T34" s="83"/>
-      <c r="U34" s="84"/>
+      <c r="S34" s="84"/>
+      <c r="T34" s="84"/>
+      <c r="U34" s="85"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="88"/>
+      <c r="B35" s="89"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -18474,12 +25242,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="85" t="s">
+      <c r="R42" s="86" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="86"/>
-      <c r="T42" s="86"/>
-      <c r="U42" s="86"/>
+      <c r="S42" s="87"/>
+      <c r="T42" s="87"/>
+      <c r="U42" s="87"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -18515,17 +25283,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="93"/>
-      <c r="D44" s="93"/>
-      <c r="E44" s="93"/>
+      <c r="C44" s="94"/>
+      <c r="D44" s="94"/>
+      <c r="E44" s="94"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="93"/>
-      <c r="D45" s="93"/>
-      <c r="E45" s="93"/>
+      <c r="C45" s="94"/>
+      <c r="D45" s="94"/>
+      <c r="E45" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -19903,47 +26671,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="87" t="s">
+      <c r="B34" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="89" t="s">
+      <c r="C34" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="89"/>
-      <c r="E34" s="90"/>
-      <c r="F34" s="91" t="s">
+      <c r="D34" s="90"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="89"/>
-      <c r="H34" s="90"/>
-      <c r="I34" s="91" t="s">
+      <c r="G34" s="90"/>
+      <c r="H34" s="91"/>
+      <c r="I34" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="89"/>
-      <c r="K34" s="90"/>
-      <c r="L34" s="91" t="s">
+      <c r="J34" s="90"/>
+      <c r="K34" s="91"/>
+      <c r="L34" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="89"/>
-      <c r="N34" s="90"/>
-      <c r="O34" s="92" t="s">
+      <c r="M34" s="90"/>
+      <c r="N34" s="91"/>
+      <c r="O34" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="92"/>
-      <c r="Q34" s="92"/>
-      <c r="R34" s="82" t="s">
+      <c r="P34" s="93"/>
+      <c r="Q34" s="93"/>
+      <c r="R34" s="83" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="83"/>
-      <c r="T34" s="83"/>
-      <c r="U34" s="84"/>
+      <c r="S34" s="84"/>
+      <c r="T34" s="84"/>
+      <c r="U34" s="85"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="88"/>
+      <c r="B35" s="89"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -20211,12 +26979,12 @@
       <c r="Q42" s="43">
         <v>9</v>
       </c>
-      <c r="R42" s="85" t="s">
+      <c r="R42" s="86" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="86"/>
-      <c r="T42" s="86"/>
-      <c r="U42" s="86"/>
+      <c r="S42" s="87"/>
+      <c r="T42" s="87"/>
+      <c r="U42" s="87"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -20252,22 +27020,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="93">
+      <c r="C44" s="94">
         <f>10+5+1+54+8+256</f>
         <v>334</v>
       </c>
-      <c r="D44" s="93"/>
-      <c r="E44" s="93"/>
+      <c r="D44" s="94"/>
+      <c r="E44" s="94"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="93">
+      <c r="C45" s="94">
         <v>12</v>
       </c>
-      <c r="D45" s="93"/>
-      <c r="E45" s="93"/>
+      <c r="D45" s="94"/>
+      <c r="E45" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -21645,47 +28413,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="87" t="s">
+      <c r="B34" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="89" t="s">
+      <c r="C34" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="89"/>
-      <c r="E34" s="90"/>
-      <c r="F34" s="91" t="s">
+      <c r="D34" s="90"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="89"/>
-      <c r="H34" s="90"/>
-      <c r="I34" s="91" t="s">
+      <c r="G34" s="90"/>
+      <c r="H34" s="91"/>
+      <c r="I34" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="89"/>
-      <c r="K34" s="90"/>
-      <c r="L34" s="91" t="s">
+      <c r="J34" s="90"/>
+      <c r="K34" s="91"/>
+      <c r="L34" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="89"/>
-      <c r="N34" s="90"/>
-      <c r="O34" s="92" t="s">
+      <c r="M34" s="90"/>
+      <c r="N34" s="91"/>
+      <c r="O34" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="92"/>
-      <c r="Q34" s="92"/>
-      <c r="R34" s="82" t="s">
+      <c r="P34" s="93"/>
+      <c r="Q34" s="93"/>
+      <c r="R34" s="83" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="83"/>
-      <c r="T34" s="83"/>
-      <c r="U34" s="84"/>
+      <c r="S34" s="84"/>
+      <c r="T34" s="84"/>
+      <c r="U34" s="85"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="88"/>
+      <c r="B35" s="89"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -21949,12 +28717,12 @@
       <c r="Q42" s="43">
         <v>1</v>
       </c>
-      <c r="R42" s="85" t="s">
+      <c r="R42" s="86" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="86"/>
-      <c r="T42" s="86"/>
-      <c r="U42" s="86"/>
+      <c r="S42" s="87"/>
+      <c r="T42" s="87"/>
+      <c r="U42" s="87"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -21990,22 +28758,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="93">
+      <c r="C44" s="94">
         <f>12+5+2+378</f>
         <v>397</v>
       </c>
-      <c r="D44" s="93"/>
-      <c r="E44" s="93"/>
+      <c r="D44" s="94"/>
+      <c r="E44" s="94"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="93">
+      <c r="C45" s="94">
         <v>12</v>
       </c>
-      <c r="D45" s="93"/>
-      <c r="E45" s="93"/>
+      <c r="D45" s="94"/>
+      <c r="E45" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -23302,47 +30070,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="87" t="s">
+      <c r="B34" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="89" t="s">
+      <c r="C34" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="89"/>
-      <c r="E34" s="90"/>
-      <c r="F34" s="91" t="s">
+      <c r="D34" s="90"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="89"/>
-      <c r="H34" s="90"/>
-      <c r="I34" s="91" t="s">
+      <c r="G34" s="90"/>
+      <c r="H34" s="91"/>
+      <c r="I34" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="89"/>
-      <c r="K34" s="90"/>
-      <c r="L34" s="91" t="s">
+      <c r="J34" s="90"/>
+      <c r="K34" s="91"/>
+      <c r="L34" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="89"/>
-      <c r="N34" s="90"/>
-      <c r="O34" s="92" t="s">
+      <c r="M34" s="90"/>
+      <c r="N34" s="91"/>
+      <c r="O34" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="92"/>
-      <c r="Q34" s="92"/>
-      <c r="R34" s="82" t="s">
+      <c r="P34" s="93"/>
+      <c r="Q34" s="93"/>
+      <c r="R34" s="83" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="83"/>
-      <c r="T34" s="83"/>
-      <c r="U34" s="84"/>
+      <c r="S34" s="84"/>
+      <c r="T34" s="84"/>
+      <c r="U34" s="85"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="88"/>
+      <c r="B35" s="89"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -23574,12 +30342,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="85" t="s">
+      <c r="R42" s="86" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="86"/>
-      <c r="T42" s="86"/>
-      <c r="U42" s="86"/>
+      <c r="S42" s="87"/>
+      <c r="T42" s="87"/>
+      <c r="U42" s="87"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -24909,47 +31677,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="87" t="s">
+      <c r="B34" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="89" t="s">
+      <c r="C34" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="89"/>
-      <c r="E34" s="90"/>
-      <c r="F34" s="91" t="s">
+      <c r="D34" s="90"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="89"/>
-      <c r="H34" s="90"/>
-      <c r="I34" s="91" t="s">
+      <c r="G34" s="90"/>
+      <c r="H34" s="91"/>
+      <c r="I34" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="89"/>
-      <c r="K34" s="90"/>
-      <c r="L34" s="91" t="s">
+      <c r="J34" s="90"/>
+      <c r="K34" s="91"/>
+      <c r="L34" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="89"/>
-      <c r="N34" s="90"/>
-      <c r="O34" s="92" t="s">
+      <c r="M34" s="90"/>
+      <c r="N34" s="91"/>
+      <c r="O34" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="92"/>
-      <c r="Q34" s="92"/>
-      <c r="R34" s="82" t="s">
+      <c r="P34" s="93"/>
+      <c r="Q34" s="93"/>
+      <c r="R34" s="83" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="83"/>
-      <c r="T34" s="83"/>
-      <c r="U34" s="84"/>
+      <c r="S34" s="84"/>
+      <c r="T34" s="84"/>
+      <c r="U34" s="85"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="88"/>
+      <c r="B35" s="89"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -25181,12 +31949,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="85" t="s">
+      <c r="R42" s="86" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="86"/>
-      <c r="T42" s="86"/>
-      <c r="U42" s="86"/>
+      <c r="S42" s="87"/>
+      <c r="T42" s="87"/>
+      <c r="U42" s="87"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -25222,17 +31990,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="93"/>
-      <c r="D44" s="93"/>
-      <c r="E44" s="93"/>
+      <c r="C44" s="94"/>
+      <c r="D44" s="94"/>
+      <c r="E44" s="94"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="93"/>
-      <c r="D45" s="93"/>
-      <c r="E45" s="93"/>
+      <c r="C45" s="94"/>
+      <c r="D45" s="94"/>
+      <c r="E45" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -26598,47 +33366,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="87" t="s">
+      <c r="B34" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="89" t="s">
+      <c r="C34" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="89"/>
-      <c r="E34" s="90"/>
-      <c r="F34" s="91" t="s">
+      <c r="D34" s="90"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="89"/>
-      <c r="H34" s="90"/>
-      <c r="I34" s="91" t="s">
+      <c r="G34" s="90"/>
+      <c r="H34" s="91"/>
+      <c r="I34" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="89"/>
-      <c r="K34" s="90"/>
-      <c r="L34" s="91" t="s">
+      <c r="J34" s="90"/>
+      <c r="K34" s="91"/>
+      <c r="L34" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="89"/>
-      <c r="N34" s="90"/>
-      <c r="O34" s="92" t="s">
+      <c r="M34" s="90"/>
+      <c r="N34" s="91"/>
+      <c r="O34" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="92"/>
-      <c r="Q34" s="92"/>
-      <c r="R34" s="82" t="s">
+      <c r="P34" s="93"/>
+      <c r="Q34" s="93"/>
+      <c r="R34" s="83" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="83"/>
-      <c r="T34" s="83"/>
-      <c r="U34" s="84"/>
+      <c r="S34" s="84"/>
+      <c r="T34" s="84"/>
+      <c r="U34" s="85"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="88"/>
+      <c r="B35" s="89"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -26918,12 +33686,12 @@
       <c r="Q42" s="43">
         <v>16</v>
       </c>
-      <c r="R42" s="85" t="s">
+      <c r="R42" s="86" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="86"/>
-      <c r="T42" s="86"/>
-      <c r="U42" s="86"/>
+      <c r="S42" s="87"/>
+      <c r="T42" s="87"/>
+      <c r="U42" s="87"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -26959,20 +33727,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="93">
+      <c r="C44" s="94">
         <f>2+5+1+2+1+25+46+10+282</f>
         <v>374</v>
       </c>
-      <c r="D44" s="93"/>
-      <c r="E44" s="93"/>
+      <c r="D44" s="94"/>
+      <c r="E44" s="94"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="93"/>
-      <c r="D45" s="93"/>
-      <c r="E45" s="93"/>
+      <c r="C45" s="94"/>
+      <c r="D45" s="94"/>
+      <c r="E45" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -28344,47 +35112,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="87" t="s">
+      <c r="B34" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="89" t="s">
+      <c r="C34" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="89"/>
-      <c r="E34" s="90"/>
-      <c r="F34" s="91" t="s">
+      <c r="D34" s="90"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="89"/>
-      <c r="H34" s="90"/>
-      <c r="I34" s="91" t="s">
+      <c r="G34" s="90"/>
+      <c r="H34" s="91"/>
+      <c r="I34" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="89"/>
-      <c r="K34" s="90"/>
-      <c r="L34" s="91" t="s">
+      <c r="J34" s="90"/>
+      <c r="K34" s="91"/>
+      <c r="L34" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="89"/>
-      <c r="N34" s="90"/>
-      <c r="O34" s="92" t="s">
+      <c r="M34" s="90"/>
+      <c r="N34" s="91"/>
+      <c r="O34" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="92"/>
-      <c r="Q34" s="92"/>
-      <c r="R34" s="82" t="s">
+      <c r="P34" s="93"/>
+      <c r="Q34" s="93"/>
+      <c r="R34" s="83" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="83"/>
-      <c r="T34" s="83"/>
-      <c r="U34" s="84"/>
+      <c r="S34" s="84"/>
+      <c r="T34" s="84"/>
+      <c r="U34" s="85"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="88"/>
+      <c r="B35" s="89"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -28640,12 +35408,12 @@
       <c r="Q42" s="43">
         <v>17</v>
       </c>
-      <c r="R42" s="85" t="s">
+      <c r="R42" s="86" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="86"/>
-      <c r="T42" s="86"/>
-      <c r="U42" s="86"/>
+      <c r="S42" s="87"/>
+      <c r="T42" s="87"/>
+      <c r="U42" s="87"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -28681,20 +35449,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="93">
+      <c r="C44" s="94">
         <f>8+1+53+6+271</f>
         <v>339</v>
       </c>
-      <c r="D44" s="93"/>
-      <c r="E44" s="93"/>
+      <c r="D44" s="94"/>
+      <c r="E44" s="94"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="93"/>
-      <c r="D45" s="93"/>
-      <c r="E45" s="93"/>
+      <c r="C45" s="94"/>
+      <c r="D45" s="94"/>
+      <c r="E45" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/GBDS JULY FILES 2026/CSR MONTH OF JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/CSR MONTH OF JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B8A8AC-5014-4641-8C6A-CF8F4C9C3FC2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D59EEC7C-2E04-4B40-9CBE-D61D549DF79B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="8" activeTab="20" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="12" activeTab="24" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | JULY" sheetId="902" r:id="rId1"/>
@@ -34,9 +34,13 @@
     <sheet name="07-07 R1" sheetId="1808" r:id="rId19"/>
     <sheet name="07-07 R2" sheetId="1809" r:id="rId20"/>
     <sheet name="07-07 R3" sheetId="1810" r:id="rId21"/>
+    <sheet name="(8)" sheetId="1811" r:id="rId22"/>
+    <sheet name="07-08 R1" sheetId="1812" r:id="rId23"/>
+    <sheet name="07-08 R2" sheetId="1813" r:id="rId24"/>
+    <sheet name="07-08 R3" sheetId="1814" r:id="rId25"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId22"/>
+    <externalReference r:id="rId26"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'(1)'!$A$1:$Z$44</definedName>
@@ -44,6 +48,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="9">'(3)'!$A$1:$Z$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'(6)'!$A$1:$Z$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="17">'(7)'!$A$1:$Z$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="21">'(8)'!$A$1:$Z$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'07-01 R1 NO TRIP'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'07-01 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'07-01 R3'!$A$1:$V$44</definedName>
@@ -59,6 +64,9 @@
     <definedName name="_xlnm.Print_Area" localSheetId="18">'07-07 R1'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="19">'07-07 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="20">'07-07 R3'!$A$1:$V$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="22">'07-08 R1'!$A$1:$Z$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="23">'07-08 R2'!$A$1:$V$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="24">'07-08 R3'!$A$1:$V$44</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -76,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2172" uniqueCount="90">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -337,6 +345,15 @@
   </si>
   <si>
     <t>DATE ___________07/07/2026___________</t>
+  </si>
+  <si>
+    <t>DATE ___________07/08/2026___________</t>
+  </si>
+  <si>
+    <t>12B</t>
+  </si>
+  <si>
+    <t>9/12B</t>
   </si>
 </sst>
 </file>
@@ -957,7 +974,7 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1212,6 +1229,9 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3076,47 +3096,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="88" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="90" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="90"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="92" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="90"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="92" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="90"/>
-      <c r="K34" s="91"/>
-      <c r="L34" s="92" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="90"/>
-      <c r="N34" s="91"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="83" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="84"/>
-      <c r="T34" s="84"/>
-      <c r="U34" s="85"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="89"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -3348,12 +3368,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="86" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="87"/>
-      <c r="T42" s="87"/>
-      <c r="U42" s="87"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -4737,47 +4757,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="88" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="90" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="90"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="92" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="90"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="92" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="90"/>
-      <c r="K34" s="91"/>
-      <c r="L34" s="92" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="90"/>
-      <c r="N34" s="91"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="83" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="84"/>
-      <c r="T34" s="84"/>
-      <c r="U34" s="85"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="89"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -5049,12 +5069,12 @@
       <c r="Q42" s="43">
         <v>3</v>
       </c>
-      <c r="R42" s="86" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="87"/>
-      <c r="T42" s="87"/>
-      <c r="U42" s="87"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -5090,22 +5110,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="94">
+      <c r="C44" s="95">
         <f>1+1+6+1+8+1+16+404</f>
         <v>438</v>
       </c>
-      <c r="D44" s="94"/>
-      <c r="E44" s="94"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="94">
+      <c r="C45" s="95">
         <v>12</v>
       </c>
-      <c r="D45" s="94"/>
-      <c r="E45" s="94"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -6477,47 +6497,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="88" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="90" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="90"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="92" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="90"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="92" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="90"/>
-      <c r="K34" s="91"/>
-      <c r="L34" s="92" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="90"/>
-      <c r="N34" s="91"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="83" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="84"/>
-      <c r="T34" s="84"/>
-      <c r="U34" s="85"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="89"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -6765,12 +6785,12 @@
       <c r="Q42" s="43">
         <v>11</v>
       </c>
-      <c r="R42" s="86" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="87"/>
-      <c r="T42" s="87"/>
-      <c r="U42" s="87"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -6806,22 +6826,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="94">
+      <c r="C44" s="95">
         <f>8+1+30+2+322</f>
         <v>363</v>
       </c>
-      <c r="D44" s="94"/>
-      <c r="E44" s="94"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="94">
+      <c r="C45" s="95">
         <v>12</v>
       </c>
-      <c r="D45" s="94"/>
-      <c r="E45" s="94"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -8199,47 +8219,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="88" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="90" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="90"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="92" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="90"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="92" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="90"/>
-      <c r="K34" s="91"/>
-      <c r="L34" s="92" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="90"/>
-      <c r="N34" s="91"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="83" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="84"/>
-      <c r="T34" s="84"/>
-      <c r="U34" s="85"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="89"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -8497,12 +8517,12 @@
       <c r="Q42" s="43">
         <v>16</v>
       </c>
-      <c r="R42" s="86" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="87"/>
-      <c r="T42" s="87"/>
-      <c r="U42" s="87"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -8538,17 +8558,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="94"/>
-      <c r="D44" s="94"/>
-      <c r="E44" s="94"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="94"/>
-      <c r="D45" s="94"/>
-      <c r="E45" s="94"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -9845,47 +9865,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="88" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="90" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="90"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="92" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="90"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="92" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="90"/>
-      <c r="K34" s="91"/>
-      <c r="L34" s="92" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="90"/>
-      <c r="N34" s="91"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="83" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="84"/>
-      <c r="T34" s="84"/>
-      <c r="U34" s="85"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="89"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -10117,12 +10137,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="86" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="87"/>
-      <c r="T42" s="87"/>
-      <c r="U42" s="87"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -11500,47 +11520,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="88" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="90" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="90"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="92" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="90"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="92" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="90"/>
-      <c r="K34" s="91"/>
-      <c r="L34" s="92" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="90"/>
-      <c r="N34" s="91"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="83" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="84"/>
-      <c r="T34" s="84"/>
-      <c r="U34" s="85"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="89"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -11824,12 +11844,12 @@
       <c r="Q42" s="43">
         <v>19</v>
       </c>
-      <c r="R42" s="86" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="87"/>
-      <c r="T42" s="87"/>
-      <c r="U42" s="87"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -11865,20 +11885,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="94">
+      <c r="C44" s="95">
         <f>1+1+5+5+3+293</f>
         <v>308</v>
       </c>
-      <c r="D44" s="94"/>
-      <c r="E44" s="94"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="94"/>
-      <c r="D45" s="94"/>
-      <c r="E45" s="94"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -13242,47 +13262,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="88" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="90" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="90"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="92" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="90"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="92" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="90"/>
-      <c r="K34" s="91"/>
-      <c r="L34" s="92" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="90"/>
-      <c r="N34" s="91"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="83" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="84"/>
-      <c r="T34" s="84"/>
-      <c r="U34" s="85"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="89"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -13538,12 +13558,12 @@
         <v>8</v>
       </c>
       <c r="Q42" s="43"/>
-      <c r="R42" s="86" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="87"/>
-      <c r="T42" s="87"/>
-      <c r="U42" s="87"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -13579,22 +13599,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="94">
+      <c r="C44" s="95">
         <f>1+10+25+306</f>
         <v>342</v>
       </c>
-      <c r="D44" s="94"/>
-      <c r="E44" s="94"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="94">
+      <c r="C45" s="95">
         <v>12</v>
       </c>
-      <c r="D45" s="94"/>
-      <c r="E45" s="94"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -14966,47 +14986,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="88" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="90" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="90"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="92" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="90"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="92" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="90"/>
-      <c r="K34" s="91"/>
-      <c r="L34" s="92" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="90"/>
-      <c r="N34" s="91"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="83" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="84"/>
-      <c r="T34" s="84"/>
-      <c r="U34" s="85"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="89"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -15258,12 +15278,12 @@
       <c r="Q42" s="43">
         <v>3</v>
       </c>
-      <c r="R42" s="86" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="87"/>
-      <c r="T42" s="87"/>
-      <c r="U42" s="87"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -15299,20 +15319,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="94">
+      <c r="C44" s="95">
         <f>14+2+20+266</f>
         <v>302</v>
       </c>
-      <c r="D44" s="94"/>
-      <c r="E44" s="94"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="94"/>
-      <c r="D45" s="94"/>
-      <c r="E45" s="94"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -16609,47 +16629,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="88" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="90" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="90"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="92" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="90"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="92" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="90"/>
-      <c r="K34" s="91"/>
-      <c r="L34" s="92" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="90"/>
-      <c r="N34" s="91"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="83" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="84"/>
-      <c r="T34" s="84"/>
-      <c r="U34" s="85"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="89"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -16881,12 +16901,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="86" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="87"/>
-      <c r="T42" s="87"/>
-      <c r="U42" s="87"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -18252,47 +18272,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="88" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="90" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="90"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="92" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="90"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="92" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="90"/>
-      <c r="K34" s="91"/>
-      <c r="L34" s="92" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="90"/>
-      <c r="N34" s="91"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="83" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="84"/>
-      <c r="T34" s="84"/>
-      <c r="U34" s="85"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="89"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -18548,12 +18568,12 @@
       <c r="Q42" s="43">
         <v>21</v>
       </c>
-      <c r="R42" s="86" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="87"/>
-      <c r="T42" s="87"/>
-      <c r="U42" s="87"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -18589,20 +18609,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="94">
+      <c r="C44" s="95">
         <f>12+11+324</f>
         <v>347</v>
       </c>
-      <c r="D44" s="94"/>
-      <c r="E44" s="94"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="94"/>
-      <c r="D45" s="94"/>
-      <c r="E45" s="94"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -19899,47 +19919,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="88" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="90" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="90"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="92" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="90"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="92" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="90"/>
-      <c r="K34" s="91"/>
-      <c r="L34" s="92" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="90"/>
-      <c r="N34" s="91"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="83" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="84"/>
-      <c r="T34" s="84"/>
-      <c r="U34" s="85"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="89"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -20171,12 +20191,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="86" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="87"/>
-      <c r="T42" s="87"/>
-      <c r="U42" s="87"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -21564,47 +21584,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="88" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="90" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="90"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="92" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="90"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="92" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="90"/>
-      <c r="K34" s="91"/>
-      <c r="L34" s="92" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="90"/>
-      <c r="N34" s="91"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="83" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="84"/>
-      <c r="T34" s="84"/>
-      <c r="U34" s="85"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="89"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -21860,12 +21880,12 @@
       <c r="Q42" s="43">
         <v>2</v>
       </c>
-      <c r="R42" s="86" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="87"/>
-      <c r="T42" s="87"/>
-      <c r="U42" s="87"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -21901,20 +21921,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="94">
+      <c r="C44" s="95">
         <f>12+70+356</f>
         <v>438</v>
       </c>
-      <c r="D44" s="94"/>
-      <c r="E44" s="94"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="94"/>
-      <c r="D45" s="94"/>
-      <c r="E45" s="94"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -23286,47 +23306,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="88" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="90" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="90"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="92" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="90"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="92" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="90"/>
-      <c r="K34" s="91"/>
-      <c r="L34" s="92" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="90"/>
-      <c r="N34" s="91"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="83" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="84"/>
-      <c r="T34" s="84"/>
-      <c r="U34" s="85"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="89"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -23614,12 +23634,12 @@
       <c r="Q42" s="43">
         <v>11</v>
       </c>
-      <c r="R42" s="86" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="87"/>
-      <c r="T42" s="87"/>
-      <c r="U42" s="87"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -23655,20 +23675,6792 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="94">
+      <c r="C44" s="95">
         <f>9+4+2+89+1+279</f>
         <v>384</v>
       </c>
-      <c r="D44" s="94"/>
-      <c r="E44" s="94"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="94"/>
-      <c r="D45" s="94"/>
-      <c r="E45" s="94"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="R34:U34"/>
+    <mergeCell ref="R42:U42"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="O34:Q34"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="90" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBC8CBF9-B72D-43BB-B949-61D1600CA4CF}">
+  <dimension ref="B1:AA43"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
+    <col min="3" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.140625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.140625" style="2" customWidth="1"/>
+    <col min="20" max="21" width="5.7109375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="29" width="5.7109375" style="2" customWidth="1"/>
+    <col min="30" max="16384" width="8.7109375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="3"/>
+    </row>
+    <row r="2" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6">
+        <f>[1]DSSR!B4</f>
+        <v>1300</v>
+      </c>
+      <c r="D3" s="6">
+        <f>[1]DSSR!C4</f>
+        <v>1534</v>
+      </c>
+      <c r="E3" s="6">
+        <f>[1]DSSR!D4</f>
+        <v>1728</v>
+      </c>
+      <c r="F3" s="6">
+        <f>[1]DSSR!E4</f>
+        <v>1728</v>
+      </c>
+      <c r="G3" s="6">
+        <f>[1]DSSR!F4</f>
+        <v>1452</v>
+      </c>
+      <c r="H3" s="6">
+        <f>[1]DSSR!G4</f>
+        <v>1240</v>
+      </c>
+      <c r="I3" s="6">
+        <f>[1]DSSR!H4</f>
+        <v>1520</v>
+      </c>
+      <c r="J3" s="6">
+        <f>[1]DSSR!I4</f>
+        <v>978</v>
+      </c>
+      <c r="K3" s="6">
+        <f>[1]DSSR!J4</f>
+        <v>945</v>
+      </c>
+      <c r="L3" s="6">
+        <f>[1]DSSR!K4</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="6">
+        <f>[1]DSSR!L4</f>
+        <v>1127</v>
+      </c>
+      <c r="N3" s="6">
+        <f>[1]DSSR!M4</f>
+        <v>773</v>
+      </c>
+      <c r="O3" s="6">
+        <f>[1]DSSR!N4</f>
+        <v>1038</v>
+      </c>
+      <c r="P3" s="6">
+        <f>[1]DSSR!O4</f>
+        <v>773</v>
+      </c>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6">
+        <f>[1]DSSR!P4</f>
+        <v>1038</v>
+      </c>
+      <c r="U3" s="6">
+        <f>[1]DSSR!Q4</f>
+        <v>773</v>
+      </c>
+      <c r="V3" s="6">
+        <f>[1]DSSR!R4</f>
+        <v>1038</v>
+      </c>
+      <c r="W3" s="6">
+        <f>[1]DSSR!S4</f>
+        <v>792</v>
+      </c>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6">
+        <f>[1]DSSR!T4</f>
+        <v>948</v>
+      </c>
+    </row>
+    <row r="4" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6">
+        <f>[1]DSSR!B5</f>
+        <v>120</v>
+      </c>
+      <c r="D4" s="6">
+        <f>[1]DSSR!C5</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="6">
+        <f>[1]DSSR!D5</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <f>[1]DSSR!E5</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="6">
+        <f>[1]DSSR!F5</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
+        <f>[1]DSSR!G5</f>
+        <v>120</v>
+      </c>
+      <c r="I4" s="6">
+        <f>[1]DSSR!H5</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <f>[1]DSSR!I5</f>
+        <v>120</v>
+      </c>
+      <c r="K4" s="6">
+        <f>[1]DSSR!J5</f>
+        <v>120</v>
+      </c>
+      <c r="L4" s="6">
+        <f>[1]DSSR!K5</f>
+        <v>111</v>
+      </c>
+      <c r="M4" s="6">
+        <f>[1]DSSR!L5</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="6">
+        <f>[1]DSSR!M5</f>
+        <v>120</v>
+      </c>
+      <c r="O4" s="6">
+        <f>[1]DSSR!N5</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="6">
+        <f>[1]DSSR!O5</f>
+        <v>120</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6">
+        <f>[1]DSSR!P5</f>
+        <v>0</v>
+      </c>
+      <c r="U4" s="6">
+        <f>[1]DSSR!Q5</f>
+        <v>120</v>
+      </c>
+      <c r="V4" s="6">
+        <f>[1]DSSR!R5</f>
+        <v>0</v>
+      </c>
+      <c r="W4" s="6">
+        <f>[1]DSSR!S5</f>
+        <v>120</v>
+      </c>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6">
+        <f>[1]DSSR!T5</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="7">
+        <v>84</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7">
+        <v>84</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7">
+        <v>84</v>
+      </c>
+      <c r="K5" s="7">
+        <v>84</v>
+      </c>
+      <c r="L5" s="7">
+        <v>84</v>
+      </c>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7">
+        <v>84</v>
+      </c>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7">
+        <v>84</v>
+      </c>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7">
+        <v>84</v>
+      </c>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7">
+        <v>84</v>
+      </c>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="L6" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="8"/>
+      <c r="C7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="R7" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="S7" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="T7" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="V7" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y7" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="12"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="14"/>
+      <c r="X8" s="59"/>
+      <c r="Y8" s="15"/>
+    </row>
+    <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="60"/>
+      <c r="Y9" s="20"/>
+    </row>
+    <row r="10" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="60"/>
+      <c r="Y10" s="20"/>
+    </row>
+    <row r="11" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="16"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="60"/>
+      <c r="Y11" s="20"/>
+    </row>
+    <row r="12" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="60"/>
+      <c r="Y12" s="20"/>
+    </row>
+    <row r="13" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="60"/>
+      <c r="Y13" s="20"/>
+    </row>
+    <row r="14" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="16"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="19"/>
+      <c r="V14" s="19"/>
+      <c r="W14" s="19"/>
+      <c r="X14" s="60"/>
+      <c r="Y14" s="20"/>
+    </row>
+    <row r="15" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="T15" s="23"/>
+      <c r="U15" s="23"/>
+      <c r="V15" s="23"/>
+      <c r="W15" s="23"/>
+      <c r="X15" s="61"/>
+      <c r="Y15" s="24"/>
+    </row>
+    <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="57"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28"/>
+      <c r="U16" s="28"/>
+      <c r="V16" s="28"/>
+      <c r="W16" s="56"/>
+      <c r="X16" s="62"/>
+      <c r="Y16" s="29"/>
+    </row>
+    <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="32"/>
+    </row>
+    <row r="18" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="34">
+        <f>[1]DSSR!B24</f>
+        <v>544</v>
+      </c>
+      <c r="D18" s="34">
+        <f>[1]DSSR!C24</f>
+        <v>1127</v>
+      </c>
+      <c r="E18" s="34">
+        <f>[1]DSSR!D24</f>
+        <v>853</v>
+      </c>
+      <c r="F18" s="34">
+        <f>[1]DSSR!E24</f>
+        <v>563</v>
+      </c>
+      <c r="G18" s="34">
+        <f>[1]DSSR!F24</f>
+        <v>575</v>
+      </c>
+      <c r="H18" s="34">
+        <f>[1]DSSR!G24</f>
+        <v>1175</v>
+      </c>
+      <c r="I18" s="34">
+        <f>[1]DSSR!H24</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="34">
+        <f>[1]DSSR!I24</f>
+        <v>791</v>
+      </c>
+      <c r="K18" s="34">
+        <f>[1]DSSR!J24</f>
+        <v>1102</v>
+      </c>
+      <c r="L18" s="34">
+        <f>[1]DSSR!K24</f>
+        <v>520</v>
+      </c>
+      <c r="M18" s="34">
+        <f>[1]DSSR!L24</f>
+        <v>1142</v>
+      </c>
+      <c r="N18" s="34">
+        <f>[1]DSSR!M24</f>
+        <v>205</v>
+      </c>
+      <c r="O18" s="34">
+        <f>[1]DSSR!N24</f>
+        <v>205</v>
+      </c>
+      <c r="P18" s="34">
+        <f>[1]DSSR!O24</f>
+        <v>205</v>
+      </c>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="34"/>
+      <c r="S18" s="34"/>
+      <c r="T18" s="34">
+        <f>[1]DSSR!P24</f>
+        <v>500</v>
+      </c>
+      <c r="U18" s="34">
+        <f>[1]DSSR!Q24</f>
+        <v>650</v>
+      </c>
+      <c r="V18" s="34">
+        <f>[1]DSSR!R24</f>
+        <v>650</v>
+      </c>
+      <c r="W18" s="34">
+        <f>[1]DSSR!S24</f>
+        <v>500</v>
+      </c>
+      <c r="X18" s="34"/>
+      <c r="Y18" s="35">
+        <f>[1]DSSR!T24</f>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="34">
+        <f>[1]DSSR!B25</f>
+        <v>111</v>
+      </c>
+      <c r="D19" s="34">
+        <f>[1]DSSR!C25</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="34">
+        <f>[1]DSSR!D25</f>
+        <v>120</v>
+      </c>
+      <c r="F19" s="34">
+        <f>[1]DSSR!E25</f>
+        <v>111</v>
+      </c>
+      <c r="G19" s="34">
+        <f>[1]DSSR!F25</f>
+        <v>111</v>
+      </c>
+      <c r="H19" s="34">
+        <f>[1]DSSR!G25</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="34">
+        <f>[1]DSSR!H25</f>
+        <v>111</v>
+      </c>
+      <c r="J19" s="34">
+        <f>[1]DSSR!I25</f>
+        <v>120</v>
+      </c>
+      <c r="K19" s="34">
+        <f>[1]DSSR!J25</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="34">
+        <f>[1]DSSR!K25</f>
+        <v>111</v>
+      </c>
+      <c r="M19" s="34">
+        <f>[1]DSSR!L25</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="34">
+        <f>[1]DSSR!M25</f>
+        <v>78</v>
+      </c>
+      <c r="O19" s="34">
+        <f>[1]DSSR!N25</f>
+        <v>78</v>
+      </c>
+      <c r="P19" s="34">
+        <f>[1]DSSR!O25</f>
+        <v>78</v>
+      </c>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+      <c r="S19" s="34"/>
+      <c r="T19" s="34">
+        <f>[1]DSSR!P25</f>
+        <v>120</v>
+      </c>
+      <c r="U19" s="34">
+        <f>[1]DSSR!Q25</f>
+        <v>0</v>
+      </c>
+      <c r="V19" s="34">
+        <f>[1]DSSR!R25</f>
+        <v>0</v>
+      </c>
+      <c r="W19" s="34">
+        <f>[1]DSSR!S25</f>
+        <v>120</v>
+      </c>
+      <c r="X19" s="34"/>
+      <c r="Y19" s="35">
+        <f>[1]DSSR!T25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="34">
+        <v>84</v>
+      </c>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34">
+        <v>84</v>
+      </c>
+      <c r="F20" s="34">
+        <v>84</v>
+      </c>
+      <c r="G20" s="34">
+        <v>84</v>
+      </c>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34">
+        <v>84</v>
+      </c>
+      <c r="J20" s="34">
+        <v>84</v>
+      </c>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34">
+        <v>84</v>
+      </c>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34">
+        <v>42</v>
+      </c>
+      <c r="O20" s="34">
+        <v>42</v>
+      </c>
+      <c r="P20" s="34">
+        <v>42</v>
+      </c>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="34"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="34">
+        <v>84</v>
+      </c>
+      <c r="U20" s="34"/>
+      <c r="V20" s="34"/>
+      <c r="W20" s="34">
+        <v>84</v>
+      </c>
+      <c r="X20" s="34"/>
+      <c r="Y20" s="35"/>
+    </row>
+    <row r="21" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="F21" s="36">
+        <f>4.5/2</f>
+        <v>2.25</v>
+      </c>
+      <c r="G21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="J21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="O21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="P21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+      <c r="S21" s="34"/>
+      <c r="T21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="U21" s="34"/>
+      <c r="V21" s="34"/>
+      <c r="W21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="X21" s="34"/>
+      <c r="Y21" s="35"/>
+    </row>
+    <row r="22" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="33"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="34"/>
+      <c r="S22" s="34"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="34"/>
+      <c r="V22" s="34"/>
+      <c r="W22" s="34"/>
+      <c r="X22" s="34"/>
+      <c r="Y22" s="35"/>
+    </row>
+    <row r="23" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="37"/>
+      <c r="C23" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O23" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P23" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q23" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="R23" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="V23" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="11"/>
+    </row>
+    <row r="24" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="14"/>
+      <c r="Y24" s="15"/>
+    </row>
+    <row r="25" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="17"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="19"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="19"/>
+      <c r="X25" s="60"/>
+      <c r="Y25" s="20"/>
+    </row>
+    <row r="26" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="16"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="19"/>
+      <c r="U26" s="19"/>
+      <c r="V26" s="19"/>
+      <c r="W26" s="19"/>
+      <c r="X26" s="60"/>
+      <c r="Y26" s="20"/>
+    </row>
+    <row r="27" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="16"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="19"/>
+      <c r="U27" s="19"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="19"/>
+      <c r="X27" s="60"/>
+      <c r="Y27" s="20"/>
+    </row>
+    <row r="28" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="16"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="19"/>
+      <c r="X28" s="60"/>
+      <c r="Y28" s="20"/>
+    </row>
+    <row r="29" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="16"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="19"/>
+      <c r="W29" s="19"/>
+      <c r="X29" s="60"/>
+      <c r="Y29" s="20"/>
+    </row>
+    <row r="30" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="16"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="19"/>
+      <c r="U30" s="19"/>
+      <c r="V30" s="19"/>
+      <c r="W30" s="19"/>
+      <c r="X30" s="60"/>
+      <c r="Y30" s="20"/>
+    </row>
+    <row r="31" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
+      <c r="M31" s="23"/>
+      <c r="N31" s="23"/>
+      <c r="O31" s="23"/>
+      <c r="P31" s="23"/>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="23"/>
+      <c r="S31" s="23"/>
+      <c r="T31" s="23"/>
+      <c r="U31" s="23"/>
+      <c r="V31" s="23"/>
+      <c r="W31" s="23"/>
+      <c r="X31" s="61"/>
+      <c r="Y31" s="24"/>
+    </row>
+    <row r="32" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="26"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="23"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="28"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="63"/>
+      <c r="Y32" s="29"/>
+    </row>
+    <row r="33" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="30"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="68"/>
+      <c r="S33" s="68"/>
+      <c r="T33" s="68"/>
+      <c r="U33" s="68"/>
+      <c r="V33" s="31"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="31"/>
+      <c r="Y33" s="31"/>
+    </row>
+    <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="89" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="91" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
+        <v>46</v>
+      </c>
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
+        <v>47</v>
+      </c>
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
+        <v>48</v>
+      </c>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
+      <c r="V34" s="66"/>
+      <c r="W34" s="3"/>
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
+    </row>
+    <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="90"/>
+      <c r="C35" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="G35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="J35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="K35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="L35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="M35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="N35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="O35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="P35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q35" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="R35" s="69"/>
+      <c r="S35" s="70"/>
+      <c r="T35" s="70"/>
+      <c r="U35" s="71"/>
+      <c r="V35" s="83"/>
+      <c r="W35" s="83"/>
+      <c r="X35" s="83"/>
+      <c r="Y35" s="83"/>
+    </row>
+    <row r="36" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="46"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="42"/>
+      <c r="L36" s="42"/>
+      <c r="M36" s="42"/>
+      <c r="N36" s="42"/>
+      <c r="O36" s="42"/>
+      <c r="P36" s="42"/>
+      <c r="Q36" s="43"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="44"/>
+      <c r="T36" s="44"/>
+      <c r="U36" s="83"/>
+      <c r="V36" s="83"/>
+      <c r="W36" s="83"/>
+      <c r="X36" s="83"/>
+      <c r="Y36" s="83"/>
+    </row>
+    <row r="37" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="53"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="48"/>
+      <c r="M37" s="48"/>
+      <c r="N37" s="48"/>
+      <c r="O37" s="48"/>
+      <c r="P37" s="48"/>
+      <c r="Q37" s="64"/>
+      <c r="R37" s="72"/>
+      <c r="S37" s="44"/>
+      <c r="T37" s="44"/>
+      <c r="U37" s="83"/>
+      <c r="V37" s="83"/>
+      <c r="W37" s="83"/>
+      <c r="X37" s="83"/>
+      <c r="Y37" s="83"/>
+    </row>
+    <row r="38" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="53"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="19"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="20"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="44"/>
+      <c r="T38" s="44"/>
+      <c r="U38" s="83"/>
+      <c r="V38" s="83"/>
+      <c r="W38" s="83"/>
+      <c r="X38" s="83"/>
+      <c r="Y38" s="83"/>
+    </row>
+    <row r="39" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="53"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="44"/>
+      <c r="T39" s="44"/>
+      <c r="U39" s="83"/>
+      <c r="V39" s="83"/>
+      <c r="W39" s="83"/>
+      <c r="X39" s="83"/>
+      <c r="Y39" s="83"/>
+    </row>
+    <row r="40" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="53"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="72"/>
+      <c r="S40" s="44"/>
+      <c r="T40" s="44"/>
+      <c r="U40" s="83"/>
+      <c r="V40" s="83"/>
+      <c r="W40" s="83"/>
+      <c r="X40" s="83"/>
+      <c r="Y40" s="83"/>
+    </row>
+    <row r="41" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="54"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="40"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="40"/>
+      <c r="M41" s="40"/>
+      <c r="N41" s="40"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="65"/>
+      <c r="R41" s="73"/>
+      <c r="S41" s="74"/>
+      <c r="T41" s="74"/>
+      <c r="U41" s="75"/>
+      <c r="V41" s="83"/>
+      <c r="W41" s="83"/>
+      <c r="X41" s="83"/>
+      <c r="Y41" s="83"/>
+    </row>
+    <row r="42" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="46"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="42"/>
+      <c r="I42" s="42"/>
+      <c r="J42" s="42"/>
+      <c r="K42" s="42"/>
+      <c r="L42" s="42"/>
+      <c r="M42" s="42"/>
+      <c r="N42" s="42"/>
+      <c r="O42" s="42"/>
+      <c r="P42" s="42"/>
+      <c r="Q42" s="43"/>
+      <c r="R42" s="87" t="s">
+        <v>54</v>
+      </c>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3"/>
+    </row>
+    <row r="43" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="3"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+      <c r="L43" s="44"/>
+      <c r="M43" s="44"/>
+      <c r="N43" s="44"/>
+      <c r="O43" s="44"/>
+      <c r="P43" s="44"/>
+      <c r="Q43" s="44"/>
+      <c r="R43" s="44"/>
+      <c r="S43" s="44"/>
+      <c r="T43" s="44"/>
+      <c r="U43" s="83"/>
+      <c r="V43" s="83"/>
+      <c r="W43" s="83"/>
+      <c r="X43" s="83"/>
+      <c r="Y43" s="83"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="R34:U34"/>
+    <mergeCell ref="R42:U42"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="O34:Q34"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="83" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{216FD856-BECA-480C-B79F-E5B76AC35593}">
+  <dimension ref="B1:AA45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
+    <col min="3" max="5" width="5.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.140625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.140625" style="2" customWidth="1"/>
+    <col min="20" max="21" width="5.7109375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="29" width="5.7109375" style="2" customWidth="1"/>
+    <col min="30" max="16384" width="8.7109375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="3"/>
+    </row>
+    <row r="2" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6">
+        <f>[1]DSSR!B4</f>
+        <v>1300</v>
+      </c>
+      <c r="D3" s="6">
+        <f>[1]DSSR!C4</f>
+        <v>1534</v>
+      </c>
+      <c r="E3" s="6">
+        <f>[1]DSSR!D4</f>
+        <v>1728</v>
+      </c>
+      <c r="F3" s="6">
+        <f>[1]DSSR!E4</f>
+        <v>1728</v>
+      </c>
+      <c r="G3" s="6">
+        <f>[1]DSSR!F4</f>
+        <v>1452</v>
+      </c>
+      <c r="H3" s="6">
+        <f>[1]DSSR!G4</f>
+        <v>1240</v>
+      </c>
+      <c r="I3" s="6">
+        <f>[1]DSSR!H4</f>
+        <v>1520</v>
+      </c>
+      <c r="J3" s="6">
+        <f>[1]DSSR!I4</f>
+        <v>978</v>
+      </c>
+      <c r="K3" s="6">
+        <f>[1]DSSR!J4</f>
+        <v>945</v>
+      </c>
+      <c r="L3" s="6">
+        <f>[1]DSSR!K4</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="6">
+        <f>[1]DSSR!L4</f>
+        <v>1127</v>
+      </c>
+      <c r="N3" s="6">
+        <f>[1]DSSR!M4</f>
+        <v>773</v>
+      </c>
+      <c r="O3" s="6">
+        <f>[1]DSSR!N4</f>
+        <v>1038</v>
+      </c>
+      <c r="P3" s="6">
+        <f>[1]DSSR!O4</f>
+        <v>773</v>
+      </c>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6">
+        <f>[1]DSSR!P4</f>
+        <v>1038</v>
+      </c>
+      <c r="U3" s="6">
+        <f>[1]DSSR!Q4</f>
+        <v>773</v>
+      </c>
+      <c r="V3" s="6">
+        <f>[1]DSSR!R4</f>
+        <v>1038</v>
+      </c>
+      <c r="W3" s="6">
+        <f>[1]DSSR!S4</f>
+        <v>792</v>
+      </c>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6">
+        <f>[1]DSSR!T4</f>
+        <v>948</v>
+      </c>
+    </row>
+    <row r="4" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6">
+        <f>[1]DSSR!B5</f>
+        <v>120</v>
+      </c>
+      <c r="D4" s="6">
+        <f>[1]DSSR!C5</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="6">
+        <f>[1]DSSR!D5</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <f>[1]DSSR!E5</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="6">
+        <f>[1]DSSR!F5</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
+        <f>[1]DSSR!G5</f>
+        <v>120</v>
+      </c>
+      <c r="I4" s="6">
+        <f>[1]DSSR!H5</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <f>[1]DSSR!I5</f>
+        <v>120</v>
+      </c>
+      <c r="K4" s="6">
+        <f>[1]DSSR!J5</f>
+        <v>120</v>
+      </c>
+      <c r="L4" s="6">
+        <f>[1]DSSR!K5</f>
+        <v>111</v>
+      </c>
+      <c r="M4" s="6">
+        <f>[1]DSSR!L5</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="6">
+        <f>[1]DSSR!M5</f>
+        <v>120</v>
+      </c>
+      <c r="O4" s="6">
+        <f>[1]DSSR!N5</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="6">
+        <f>[1]DSSR!O5</f>
+        <v>120</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6">
+        <f>[1]DSSR!P5</f>
+        <v>0</v>
+      </c>
+      <c r="U4" s="6">
+        <f>[1]DSSR!Q5</f>
+        <v>120</v>
+      </c>
+      <c r="V4" s="6">
+        <f>[1]DSSR!R5</f>
+        <v>0</v>
+      </c>
+      <c r="W4" s="6">
+        <f>[1]DSSR!S5</f>
+        <v>120</v>
+      </c>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6">
+        <f>[1]DSSR!T5</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="7">
+        <v>84</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7">
+        <v>84</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7">
+        <v>84</v>
+      </c>
+      <c r="K5" s="7">
+        <v>84</v>
+      </c>
+      <c r="L5" s="7">
+        <v>84</v>
+      </c>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7">
+        <v>84</v>
+      </c>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7">
+        <v>84</v>
+      </c>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7">
+        <v>84</v>
+      </c>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7">
+        <v>84</v>
+      </c>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="L6" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="R7" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="S7" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="T7" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="V7" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y7" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="12"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14">
+        <v>1</v>
+      </c>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14">
+        <v>10</v>
+      </c>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14">
+        <v>1</v>
+      </c>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="14"/>
+      <c r="X8" s="59">
+        <v>2</v>
+      </c>
+      <c r="Y8" s="15"/>
+    </row>
+    <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="60"/>
+      <c r="Y9" s="20"/>
+    </row>
+    <row r="10" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="60"/>
+      <c r="Y10" s="20"/>
+    </row>
+    <row r="11" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="16"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="60"/>
+      <c r="Y11" s="20"/>
+    </row>
+    <row r="12" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="60"/>
+      <c r="Y12" s="20"/>
+    </row>
+    <row r="13" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="60"/>
+      <c r="Y13" s="20"/>
+    </row>
+    <row r="14" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="16"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="19"/>
+      <c r="V14" s="19"/>
+      <c r="W14" s="19"/>
+      <c r="X14" s="60"/>
+      <c r="Y14" s="20"/>
+    </row>
+    <row r="15" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23">
+        <v>1</v>
+      </c>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="T15" s="23">
+        <v>1</v>
+      </c>
+      <c r="U15" s="23"/>
+      <c r="V15" s="23"/>
+      <c r="W15" s="23"/>
+      <c r="X15" s="61">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="24"/>
+    </row>
+    <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="57"/>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
+      <c r="U16" s="28"/>
+      <c r="V16" s="28"/>
+      <c r="W16" s="56"/>
+      <c r="X16" s="62">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="29"/>
+    </row>
+    <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="32"/>
+    </row>
+    <row r="18" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="34">
+        <f>[1]DSSR!B24</f>
+        <v>544</v>
+      </c>
+      <c r="D18" s="34">
+        <f>[1]DSSR!C24</f>
+        <v>1127</v>
+      </c>
+      <c r="E18" s="34">
+        <f>[1]DSSR!D24</f>
+        <v>853</v>
+      </c>
+      <c r="F18" s="34">
+        <f>[1]DSSR!E24</f>
+        <v>563</v>
+      </c>
+      <c r="G18" s="34">
+        <f>[1]DSSR!F24</f>
+        <v>575</v>
+      </c>
+      <c r="H18" s="34">
+        <f>[1]DSSR!G24</f>
+        <v>1175</v>
+      </c>
+      <c r="I18" s="34">
+        <f>[1]DSSR!H24</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="34">
+        <f>[1]DSSR!I24</f>
+        <v>791</v>
+      </c>
+      <c r="K18" s="34">
+        <f>[1]DSSR!J24</f>
+        <v>1102</v>
+      </c>
+      <c r="L18" s="34">
+        <f>[1]DSSR!K24</f>
+        <v>520</v>
+      </c>
+      <c r="M18" s="34">
+        <f>[1]DSSR!L24</f>
+        <v>1142</v>
+      </c>
+      <c r="N18" s="34">
+        <f>[1]DSSR!M24</f>
+        <v>205</v>
+      </c>
+      <c r="O18" s="34">
+        <f>[1]DSSR!N24</f>
+        <v>205</v>
+      </c>
+      <c r="P18" s="34">
+        <f>[1]DSSR!O24</f>
+        <v>205</v>
+      </c>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="34"/>
+      <c r="S18" s="34"/>
+      <c r="T18" s="34">
+        <f>[1]DSSR!P24</f>
+        <v>500</v>
+      </c>
+      <c r="U18" s="34">
+        <f>[1]DSSR!Q24</f>
+        <v>650</v>
+      </c>
+      <c r="V18" s="34">
+        <f>[1]DSSR!R24</f>
+        <v>650</v>
+      </c>
+      <c r="W18" s="34">
+        <f>[1]DSSR!S24</f>
+        <v>500</v>
+      </c>
+      <c r="X18" s="34"/>
+      <c r="Y18" s="35">
+        <f>[1]DSSR!T24</f>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="34">
+        <f>[1]DSSR!B25</f>
+        <v>111</v>
+      </c>
+      <c r="D19" s="34">
+        <f>[1]DSSR!C25</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="34">
+        <f>[1]DSSR!D25</f>
+        <v>120</v>
+      </c>
+      <c r="F19" s="34">
+        <f>[1]DSSR!E25</f>
+        <v>111</v>
+      </c>
+      <c r="G19" s="34">
+        <f>[1]DSSR!F25</f>
+        <v>111</v>
+      </c>
+      <c r="H19" s="34">
+        <f>[1]DSSR!G25</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="34">
+        <f>[1]DSSR!H25</f>
+        <v>111</v>
+      </c>
+      <c r="J19" s="34">
+        <f>[1]DSSR!I25</f>
+        <v>120</v>
+      </c>
+      <c r="K19" s="34">
+        <f>[1]DSSR!J25</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="34">
+        <f>[1]DSSR!K25</f>
+        <v>111</v>
+      </c>
+      <c r="M19" s="34">
+        <f>[1]DSSR!L25</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="34">
+        <f>[1]DSSR!M25</f>
+        <v>78</v>
+      </c>
+      <c r="O19" s="34">
+        <f>[1]DSSR!N25</f>
+        <v>78</v>
+      </c>
+      <c r="P19" s="34">
+        <f>[1]DSSR!O25</f>
+        <v>78</v>
+      </c>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+      <c r="S19" s="34"/>
+      <c r="T19" s="34">
+        <f>[1]DSSR!P25</f>
+        <v>120</v>
+      </c>
+      <c r="U19" s="34">
+        <f>[1]DSSR!Q25</f>
+        <v>0</v>
+      </c>
+      <c r="V19" s="34">
+        <f>[1]DSSR!R25</f>
+        <v>0</v>
+      </c>
+      <c r="W19" s="34">
+        <f>[1]DSSR!S25</f>
+        <v>120</v>
+      </c>
+      <c r="X19" s="34"/>
+      <c r="Y19" s="35">
+        <f>[1]DSSR!T25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="34">
+        <v>84</v>
+      </c>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34">
+        <v>84</v>
+      </c>
+      <c r="F20" s="34">
+        <v>84</v>
+      </c>
+      <c r="G20" s="34">
+        <v>84</v>
+      </c>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34">
+        <v>84</v>
+      </c>
+      <c r="J20" s="34">
+        <v>84</v>
+      </c>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34">
+        <v>84</v>
+      </c>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34">
+        <v>42</v>
+      </c>
+      <c r="O20" s="34">
+        <v>42</v>
+      </c>
+      <c r="P20" s="34">
+        <v>42</v>
+      </c>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="34"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="34">
+        <v>84</v>
+      </c>
+      <c r="U20" s="34"/>
+      <c r="V20" s="34"/>
+      <c r="W20" s="34">
+        <v>84</v>
+      </c>
+      <c r="X20" s="34"/>
+      <c r="Y20" s="35"/>
+    </row>
+    <row r="21" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="F21" s="36">
+        <f>4.5/2</f>
+        <v>2.25</v>
+      </c>
+      <c r="G21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="J21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="O21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="P21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+      <c r="S21" s="34"/>
+      <c r="T21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="U21" s="34"/>
+      <c r="V21" s="34"/>
+      <c r="W21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="X21" s="34"/>
+      <c r="Y21" s="35"/>
+    </row>
+    <row r="22" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="33"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="34"/>
+      <c r="S22" s="34"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="34"/>
+      <c r="V22" s="34"/>
+      <c r="W22" s="34"/>
+      <c r="X22" s="34"/>
+      <c r="Y22" s="35"/>
+    </row>
+    <row r="23" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="37"/>
+      <c r="C23" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O23" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P23" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q23" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="R23" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="V23" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="11"/>
+    </row>
+    <row r="24" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14">
+        <v>5</v>
+      </c>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14">
+        <v>20</v>
+      </c>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14">
+        <v>45</v>
+      </c>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14">
+        <v>333</v>
+      </c>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="14"/>
+      <c r="Y24" s="15"/>
+    </row>
+    <row r="25" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="17"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="19"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="19"/>
+      <c r="X25" s="60"/>
+      <c r="Y25" s="20"/>
+    </row>
+    <row r="26" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="16"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="19"/>
+      <c r="U26" s="19"/>
+      <c r="V26" s="19"/>
+      <c r="W26" s="19"/>
+      <c r="X26" s="60"/>
+      <c r="Y26" s="20"/>
+    </row>
+    <row r="27" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="16"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="19"/>
+      <c r="U27" s="19"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="19"/>
+      <c r="X27" s="60"/>
+      <c r="Y27" s="20"/>
+    </row>
+    <row r="28" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="16"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="19"/>
+      <c r="X28" s="60"/>
+      <c r="Y28" s="20"/>
+    </row>
+    <row r="29" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="16"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="19"/>
+      <c r="W29" s="19"/>
+      <c r="X29" s="60"/>
+      <c r="Y29" s="20"/>
+    </row>
+    <row r="30" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="16"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="19"/>
+      <c r="U30" s="19"/>
+      <c r="V30" s="19"/>
+      <c r="W30" s="19"/>
+      <c r="X30" s="60"/>
+      <c r="Y30" s="20"/>
+    </row>
+    <row r="31" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23">
+        <v>0</v>
+      </c>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23">
+        <v>0</v>
+      </c>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="23">
+        <v>0</v>
+      </c>
+      <c r="L31" s="23"/>
+      <c r="M31" s="23">
+        <v>44</v>
+      </c>
+      <c r="N31" s="23"/>
+      <c r="O31" s="23"/>
+      <c r="P31" s="23"/>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="23"/>
+      <c r="S31" s="23"/>
+      <c r="T31" s="23"/>
+      <c r="U31" s="23"/>
+      <c r="V31" s="23"/>
+      <c r="W31" s="23"/>
+      <c r="X31" s="61"/>
+      <c r="Y31" s="24"/>
+    </row>
+    <row r="32" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="26"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27">
+        <v>5</v>
+      </c>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28">
+        <v>20</v>
+      </c>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28">
+        <v>45</v>
+      </c>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28">
+        <v>289</v>
+      </c>
+      <c r="N32" s="28"/>
+      <c r="O32" s="23"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="28"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="63"/>
+      <c r="Y32" s="29"/>
+    </row>
+    <row r="33" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="30"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="68"/>
+      <c r="S33" s="68"/>
+      <c r="T33" s="68"/>
+      <c r="U33" s="68"/>
+      <c r="V33" s="31"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="31"/>
+      <c r="Y33" s="31"/>
+    </row>
+    <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="89" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="91" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
+        <v>46</v>
+      </c>
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
+        <v>47</v>
+      </c>
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
+        <v>48</v>
+      </c>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
+      <c r="V34" s="66"/>
+      <c r="W34" s="3"/>
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
+    </row>
+    <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="90"/>
+      <c r="C35" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="G35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="J35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="K35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="L35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="M35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="N35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="O35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="P35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q35" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="R35" s="69"/>
+      <c r="S35" s="70"/>
+      <c r="T35" s="70"/>
+      <c r="U35" s="71"/>
+      <c r="V35" s="83"/>
+      <c r="W35" s="83"/>
+      <c r="X35" s="83"/>
+      <c r="Y35" s="83"/>
+    </row>
+    <row r="36" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="46"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42">
+        <v>307</v>
+      </c>
+      <c r="G36" s="42">
+        <v>6</v>
+      </c>
+      <c r="H36" s="42">
+        <v>3</v>
+      </c>
+      <c r="I36" s="42">
+        <v>6</v>
+      </c>
+      <c r="J36" s="42">
+        <v>1</v>
+      </c>
+      <c r="K36" s="42"/>
+      <c r="L36" s="42">
+        <v>50</v>
+      </c>
+      <c r="M36" s="42">
+        <v>1</v>
+      </c>
+      <c r="N36" s="42"/>
+      <c r="O36" s="42"/>
+      <c r="P36" s="42"/>
+      <c r="Q36" s="43">
+        <v>4</v>
+      </c>
+      <c r="R36" s="72"/>
+      <c r="S36" s="44"/>
+      <c r="T36" s="44"/>
+      <c r="U36" s="83"/>
+      <c r="V36" s="83"/>
+      <c r="W36" s="83"/>
+      <c r="X36" s="83"/>
+      <c r="Y36" s="83"/>
+    </row>
+    <row r="37" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="53"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="48"/>
+      <c r="M37" s="48"/>
+      <c r="N37" s="48"/>
+      <c r="O37" s="48"/>
+      <c r="P37" s="48"/>
+      <c r="Q37" s="64"/>
+      <c r="R37" s="72"/>
+      <c r="S37" s="44"/>
+      <c r="T37" s="44"/>
+      <c r="U37" s="83"/>
+      <c r="V37" s="83"/>
+      <c r="W37" s="83"/>
+      <c r="X37" s="83"/>
+      <c r="Y37" s="83"/>
+    </row>
+    <row r="38" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="53"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="19"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="20"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="44"/>
+      <c r="T38" s="44"/>
+      <c r="U38" s="83"/>
+      <c r="V38" s="83"/>
+      <c r="W38" s="83"/>
+      <c r="X38" s="83"/>
+      <c r="Y38" s="83"/>
+    </row>
+    <row r="39" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="53"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="44"/>
+      <c r="T39" s="44"/>
+      <c r="U39" s="83"/>
+      <c r="V39" s="83"/>
+      <c r="W39" s="83"/>
+      <c r="X39" s="83"/>
+      <c r="Y39" s="83"/>
+    </row>
+    <row r="40" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="53"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="72"/>
+      <c r="S40" s="44"/>
+      <c r="T40" s="44"/>
+      <c r="U40" s="83"/>
+      <c r="V40" s="83"/>
+      <c r="W40" s="83"/>
+      <c r="X40" s="83"/>
+      <c r="Y40" s="83"/>
+    </row>
+    <row r="41" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="54"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="40"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="40"/>
+      <c r="M41" s="40"/>
+      <c r="N41" s="40"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="65"/>
+      <c r="R41" s="73"/>
+      <c r="S41" s="74"/>
+      <c r="T41" s="74"/>
+      <c r="U41" s="75"/>
+      <c r="V41" s="83"/>
+      <c r="W41" s="83"/>
+      <c r="X41" s="83"/>
+      <c r="Y41" s="83"/>
+    </row>
+    <row r="42" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="46"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42">
+        <v>307</v>
+      </c>
+      <c r="G42" s="42">
+        <v>6</v>
+      </c>
+      <c r="H42" s="42">
+        <v>3</v>
+      </c>
+      <c r="I42" s="42">
+        <v>6</v>
+      </c>
+      <c r="J42" s="42">
+        <v>1</v>
+      </c>
+      <c r="K42" s="42"/>
+      <c r="L42" s="42">
+        <v>50</v>
+      </c>
+      <c r="M42" s="42">
+        <v>1</v>
+      </c>
+      <c r="N42" s="42"/>
+      <c r="O42" s="42"/>
+      <c r="P42" s="42"/>
+      <c r="Q42" s="43">
+        <v>4</v>
+      </c>
+      <c r="R42" s="87" t="s">
+        <v>54</v>
+      </c>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3"/>
+    </row>
+    <row r="43" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="3"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+      <c r="L43" s="44"/>
+      <c r="M43" s="44"/>
+      <c r="N43" s="44"/>
+      <c r="O43" s="44"/>
+      <c r="P43" s="44"/>
+      <c r="Q43" s="44"/>
+      <c r="R43" s="44"/>
+      <c r="S43" s="44"/>
+      <c r="T43" s="44"/>
+      <c r="U43" s="83"/>
+      <c r="V43" s="83"/>
+      <c r="W43" s="83"/>
+      <c r="X43" s="83"/>
+      <c r="Y43" s="83"/>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B44" s="76" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" s="95">
+        <f>5+20+45+289</f>
+        <v>359</v>
+      </c>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B45" s="76" t="s">
+        <v>69</v>
+      </c>
+      <c r="C45" s="95">
+        <v>12</v>
+      </c>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="R34:U34"/>
+    <mergeCell ref="R42:U42"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="O34:Q34"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="83" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4B5CDE8-EEFC-462B-A039-DBF94D3E1AFB}">
+  <dimension ref="B1:AA45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.140625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.140625" style="2" customWidth="1"/>
+    <col min="20" max="21" width="5.7109375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="29" width="5.7109375" style="2" customWidth="1"/>
+    <col min="30" max="16384" width="8.7109375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="3"/>
+    </row>
+    <row r="2" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6">
+        <f>[1]DSSR!B4</f>
+        <v>1300</v>
+      </c>
+      <c r="D3" s="6">
+        <f>[1]DSSR!C4</f>
+        <v>1534</v>
+      </c>
+      <c r="E3" s="6">
+        <f>[1]DSSR!D4</f>
+        <v>1728</v>
+      </c>
+      <c r="F3" s="6">
+        <f>[1]DSSR!E4</f>
+        <v>1728</v>
+      </c>
+      <c r="G3" s="6">
+        <f>[1]DSSR!F4</f>
+        <v>1452</v>
+      </c>
+      <c r="H3" s="6">
+        <f>[1]DSSR!G4</f>
+        <v>1240</v>
+      </c>
+      <c r="I3" s="6">
+        <f>[1]DSSR!H4</f>
+        <v>1520</v>
+      </c>
+      <c r="J3" s="6">
+        <f>[1]DSSR!I4</f>
+        <v>978</v>
+      </c>
+      <c r="K3" s="6">
+        <f>[1]DSSR!J4</f>
+        <v>945</v>
+      </c>
+      <c r="L3" s="6">
+        <f>[1]DSSR!K4</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="6">
+        <f>[1]DSSR!L4</f>
+        <v>1127</v>
+      </c>
+      <c r="N3" s="6">
+        <f>[1]DSSR!M4</f>
+        <v>773</v>
+      </c>
+      <c r="O3" s="6">
+        <f>[1]DSSR!N4</f>
+        <v>1038</v>
+      </c>
+      <c r="P3" s="6">
+        <f>[1]DSSR!O4</f>
+        <v>773</v>
+      </c>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6">
+        <f>[1]DSSR!P4</f>
+        <v>1038</v>
+      </c>
+      <c r="U3" s="6">
+        <f>[1]DSSR!Q4</f>
+        <v>773</v>
+      </c>
+      <c r="V3" s="6">
+        <f>[1]DSSR!R4</f>
+        <v>1038</v>
+      </c>
+      <c r="W3" s="6">
+        <f>[1]DSSR!S4</f>
+        <v>792</v>
+      </c>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6">
+        <f>[1]DSSR!T4</f>
+        <v>948</v>
+      </c>
+    </row>
+    <row r="4" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6">
+        <f>[1]DSSR!B5</f>
+        <v>120</v>
+      </c>
+      <c r="D4" s="6">
+        <f>[1]DSSR!C5</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="6">
+        <f>[1]DSSR!D5</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <f>[1]DSSR!E5</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="6">
+        <f>[1]DSSR!F5</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
+        <f>[1]DSSR!G5</f>
+        <v>120</v>
+      </c>
+      <c r="I4" s="6">
+        <f>[1]DSSR!H5</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <f>[1]DSSR!I5</f>
+        <v>120</v>
+      </c>
+      <c r="K4" s="6">
+        <f>[1]DSSR!J5</f>
+        <v>120</v>
+      </c>
+      <c r="L4" s="6">
+        <f>[1]DSSR!K5</f>
+        <v>111</v>
+      </c>
+      <c r="M4" s="6">
+        <f>[1]DSSR!L5</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="6">
+        <f>[1]DSSR!M5</f>
+        <v>120</v>
+      </c>
+      <c r="O4" s="6">
+        <f>[1]DSSR!N5</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="6">
+        <f>[1]DSSR!O5</f>
+        <v>120</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6">
+        <f>[1]DSSR!P5</f>
+        <v>0</v>
+      </c>
+      <c r="U4" s="6">
+        <f>[1]DSSR!Q5</f>
+        <v>120</v>
+      </c>
+      <c r="V4" s="6">
+        <f>[1]DSSR!R5</f>
+        <v>0</v>
+      </c>
+      <c r="W4" s="6">
+        <f>[1]DSSR!S5</f>
+        <v>120</v>
+      </c>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6">
+        <f>[1]DSSR!T5</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="7">
+        <v>84</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7">
+        <v>84</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7">
+        <v>84</v>
+      </c>
+      <c r="K5" s="7">
+        <v>84</v>
+      </c>
+      <c r="L5" s="7">
+        <v>84</v>
+      </c>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7">
+        <v>84</v>
+      </c>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7">
+        <v>84</v>
+      </c>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7">
+        <v>84</v>
+      </c>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7">
+        <v>84</v>
+      </c>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="L6" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="R7" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="S7" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="T7" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="V7" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y7" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="12"/>
+      <c r="C8" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14">
+        <v>2</v>
+      </c>
+      <c r="F8" s="14">
+        <v>2</v>
+      </c>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14">
+        <v>13</v>
+      </c>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14">
+        <v>1</v>
+      </c>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="14">
+        <v>3</v>
+      </c>
+      <c r="X8" s="59"/>
+      <c r="Y8" s="15"/>
+    </row>
+    <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="60"/>
+      <c r="Y9" s="20"/>
+    </row>
+    <row r="10" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="60"/>
+      <c r="Y10" s="20"/>
+    </row>
+    <row r="11" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="16"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="60"/>
+      <c r="Y11" s="20"/>
+    </row>
+    <row r="12" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="60"/>
+      <c r="Y12" s="20"/>
+    </row>
+    <row r="13" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="60"/>
+      <c r="Y13" s="20"/>
+    </row>
+    <row r="14" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="16"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="19"/>
+      <c r="V14" s="19"/>
+      <c r="W14" s="19"/>
+      <c r="X14" s="60"/>
+      <c r="Y14" s="20"/>
+    </row>
+    <row r="15" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23">
+        <v>2</v>
+      </c>
+      <c r="F15" s="23">
+        <v>2</v>
+      </c>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23">
+        <v>5</v>
+      </c>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="T15" s="23">
+        <v>1</v>
+      </c>
+      <c r="U15" s="23"/>
+      <c r="V15" s="23"/>
+      <c r="W15" s="23">
+        <v>2</v>
+      </c>
+      <c r="X15" s="61"/>
+      <c r="Y15" s="24"/>
+    </row>
+    <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+      <c r="D16" s="58"/>
+      <c r="E16" s="27">
+        <v>0</v>
+      </c>
+      <c r="F16" s="27">
+        <v>0</v>
+      </c>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28">
+        <v>8</v>
+      </c>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
+      <c r="U16" s="28"/>
+      <c r="V16" s="28"/>
+      <c r="W16" s="56">
+        <v>1</v>
+      </c>
+      <c r="X16" s="62"/>
+      <c r="Y16" s="29"/>
+    </row>
+    <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="32"/>
+    </row>
+    <row r="18" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="34">
+        <f>[1]DSSR!B24</f>
+        <v>544</v>
+      </c>
+      <c r="D18" s="34">
+        <f>[1]DSSR!C24</f>
+        <v>1127</v>
+      </c>
+      <c r="E18" s="34">
+        <f>[1]DSSR!D24</f>
+        <v>853</v>
+      </c>
+      <c r="F18" s="34">
+        <f>[1]DSSR!E24</f>
+        <v>563</v>
+      </c>
+      <c r="G18" s="34">
+        <f>[1]DSSR!F24</f>
+        <v>575</v>
+      </c>
+      <c r="H18" s="34">
+        <f>[1]DSSR!G24</f>
+        <v>1175</v>
+      </c>
+      <c r="I18" s="34">
+        <f>[1]DSSR!H24</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="34">
+        <f>[1]DSSR!I24</f>
+        <v>791</v>
+      </c>
+      <c r="K18" s="34">
+        <f>[1]DSSR!J24</f>
+        <v>1102</v>
+      </c>
+      <c r="L18" s="34">
+        <f>[1]DSSR!K24</f>
+        <v>520</v>
+      </c>
+      <c r="M18" s="34">
+        <f>[1]DSSR!L24</f>
+        <v>1142</v>
+      </c>
+      <c r="N18" s="34">
+        <f>[1]DSSR!M24</f>
+        <v>205</v>
+      </c>
+      <c r="O18" s="34">
+        <f>[1]DSSR!N24</f>
+        <v>205</v>
+      </c>
+      <c r="P18" s="34">
+        <f>[1]DSSR!O24</f>
+        <v>205</v>
+      </c>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="34"/>
+      <c r="S18" s="34"/>
+      <c r="T18" s="34">
+        <f>[1]DSSR!P24</f>
+        <v>500</v>
+      </c>
+      <c r="U18" s="34">
+        <f>[1]DSSR!Q24</f>
+        <v>650</v>
+      </c>
+      <c r="V18" s="34">
+        <f>[1]DSSR!R24</f>
+        <v>650</v>
+      </c>
+      <c r="W18" s="34">
+        <f>[1]DSSR!S24</f>
+        <v>500</v>
+      </c>
+      <c r="X18" s="34"/>
+      <c r="Y18" s="35">
+        <f>[1]DSSR!T24</f>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="34">
+        <f>[1]DSSR!B25</f>
+        <v>111</v>
+      </c>
+      <c r="D19" s="34">
+        <f>[1]DSSR!C25</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="34">
+        <f>[1]DSSR!D25</f>
+        <v>120</v>
+      </c>
+      <c r="F19" s="34">
+        <f>[1]DSSR!E25</f>
+        <v>111</v>
+      </c>
+      <c r="G19" s="34">
+        <f>[1]DSSR!F25</f>
+        <v>111</v>
+      </c>
+      <c r="H19" s="34">
+        <f>[1]DSSR!G25</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="34">
+        <f>[1]DSSR!H25</f>
+        <v>111</v>
+      </c>
+      <c r="J19" s="34">
+        <f>[1]DSSR!I25</f>
+        <v>120</v>
+      </c>
+      <c r="K19" s="34">
+        <f>[1]DSSR!J25</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="34">
+        <f>[1]DSSR!K25</f>
+        <v>111</v>
+      </c>
+      <c r="M19" s="34">
+        <f>[1]DSSR!L25</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="34">
+        <f>[1]DSSR!M25</f>
+        <v>78</v>
+      </c>
+      <c r="O19" s="34">
+        <f>[1]DSSR!N25</f>
+        <v>78</v>
+      </c>
+      <c r="P19" s="34">
+        <f>[1]DSSR!O25</f>
+        <v>78</v>
+      </c>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+      <c r="S19" s="34"/>
+      <c r="T19" s="34">
+        <f>[1]DSSR!P25</f>
+        <v>120</v>
+      </c>
+      <c r="U19" s="34">
+        <f>[1]DSSR!Q25</f>
+        <v>0</v>
+      </c>
+      <c r="V19" s="34">
+        <f>[1]DSSR!R25</f>
+        <v>0</v>
+      </c>
+      <c r="W19" s="34">
+        <f>[1]DSSR!S25</f>
+        <v>120</v>
+      </c>
+      <c r="X19" s="34"/>
+      <c r="Y19" s="35">
+        <f>[1]DSSR!T25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="34">
+        <v>84</v>
+      </c>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34">
+        <v>84</v>
+      </c>
+      <c r="F20" s="34">
+        <v>84</v>
+      </c>
+      <c r="G20" s="34">
+        <v>84</v>
+      </c>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34">
+        <v>84</v>
+      </c>
+      <c r="J20" s="34">
+        <v>84</v>
+      </c>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34">
+        <v>84</v>
+      </c>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34">
+        <v>42</v>
+      </c>
+      <c r="O20" s="34">
+        <v>42</v>
+      </c>
+      <c r="P20" s="34">
+        <v>42</v>
+      </c>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="34"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="34">
+        <v>84</v>
+      </c>
+      <c r="U20" s="34"/>
+      <c r="V20" s="34"/>
+      <c r="W20" s="34">
+        <v>84</v>
+      </c>
+      <c r="X20" s="34"/>
+      <c r="Y20" s="35"/>
+    </row>
+    <row r="21" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="F21" s="36">
+        <f>4.5/2</f>
+        <v>2.25</v>
+      </c>
+      <c r="G21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="J21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="O21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="P21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+      <c r="S21" s="34"/>
+      <c r="T21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="U21" s="34"/>
+      <c r="V21" s="34"/>
+      <c r="W21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="X21" s="34"/>
+      <c r="Y21" s="35"/>
+    </row>
+    <row r="22" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="33"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="34"/>
+      <c r="S22" s="34"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="34"/>
+      <c r="V22" s="34"/>
+      <c r="W22" s="34"/>
+      <c r="X22" s="34"/>
+      <c r="Y22" s="35"/>
+    </row>
+    <row r="23" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="37"/>
+      <c r="C23" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O23" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P23" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q23" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="R23" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="V23" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="11"/>
+    </row>
+    <row r="24" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="79" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14">
+        <v>38</v>
+      </c>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14">
+        <v>406</v>
+      </c>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14">
+        <v>1</v>
+      </c>
+      <c r="P24" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="14"/>
+      <c r="Y24" s="15"/>
+    </row>
+    <row r="25" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="17"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="19"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="19"/>
+      <c r="X25" s="60"/>
+      <c r="Y25" s="20"/>
+    </row>
+    <row r="26" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="16"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="19"/>
+      <c r="U26" s="19"/>
+      <c r="V26" s="19"/>
+      <c r="W26" s="19"/>
+      <c r="X26" s="60"/>
+      <c r="Y26" s="20"/>
+    </row>
+    <row r="27" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="16"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="19"/>
+      <c r="U27" s="19"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="19"/>
+      <c r="X27" s="60"/>
+      <c r="Y27" s="20"/>
+    </row>
+    <row r="28" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="16"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="19"/>
+      <c r="X28" s="60"/>
+      <c r="Y28" s="20"/>
+    </row>
+    <row r="29" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="16"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="19"/>
+      <c r="W29" s="19"/>
+      <c r="X29" s="60"/>
+      <c r="Y29" s="20"/>
+    </row>
+    <row r="30" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="16"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="19"/>
+      <c r="U30" s="19"/>
+      <c r="V30" s="19"/>
+      <c r="W30" s="19"/>
+      <c r="X30" s="60"/>
+      <c r="Y30" s="20"/>
+    </row>
+    <row r="31" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23">
+        <v>12</v>
+      </c>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="23">
+        <v>1</v>
+      </c>
+      <c r="L31" s="23"/>
+      <c r="M31" s="23">
+        <v>152</v>
+      </c>
+      <c r="N31" s="23"/>
+      <c r="O31" s="23">
+        <v>1</v>
+      </c>
+      <c r="P31" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="23"/>
+      <c r="S31" s="23"/>
+      <c r="T31" s="23"/>
+      <c r="U31" s="23"/>
+      <c r="V31" s="23"/>
+      <c r="W31" s="23"/>
+      <c r="X31" s="61"/>
+      <c r="Y31" s="24"/>
+    </row>
+    <row r="32" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="26"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27">
+        <v>1</v>
+      </c>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28">
+        <v>26</v>
+      </c>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28">
+        <v>1</v>
+      </c>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28">
+        <v>254</v>
+      </c>
+      <c r="N32" s="28"/>
+      <c r="O32" s="23">
+        <v>0</v>
+      </c>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="28"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="63"/>
+      <c r="Y32" s="29"/>
+    </row>
+    <row r="33" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="30"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="68"/>
+      <c r="S33" s="68"/>
+      <c r="T33" s="68"/>
+      <c r="U33" s="68"/>
+      <c r="V33" s="31"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="31"/>
+      <c r="Y33" s="31"/>
+    </row>
+    <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="89" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="91" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
+        <v>46</v>
+      </c>
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
+        <v>47</v>
+      </c>
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
+        <v>48</v>
+      </c>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
+      <c r="V34" s="66"/>
+      <c r="W34" s="3"/>
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
+    </row>
+    <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="90"/>
+      <c r="C35" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="G35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="J35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="K35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="L35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="M35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="N35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="O35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="P35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q35" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="R35" s="69"/>
+      <c r="S35" s="70"/>
+      <c r="T35" s="70"/>
+      <c r="U35" s="71"/>
+      <c r="V35" s="83"/>
+      <c r="W35" s="83"/>
+      <c r="X35" s="83"/>
+      <c r="Y35" s="83"/>
+    </row>
+    <row r="36" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="46"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42">
+        <v>364</v>
+      </c>
+      <c r="G36" s="42">
+        <v>6</v>
+      </c>
+      <c r="H36" s="42">
+        <v>1</v>
+      </c>
+      <c r="I36" s="42">
+        <v>5</v>
+      </c>
+      <c r="J36" s="42"/>
+      <c r="K36" s="42"/>
+      <c r="L36" s="42">
+        <v>3</v>
+      </c>
+      <c r="M36" s="42"/>
+      <c r="N36" s="42"/>
+      <c r="O36" s="42">
+        <v>3</v>
+      </c>
+      <c r="P36" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>5</v>
+      </c>
+      <c r="R36" s="72"/>
+      <c r="S36" s="44"/>
+      <c r="T36" s="44"/>
+      <c r="U36" s="83"/>
+      <c r="V36" s="83"/>
+      <c r="W36" s="83"/>
+      <c r="X36" s="83"/>
+      <c r="Y36" s="83"/>
+    </row>
+    <row r="37" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="53"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="48"/>
+      <c r="M37" s="48"/>
+      <c r="N37" s="48"/>
+      <c r="O37" s="48"/>
+      <c r="P37" s="48"/>
+      <c r="Q37" s="64"/>
+      <c r="R37" s="72"/>
+      <c r="S37" s="44"/>
+      <c r="T37" s="44"/>
+      <c r="U37" s="83"/>
+      <c r="V37" s="83"/>
+      <c r="W37" s="83"/>
+      <c r="X37" s="83"/>
+      <c r="Y37" s="83"/>
+    </row>
+    <row r="38" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="53"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="19"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="20"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="44"/>
+      <c r="T38" s="44"/>
+      <c r="U38" s="83"/>
+      <c r="V38" s="83"/>
+      <c r="W38" s="83"/>
+      <c r="X38" s="83"/>
+      <c r="Y38" s="83"/>
+    </row>
+    <row r="39" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="53"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="44"/>
+      <c r="T39" s="44"/>
+      <c r="U39" s="83"/>
+      <c r="V39" s="83"/>
+      <c r="W39" s="83"/>
+      <c r="X39" s="83"/>
+      <c r="Y39" s="83"/>
+    </row>
+    <row r="40" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="53"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="72"/>
+      <c r="S40" s="44"/>
+      <c r="T40" s="44"/>
+      <c r="U40" s="83"/>
+      <c r="V40" s="83"/>
+      <c r="W40" s="83"/>
+      <c r="X40" s="83"/>
+      <c r="Y40" s="83"/>
+    </row>
+    <row r="41" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="54"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="40"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="40"/>
+      <c r="M41" s="40"/>
+      <c r="N41" s="40"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="65"/>
+      <c r="R41" s="73"/>
+      <c r="S41" s="74"/>
+      <c r="T41" s="74"/>
+      <c r="U41" s="75"/>
+      <c r="V41" s="83"/>
+      <c r="W41" s="83"/>
+      <c r="X41" s="83"/>
+      <c r="Y41" s="83"/>
+    </row>
+    <row r="42" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="46"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42">
+        <v>364</v>
+      </c>
+      <c r="G42" s="42">
+        <v>6</v>
+      </c>
+      <c r="H42" s="42">
+        <v>1</v>
+      </c>
+      <c r="I42" s="42">
+        <v>5</v>
+      </c>
+      <c r="J42" s="42"/>
+      <c r="K42" s="42"/>
+      <c r="L42" s="42">
+        <v>3</v>
+      </c>
+      <c r="M42" s="42"/>
+      <c r="N42" s="42"/>
+      <c r="O42" s="42">
+        <v>3</v>
+      </c>
+      <c r="P42" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>5</v>
+      </c>
+      <c r="R42" s="87" t="s">
+        <v>54</v>
+      </c>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3"/>
+    </row>
+    <row r="43" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="3"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+      <c r="L43" s="44"/>
+      <c r="M43" s="44"/>
+      <c r="N43" s="44"/>
+      <c r="O43" s="44"/>
+      <c r="P43" s="44"/>
+      <c r="Q43" s="44"/>
+      <c r="R43" s="44"/>
+      <c r="S43" s="44"/>
+      <c r="T43" s="44"/>
+      <c r="U43" s="83"/>
+      <c r="V43" s="83"/>
+      <c r="W43" s="83"/>
+      <c r="X43" s="83"/>
+      <c r="Y43" s="83"/>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B44" s="76" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" s="95">
+        <f>8+1+1+26+1+254</f>
+        <v>291</v>
+      </c>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B45" s="76" t="s">
+        <v>69</v>
+      </c>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="R34:U34"/>
+    <mergeCell ref="R42:U42"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="O34:Q34"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="90" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B613836C-C16E-4423-8438-F674E45BBEA2}">
+  <dimension ref="B1:AA45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.140625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.140625" style="2" customWidth="1"/>
+    <col min="20" max="21" width="5.7109375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="29" width="5.7109375" style="2" customWidth="1"/>
+    <col min="30" max="16384" width="8.7109375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="3"/>
+    </row>
+    <row r="2" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6">
+        <f>[1]DSSR!B4</f>
+        <v>1300</v>
+      </c>
+      <c r="D3" s="6">
+        <f>[1]DSSR!C4</f>
+        <v>1534</v>
+      </c>
+      <c r="E3" s="6">
+        <f>[1]DSSR!D4</f>
+        <v>1728</v>
+      </c>
+      <c r="F3" s="6">
+        <f>[1]DSSR!E4</f>
+        <v>1728</v>
+      </c>
+      <c r="G3" s="6">
+        <f>[1]DSSR!F4</f>
+        <v>1452</v>
+      </c>
+      <c r="H3" s="6">
+        <f>[1]DSSR!G4</f>
+        <v>1240</v>
+      </c>
+      <c r="I3" s="6">
+        <f>[1]DSSR!H4</f>
+        <v>1520</v>
+      </c>
+      <c r="J3" s="6">
+        <f>[1]DSSR!I4</f>
+        <v>978</v>
+      </c>
+      <c r="K3" s="6">
+        <f>[1]DSSR!J4</f>
+        <v>945</v>
+      </c>
+      <c r="L3" s="6">
+        <f>[1]DSSR!K4</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="6">
+        <f>[1]DSSR!L4</f>
+        <v>1127</v>
+      </c>
+      <c r="N3" s="6">
+        <f>[1]DSSR!M4</f>
+        <v>773</v>
+      </c>
+      <c r="O3" s="6">
+        <f>[1]DSSR!N4</f>
+        <v>1038</v>
+      </c>
+      <c r="P3" s="6">
+        <f>[1]DSSR!O4</f>
+        <v>773</v>
+      </c>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6">
+        <f>[1]DSSR!P4</f>
+        <v>1038</v>
+      </c>
+      <c r="U3" s="6">
+        <f>[1]DSSR!Q4</f>
+        <v>773</v>
+      </c>
+      <c r="V3" s="6">
+        <f>[1]DSSR!R4</f>
+        <v>1038</v>
+      </c>
+      <c r="W3" s="6">
+        <f>[1]DSSR!S4</f>
+        <v>792</v>
+      </c>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6">
+        <f>[1]DSSR!T4</f>
+        <v>948</v>
+      </c>
+    </row>
+    <row r="4" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6">
+        <f>[1]DSSR!B5</f>
+        <v>120</v>
+      </c>
+      <c r="D4" s="6">
+        <f>[1]DSSR!C5</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="6">
+        <f>[1]DSSR!D5</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <f>[1]DSSR!E5</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="6">
+        <f>[1]DSSR!F5</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
+        <f>[1]DSSR!G5</f>
+        <v>120</v>
+      </c>
+      <c r="I4" s="6">
+        <f>[1]DSSR!H5</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <f>[1]DSSR!I5</f>
+        <v>120</v>
+      </c>
+      <c r="K4" s="6">
+        <f>[1]DSSR!J5</f>
+        <v>120</v>
+      </c>
+      <c r="L4" s="6">
+        <f>[1]DSSR!K5</f>
+        <v>111</v>
+      </c>
+      <c r="M4" s="6">
+        <f>[1]DSSR!L5</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="6">
+        <f>[1]DSSR!M5</f>
+        <v>120</v>
+      </c>
+      <c r="O4" s="6">
+        <f>[1]DSSR!N5</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="6">
+        <f>[1]DSSR!O5</f>
+        <v>120</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6">
+        <f>[1]DSSR!P5</f>
+        <v>0</v>
+      </c>
+      <c r="U4" s="6">
+        <f>[1]DSSR!Q5</f>
+        <v>120</v>
+      </c>
+      <c r="V4" s="6">
+        <f>[1]DSSR!R5</f>
+        <v>0</v>
+      </c>
+      <c r="W4" s="6">
+        <f>[1]DSSR!S5</f>
+        <v>120</v>
+      </c>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6">
+        <f>[1]DSSR!T5</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="7">
+        <v>84</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7">
+        <v>84</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7">
+        <v>84</v>
+      </c>
+      <c r="K5" s="7">
+        <v>84</v>
+      </c>
+      <c r="L5" s="7">
+        <v>84</v>
+      </c>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7">
+        <v>84</v>
+      </c>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7">
+        <v>84</v>
+      </c>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7">
+        <v>84</v>
+      </c>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7">
+        <v>84</v>
+      </c>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="L6" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="R7" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="S7" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="T7" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="V7" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y7" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="12"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14">
+        <v>2</v>
+      </c>
+      <c r="E8" s="14">
+        <v>17</v>
+      </c>
+      <c r="F8" s="14">
+        <v>17</v>
+      </c>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14">
+        <v>22</v>
+      </c>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14">
+        <v>2</v>
+      </c>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="14">
+        <v>4</v>
+      </c>
+      <c r="X8" s="59"/>
+      <c r="Y8" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="60"/>
+      <c r="Y9" s="20"/>
+    </row>
+    <row r="10" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="60"/>
+      <c r="Y10" s="20"/>
+    </row>
+    <row r="11" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="16"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="60"/>
+      <c r="Y11" s="20"/>
+    </row>
+    <row r="12" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="60"/>
+      <c r="Y12" s="20"/>
+    </row>
+    <row r="13" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="60"/>
+      <c r="Y13" s="20"/>
+    </row>
+    <row r="14" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="16"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="19"/>
+      <c r="V14" s="19"/>
+      <c r="W14" s="19"/>
+      <c r="X14" s="60"/>
+      <c r="Y14" s="20"/>
+    </row>
+    <row r="15" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23">
+        <v>2</v>
+      </c>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
+      <c r="F15" s="23">
+        <v>0</v>
+      </c>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23">
+        <v>10</v>
+      </c>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="T15" s="23">
+        <v>2</v>
+      </c>
+      <c r="U15" s="23"/>
+      <c r="V15" s="23"/>
+      <c r="W15" s="23">
+        <v>4</v>
+      </c>
+      <c r="X15" s="61"/>
+      <c r="Y15" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="57"/>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
+      <c r="E16" s="27">
+        <v>15</v>
+      </c>
+      <c r="F16" s="27">
+        <v>17</v>
+      </c>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28">
+        <v>12</v>
+      </c>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
+      <c r="U16" s="28"/>
+      <c r="V16" s="28"/>
+      <c r="W16" s="56">
+        <v>0</v>
+      </c>
+      <c r="X16" s="62"/>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="32"/>
+    </row>
+    <row r="18" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="34">
+        <f>[1]DSSR!B24</f>
+        <v>544</v>
+      </c>
+      <c r="D18" s="34">
+        <f>[1]DSSR!C24</f>
+        <v>1127</v>
+      </c>
+      <c r="E18" s="34">
+        <f>[1]DSSR!D24</f>
+        <v>853</v>
+      </c>
+      <c r="F18" s="34">
+        <f>[1]DSSR!E24</f>
+        <v>563</v>
+      </c>
+      <c r="G18" s="34">
+        <f>[1]DSSR!F24</f>
+        <v>575</v>
+      </c>
+      <c r="H18" s="34">
+        <f>[1]DSSR!G24</f>
+        <v>1175</v>
+      </c>
+      <c r="I18" s="34">
+        <f>[1]DSSR!H24</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="34">
+        <f>[1]DSSR!I24</f>
+        <v>791</v>
+      </c>
+      <c r="K18" s="34">
+        <f>[1]DSSR!J24</f>
+        <v>1102</v>
+      </c>
+      <c r="L18" s="34">
+        <f>[1]DSSR!K24</f>
+        <v>520</v>
+      </c>
+      <c r="M18" s="34">
+        <f>[1]DSSR!L24</f>
+        <v>1142</v>
+      </c>
+      <c r="N18" s="34">
+        <f>[1]DSSR!M24</f>
+        <v>205</v>
+      </c>
+      <c r="O18" s="34">
+        <f>[1]DSSR!N24</f>
+        <v>205</v>
+      </c>
+      <c r="P18" s="34">
+        <f>[1]DSSR!O24</f>
+        <v>205</v>
+      </c>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="34"/>
+      <c r="S18" s="34"/>
+      <c r="T18" s="34">
+        <f>[1]DSSR!P24</f>
+        <v>500</v>
+      </c>
+      <c r="U18" s="34">
+        <f>[1]DSSR!Q24</f>
+        <v>650</v>
+      </c>
+      <c r="V18" s="34">
+        <f>[1]DSSR!R24</f>
+        <v>650</v>
+      </c>
+      <c r="W18" s="34">
+        <f>[1]DSSR!S24</f>
+        <v>500</v>
+      </c>
+      <c r="X18" s="34"/>
+      <c r="Y18" s="35">
+        <f>[1]DSSR!T24</f>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="34">
+        <f>[1]DSSR!B25</f>
+        <v>111</v>
+      </c>
+      <c r="D19" s="34">
+        <f>[1]DSSR!C25</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="34">
+        <f>[1]DSSR!D25</f>
+        <v>120</v>
+      </c>
+      <c r="F19" s="34">
+        <f>[1]DSSR!E25</f>
+        <v>111</v>
+      </c>
+      <c r="G19" s="34">
+        <f>[1]DSSR!F25</f>
+        <v>111</v>
+      </c>
+      <c r="H19" s="34">
+        <f>[1]DSSR!G25</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="34">
+        <f>[1]DSSR!H25</f>
+        <v>111</v>
+      </c>
+      <c r="J19" s="34">
+        <f>[1]DSSR!I25</f>
+        <v>120</v>
+      </c>
+      <c r="K19" s="34">
+        <f>[1]DSSR!J25</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="34">
+        <f>[1]DSSR!K25</f>
+        <v>111</v>
+      </c>
+      <c r="M19" s="34">
+        <f>[1]DSSR!L25</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="34">
+        <f>[1]DSSR!M25</f>
+        <v>78</v>
+      </c>
+      <c r="O19" s="34">
+        <f>[1]DSSR!N25</f>
+        <v>78</v>
+      </c>
+      <c r="P19" s="34">
+        <f>[1]DSSR!O25</f>
+        <v>78</v>
+      </c>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+      <c r="S19" s="34"/>
+      <c r="T19" s="34">
+        <f>[1]DSSR!P25</f>
+        <v>120</v>
+      </c>
+      <c r="U19" s="34">
+        <f>[1]DSSR!Q25</f>
+        <v>0</v>
+      </c>
+      <c r="V19" s="34">
+        <f>[1]DSSR!R25</f>
+        <v>0</v>
+      </c>
+      <c r="W19" s="34">
+        <f>[1]DSSR!S25</f>
+        <v>120</v>
+      </c>
+      <c r="X19" s="34"/>
+      <c r="Y19" s="35">
+        <f>[1]DSSR!T25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="34">
+        <v>84</v>
+      </c>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34">
+        <v>84</v>
+      </c>
+      <c r="F20" s="34">
+        <v>84</v>
+      </c>
+      <c r="G20" s="34">
+        <v>84</v>
+      </c>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34">
+        <v>84</v>
+      </c>
+      <c r="J20" s="34">
+        <v>84</v>
+      </c>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34">
+        <v>84</v>
+      </c>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34">
+        <v>42</v>
+      </c>
+      <c r="O20" s="34">
+        <v>42</v>
+      </c>
+      <c r="P20" s="34">
+        <v>42</v>
+      </c>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="34"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="34">
+        <v>84</v>
+      </c>
+      <c r="U20" s="34"/>
+      <c r="V20" s="34"/>
+      <c r="W20" s="34">
+        <v>84</v>
+      </c>
+      <c r="X20" s="34"/>
+      <c r="Y20" s="35"/>
+    </row>
+    <row r="21" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="F21" s="36">
+        <f>4.5/2</f>
+        <v>2.25</v>
+      </c>
+      <c r="G21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="J21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="O21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="P21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+      <c r="S21" s="34"/>
+      <c r="T21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="U21" s="34"/>
+      <c r="V21" s="34"/>
+      <c r="W21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="X21" s="34"/>
+      <c r="Y21" s="35"/>
+    </row>
+    <row r="22" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="33"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="34"/>
+      <c r="S22" s="34"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="34"/>
+      <c r="V22" s="34"/>
+      <c r="W22" s="34"/>
+      <c r="X22" s="34"/>
+      <c r="Y22" s="35"/>
+    </row>
+    <row r="23" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="37"/>
+      <c r="C23" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O23" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P23" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q23" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="R23" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="V23" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="11"/>
+    </row>
+    <row r="24" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14">
+        <v>3</v>
+      </c>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14">
+        <v>55</v>
+      </c>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14">
+        <v>471</v>
+      </c>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="14"/>
+      <c r="Y24" s="15"/>
+    </row>
+    <row r="25" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="17"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="19"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="19"/>
+      <c r="X25" s="60"/>
+      <c r="Y25" s="20"/>
+    </row>
+    <row r="26" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="16"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="19"/>
+      <c r="U26" s="19"/>
+      <c r="V26" s="19"/>
+      <c r="W26" s="19"/>
+      <c r="X26" s="60"/>
+      <c r="Y26" s="20"/>
+    </row>
+    <row r="27" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="16"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="19"/>
+      <c r="U27" s="19"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="19"/>
+      <c r="X27" s="60"/>
+      <c r="Y27" s="20"/>
+    </row>
+    <row r="28" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="16"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="19"/>
+      <c r="X28" s="60"/>
+      <c r="Y28" s="20"/>
+    </row>
+    <row r="29" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="16"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="19"/>
+      <c r="W29" s="19"/>
+      <c r="X29" s="60"/>
+      <c r="Y29" s="20"/>
+    </row>
+    <row r="30" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="16"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="19"/>
+      <c r="U30" s="19"/>
+      <c r="V30" s="19"/>
+      <c r="W30" s="19"/>
+      <c r="X30" s="60"/>
+      <c r="Y30" s="20"/>
+    </row>
+    <row r="31" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23">
+        <v>3</v>
+      </c>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23">
+        <v>0</v>
+      </c>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="23">
+        <v>2</v>
+      </c>
+      <c r="L31" s="23"/>
+      <c r="M31" s="23">
+        <v>97</v>
+      </c>
+      <c r="N31" s="23"/>
+      <c r="O31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="23"/>
+      <c r="S31" s="23"/>
+      <c r="T31" s="23"/>
+      <c r="U31" s="23"/>
+      <c r="V31" s="23"/>
+      <c r="W31" s="23"/>
+      <c r="X31" s="61"/>
+      <c r="Y31" s="24"/>
+    </row>
+    <row r="32" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="26"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28">
+        <v>55</v>
+      </c>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28">
+        <v>374</v>
+      </c>
+      <c r="N32" s="28"/>
+      <c r="O32" s="23"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="28"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="63"/>
+      <c r="Y32" s="29"/>
+    </row>
+    <row r="33" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="30"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="68"/>
+      <c r="S33" s="68"/>
+      <c r="T33" s="68"/>
+      <c r="U33" s="68"/>
+      <c r="V33" s="31"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="31"/>
+      <c r="Y33" s="31"/>
+    </row>
+    <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="89" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="91" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
+        <v>46</v>
+      </c>
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
+        <v>47</v>
+      </c>
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
+        <v>48</v>
+      </c>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
+      <c r="V34" s="66"/>
+      <c r="W34" s="3"/>
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
+    </row>
+    <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="90"/>
+      <c r="C35" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="G35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="J35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="K35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="L35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="M35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="N35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="O35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="P35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q35" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="R35" s="69"/>
+      <c r="S35" s="70"/>
+      <c r="T35" s="70"/>
+      <c r="U35" s="71"/>
+      <c r="V35" s="83"/>
+      <c r="W35" s="83"/>
+      <c r="X35" s="83"/>
+      <c r="Y35" s="83"/>
+    </row>
+    <row r="36" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="46"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42">
+        <v>391</v>
+      </c>
+      <c r="G36" s="42">
+        <v>1</v>
+      </c>
+      <c r="H36" s="42">
+        <v>5</v>
+      </c>
+      <c r="I36" s="42">
+        <v>2</v>
+      </c>
+      <c r="J36" s="42"/>
+      <c r="K36" s="42">
+        <v>2</v>
+      </c>
+      <c r="L36" s="42"/>
+      <c r="M36" s="42"/>
+      <c r="N36" s="42"/>
+      <c r="O36" s="42">
+        <v>3</v>
+      </c>
+      <c r="P36" s="42">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>21</v>
+      </c>
+      <c r="R36" s="72"/>
+      <c r="S36" s="44"/>
+      <c r="T36" s="44"/>
+      <c r="U36" s="83"/>
+      <c r="V36" s="83"/>
+      <c r="W36" s="83"/>
+      <c r="X36" s="83"/>
+      <c r="Y36" s="83"/>
+    </row>
+    <row r="37" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="53"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="48"/>
+      <c r="M37" s="48"/>
+      <c r="N37" s="48"/>
+      <c r="O37" s="48"/>
+      <c r="P37" s="48"/>
+      <c r="Q37" s="64"/>
+      <c r="R37" s="72"/>
+      <c r="S37" s="44"/>
+      <c r="T37" s="44"/>
+      <c r="U37" s="83"/>
+      <c r="V37" s="83"/>
+      <c r="W37" s="83"/>
+      <c r="X37" s="83"/>
+      <c r="Y37" s="83"/>
+    </row>
+    <row r="38" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="53"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="19"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="20"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="44"/>
+      <c r="T38" s="44"/>
+      <c r="U38" s="83"/>
+      <c r="V38" s="83"/>
+      <c r="W38" s="83"/>
+      <c r="X38" s="83"/>
+      <c r="Y38" s="83"/>
+    </row>
+    <row r="39" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="53"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="44"/>
+      <c r="T39" s="44"/>
+      <c r="U39" s="83"/>
+      <c r="V39" s="83"/>
+      <c r="W39" s="83"/>
+      <c r="X39" s="83"/>
+      <c r="Y39" s="83"/>
+    </row>
+    <row r="40" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="53"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="72"/>
+      <c r="S40" s="44"/>
+      <c r="T40" s="44"/>
+      <c r="U40" s="83"/>
+      <c r="V40" s="83"/>
+      <c r="W40" s="83"/>
+      <c r="X40" s="83"/>
+      <c r="Y40" s="83"/>
+    </row>
+    <row r="41" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="54"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="40"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="40"/>
+      <c r="M41" s="40"/>
+      <c r="N41" s="40"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="65"/>
+      <c r="R41" s="73"/>
+      <c r="S41" s="74"/>
+      <c r="T41" s="74"/>
+      <c r="U41" s="75"/>
+      <c r="V41" s="83"/>
+      <c r="W41" s="83"/>
+      <c r="X41" s="83"/>
+      <c r="Y41" s="83"/>
+    </row>
+    <row r="42" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="46"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42">
+        <v>391</v>
+      </c>
+      <c r="G42" s="42">
+        <v>1</v>
+      </c>
+      <c r="H42" s="42">
+        <v>5</v>
+      </c>
+      <c r="I42" s="42">
+        <v>2</v>
+      </c>
+      <c r="J42" s="42"/>
+      <c r="K42" s="42">
+        <v>2</v>
+      </c>
+      <c r="L42" s="42"/>
+      <c r="M42" s="42"/>
+      <c r="N42" s="42"/>
+      <c r="O42" s="42">
+        <v>3</v>
+      </c>
+      <c r="P42" s="42">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>21</v>
+      </c>
+      <c r="R42" s="87" t="s">
+        <v>54</v>
+      </c>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3"/>
+    </row>
+    <row r="43" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="3"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+      <c r="L43" s="44"/>
+      <c r="M43" s="44"/>
+      <c r="N43" s="44"/>
+      <c r="O43" s="44"/>
+      <c r="P43" s="44"/>
+      <c r="Q43" s="44"/>
+      <c r="R43" s="44"/>
+      <c r="S43" s="44"/>
+      <c r="T43" s="44"/>
+      <c r="U43" s="83"/>
+      <c r="V43" s="83"/>
+      <c r="W43" s="83"/>
+      <c r="X43" s="83"/>
+      <c r="Y43" s="83"/>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B44" s="76" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" s="95">
+        <f>15+17+12+55+374</f>
+        <v>473</v>
+      </c>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B45" s="76" t="s">
+        <v>69</v>
+      </c>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -24970,47 +31762,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="88" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="90" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="90"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="92" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="90"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="92" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="90"/>
-      <c r="K34" s="91"/>
-      <c r="L34" s="92" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="90"/>
-      <c r="N34" s="91"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="83" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="84"/>
-      <c r="T34" s="84"/>
-      <c r="U34" s="85"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="89"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -25242,12 +32034,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="86" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="87"/>
-      <c r="T42" s="87"/>
-      <c r="U42" s="87"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -25283,17 +32075,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="94"/>
-      <c r="D44" s="94"/>
-      <c r="E44" s="94"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="94"/>
-      <c r="D45" s="94"/>
-      <c r="E45" s="94"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -26671,47 +33463,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="88" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="90" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="90"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="92" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="90"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="92" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="90"/>
-      <c r="K34" s="91"/>
-      <c r="L34" s="92" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="90"/>
-      <c r="N34" s="91"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="83" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="84"/>
-      <c r="T34" s="84"/>
-      <c r="U34" s="85"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="89"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -26979,12 +33771,12 @@
       <c r="Q42" s="43">
         <v>9</v>
       </c>
-      <c r="R42" s="86" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="87"/>
-      <c r="T42" s="87"/>
-      <c r="U42" s="87"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -27020,22 +33812,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="94">
+      <c r="C44" s="95">
         <f>10+5+1+54+8+256</f>
         <v>334</v>
       </c>
-      <c r="D44" s="94"/>
-      <c r="E44" s="94"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="94">
+      <c r="C45" s="95">
         <v>12</v>
       </c>
-      <c r="D45" s="94"/>
-      <c r="E45" s="94"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -28413,47 +35205,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="88" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="90" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="90"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="92" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="90"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="92" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="90"/>
-      <c r="K34" s="91"/>
-      <c r="L34" s="92" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="90"/>
-      <c r="N34" s="91"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="83" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="84"/>
-      <c r="T34" s="84"/>
-      <c r="U34" s="85"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="89"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -28717,12 +35509,12 @@
       <c r="Q42" s="43">
         <v>1</v>
       </c>
-      <c r="R42" s="86" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="87"/>
-      <c r="T42" s="87"/>
-      <c r="U42" s="87"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -28758,22 +35550,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="94">
+      <c r="C44" s="95">
         <f>12+5+2+378</f>
         <v>397</v>
       </c>
-      <c r="D44" s="94"/>
-      <c r="E44" s="94"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="94">
+      <c r="C45" s="95">
         <v>12</v>
       </c>
-      <c r="D45" s="94"/>
-      <c r="E45" s="94"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -30070,47 +36862,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="88" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="90" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="90"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="92" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="90"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="92" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="90"/>
-      <c r="K34" s="91"/>
-      <c r="L34" s="92" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="90"/>
-      <c r="N34" s="91"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="83" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="84"/>
-      <c r="T34" s="84"/>
-      <c r="U34" s="85"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="89"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -30342,12 +37134,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="86" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="87"/>
-      <c r="T42" s="87"/>
-      <c r="U42" s="87"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -31677,47 +38469,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="88" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="90" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="90"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="92" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="90"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="92" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="90"/>
-      <c r="K34" s="91"/>
-      <c r="L34" s="92" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="90"/>
-      <c r="N34" s="91"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="83" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="84"/>
-      <c r="T34" s="84"/>
-      <c r="U34" s="85"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="89"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -31949,12 +38741,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="86" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="87"/>
-      <c r="T42" s="87"/>
-      <c r="U42" s="87"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -31990,17 +38782,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="94"/>
-      <c r="D44" s="94"/>
-      <c r="E44" s="94"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="94"/>
-      <c r="D45" s="94"/>
-      <c r="E45" s="94"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -33366,47 +40158,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="88" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="90" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="90"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="92" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="90"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="92" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="90"/>
-      <c r="K34" s="91"/>
-      <c r="L34" s="92" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="90"/>
-      <c r="N34" s="91"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="83" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="84"/>
-      <c r="T34" s="84"/>
-      <c r="U34" s="85"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="89"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -33686,12 +40478,12 @@
       <c r="Q42" s="43">
         <v>16</v>
       </c>
-      <c r="R42" s="86" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="87"/>
-      <c r="T42" s="87"/>
-      <c r="U42" s="87"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -33727,20 +40519,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="94">
+      <c r="C44" s="95">
         <f>2+5+1+2+1+25+46+10+282</f>
         <v>374</v>
       </c>
-      <c r="D44" s="94"/>
-      <c r="E44" s="94"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="94"/>
-      <c r="D45" s="94"/>
-      <c r="E45" s="94"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -35112,47 +41904,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="88" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="90" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="90"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="92" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="90"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="92" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="90"/>
-      <c r="K34" s="91"/>
-      <c r="L34" s="92" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="90"/>
-      <c r="N34" s="91"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="83" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="84"/>
-      <c r="T34" s="84"/>
-      <c r="U34" s="85"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="89"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -35408,12 +42200,12 @@
       <c r="Q42" s="43">
         <v>17</v>
       </c>
-      <c r="R42" s="86" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="87"/>
-      <c r="T42" s="87"/>
-      <c r="U42" s="87"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -35449,20 +42241,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="94">
+      <c r="C44" s="95">
         <f>8+1+53+6+271</f>
         <v>339</v>
       </c>
-      <c r="D44" s="94"/>
-      <c r="E44" s="94"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="94"/>
-      <c r="D45" s="94"/>
-      <c r="E45" s="94"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/GBDS JULY FILES 2026/CSR MONTH OF JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/CSR MONTH OF JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D59EEC7C-2E04-4B40-9CBE-D61D549DF79B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3816C0-DA39-4121-8594-D3C628FB32A1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="12" activeTab="24" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="16" activeTab="28" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | JULY" sheetId="902" r:id="rId1"/>
@@ -38,9 +38,13 @@
     <sheet name="07-08 R1" sheetId="1812" r:id="rId23"/>
     <sheet name="07-08 R2" sheetId="1813" r:id="rId24"/>
     <sheet name="07-08 R3" sheetId="1814" r:id="rId25"/>
+    <sheet name="(9)" sheetId="1815" r:id="rId26"/>
+    <sheet name="07-09 R1" sheetId="1816" r:id="rId27"/>
+    <sheet name="07-08 R2 (2)" sheetId="1817" r:id="rId28"/>
+    <sheet name="07-09 R3" sheetId="1818" r:id="rId29"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId26"/>
+    <externalReference r:id="rId30"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'(1)'!$A$1:$Z$44</definedName>
@@ -49,6 +53,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="13">'(6)'!$A$1:$Z$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="17">'(7)'!$A$1:$Z$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="21">'(8)'!$A$1:$Z$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="25">'(9)'!$A$1:$Z$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'07-01 R1 NO TRIP'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'07-01 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'07-01 R3'!$A$1:$V$44</definedName>
@@ -66,7 +71,10 @@
     <definedName name="_xlnm.Print_Area" localSheetId="20">'07-07 R3'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="22">'07-08 R1'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="23">'07-08 R2'!$A$1:$V$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="27">'07-08 R2 (2)'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="24">'07-08 R3'!$A$1:$V$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="26">'07-09 R1'!$A$1:$Z$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="28">'07-09 R3'!$A$1:$V$44</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -84,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2172" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2535" uniqueCount="91">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -354,6 +362,9 @@
   </si>
   <si>
     <t>9/12B</t>
+  </si>
+  <si>
+    <t>DATE ___________07/09/2026___________</t>
   </si>
 </sst>
 </file>
@@ -974,7 +985,7 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1229,6 +1240,9 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3096,47 +3110,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -3368,12 +3382,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -4757,47 +4771,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -5069,12 +5083,12 @@
       <c r="Q42" s="43">
         <v>3</v>
       </c>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -5110,22 +5124,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95">
+      <c r="C44" s="96">
         <f>1+1+6+1+8+1+16+404</f>
         <v>438</v>
       </c>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95">
+      <c r="C45" s="96">
         <v>12</v>
       </c>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -6497,47 +6511,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -6785,12 +6799,12 @@
       <c r="Q42" s="43">
         <v>11</v>
       </c>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -6826,22 +6840,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95">
+      <c r="C44" s="96">
         <f>8+1+30+2+322</f>
         <v>363</v>
       </c>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95">
+      <c r="C45" s="96">
         <v>12</v>
       </c>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -8219,47 +8233,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -8517,12 +8531,12 @@
       <c r="Q42" s="43">
         <v>16</v>
       </c>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -8558,17 +8572,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="C44" s="96"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -9865,47 +9879,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -10137,12 +10151,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -11520,47 +11534,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -11844,12 +11858,12 @@
       <c r="Q42" s="43">
         <v>19</v>
       </c>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -11885,20 +11899,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95">
+      <c r="C44" s="96">
         <f>1+1+5+5+3+293</f>
         <v>308</v>
       </c>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -13262,47 +13276,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -13558,12 +13572,12 @@
         <v>8</v>
       </c>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -13599,22 +13613,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95">
+      <c r="C44" s="96">
         <f>1+10+25+306</f>
         <v>342</v>
       </c>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95">
+      <c r="C45" s="96">
         <v>12</v>
       </c>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -14986,47 +15000,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -15278,12 +15292,12 @@
       <c r="Q42" s="43">
         <v>3</v>
       </c>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -15319,20 +15333,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95">
+      <c r="C44" s="96">
         <f>14+2+20+266</f>
         <v>302</v>
       </c>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -16629,47 +16643,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -16901,12 +16915,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -18272,47 +18286,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -18568,12 +18582,12 @@
       <c r="Q42" s="43">
         <v>21</v>
       </c>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -18609,20 +18623,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95">
+      <c r="C44" s="96">
         <f>12+11+324</f>
         <v>347</v>
       </c>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -19919,47 +19933,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -20191,12 +20205,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -21584,47 +21598,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -21880,12 +21894,12 @@
       <c r="Q42" s="43">
         <v>2</v>
       </c>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -21921,20 +21935,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95">
+      <c r="C44" s="96">
         <f>12+70+356</f>
         <v>438</v>
       </c>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -23306,47 +23320,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -23634,12 +23648,12 @@
       <c r="Q42" s="43">
         <v>11</v>
       </c>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -23675,20 +23689,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95">
+      <c r="C44" s="96">
         <f>9+4+2+89+1+279</f>
         <v>384</v>
       </c>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -24985,47 +24999,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -25257,12 +25271,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -26640,47 +26654,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -26944,12 +26958,12 @@
       <c r="Q42" s="43">
         <v>4</v>
       </c>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -26985,22 +26999,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95">
+      <c r="C44" s="96">
         <f>5+20+45+289</f>
         <v>359</v>
       </c>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95">
+      <c r="C45" s="96">
         <v>12</v>
       </c>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -28372,47 +28386,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -28676,12 +28690,12 @@
       <c r="Q42" s="43">
         <v>5</v>
       </c>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -28717,20 +28731,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95">
+      <c r="C44" s="96">
         <f>8+1+1+26+1+254</f>
         <v>291</v>
       </c>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -30102,47 +30116,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -30406,12 +30420,12 @@
       <c r="Q42" s="43">
         <v>21</v>
       </c>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -30447,20 +30461,6822 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95">
+      <c r="C44" s="96">
         <f>15+17+12+55+374</f>
         <v>473</v>
       </c>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="R34:U34"/>
+    <mergeCell ref="R42:U42"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="O34:Q34"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="90" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86948D60-E5A3-4308-BEAF-80B025320197}">
+  <dimension ref="B1:AA43"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
+    <col min="3" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.140625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.140625" style="2" customWidth="1"/>
+    <col min="20" max="21" width="5.7109375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="29" width="5.7109375" style="2" customWidth="1"/>
+    <col min="30" max="16384" width="8.7109375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="3"/>
+    </row>
+    <row r="2" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6">
+        <f>[1]DSSR!B4</f>
+        <v>1300</v>
+      </c>
+      <c r="D3" s="6">
+        <f>[1]DSSR!C4</f>
+        <v>1534</v>
+      </c>
+      <c r="E3" s="6">
+        <f>[1]DSSR!D4</f>
+        <v>1728</v>
+      </c>
+      <c r="F3" s="6">
+        <f>[1]DSSR!E4</f>
+        <v>1728</v>
+      </c>
+      <c r="G3" s="6">
+        <f>[1]DSSR!F4</f>
+        <v>1452</v>
+      </c>
+      <c r="H3" s="6">
+        <f>[1]DSSR!G4</f>
+        <v>1240</v>
+      </c>
+      <c r="I3" s="6">
+        <f>[1]DSSR!H4</f>
+        <v>1520</v>
+      </c>
+      <c r="J3" s="6">
+        <f>[1]DSSR!I4</f>
+        <v>978</v>
+      </c>
+      <c r="K3" s="6">
+        <f>[1]DSSR!J4</f>
+        <v>945</v>
+      </c>
+      <c r="L3" s="6">
+        <f>[1]DSSR!K4</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="6">
+        <f>[1]DSSR!L4</f>
+        <v>1127</v>
+      </c>
+      <c r="N3" s="6">
+        <f>[1]DSSR!M4</f>
+        <v>773</v>
+      </c>
+      <c r="O3" s="6">
+        <f>[1]DSSR!N4</f>
+        <v>1038</v>
+      </c>
+      <c r="P3" s="6">
+        <f>[1]DSSR!O4</f>
+        <v>773</v>
+      </c>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6">
+        <f>[1]DSSR!P4</f>
+        <v>1038</v>
+      </c>
+      <c r="U3" s="6">
+        <f>[1]DSSR!Q4</f>
+        <v>773</v>
+      </c>
+      <c r="V3" s="6">
+        <f>[1]DSSR!R4</f>
+        <v>1038</v>
+      </c>
+      <c r="W3" s="6">
+        <f>[1]DSSR!S4</f>
+        <v>792</v>
+      </c>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6">
+        <f>[1]DSSR!T4</f>
+        <v>948</v>
+      </c>
+    </row>
+    <row r="4" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6">
+        <f>[1]DSSR!B5</f>
+        <v>120</v>
+      </c>
+      <c r="D4" s="6">
+        <f>[1]DSSR!C5</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="6">
+        <f>[1]DSSR!D5</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <f>[1]DSSR!E5</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="6">
+        <f>[1]DSSR!F5</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
+        <f>[1]DSSR!G5</f>
+        <v>120</v>
+      </c>
+      <c r="I4" s="6">
+        <f>[1]DSSR!H5</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <f>[1]DSSR!I5</f>
+        <v>120</v>
+      </c>
+      <c r="K4" s="6">
+        <f>[1]DSSR!J5</f>
+        <v>120</v>
+      </c>
+      <c r="L4" s="6">
+        <f>[1]DSSR!K5</f>
+        <v>111</v>
+      </c>
+      <c r="M4" s="6">
+        <f>[1]DSSR!L5</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="6">
+        <f>[1]DSSR!M5</f>
+        <v>120</v>
+      </c>
+      <c r="O4" s="6">
+        <f>[1]DSSR!N5</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="6">
+        <f>[1]DSSR!O5</f>
+        <v>120</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6">
+        <f>[1]DSSR!P5</f>
+        <v>0</v>
+      </c>
+      <c r="U4" s="6">
+        <f>[1]DSSR!Q5</f>
+        <v>120</v>
+      </c>
+      <c r="V4" s="6">
+        <f>[1]DSSR!R5</f>
+        <v>0</v>
+      </c>
+      <c r="W4" s="6">
+        <f>[1]DSSR!S5</f>
+        <v>120</v>
+      </c>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6">
+        <f>[1]DSSR!T5</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="7">
+        <v>84</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7">
+        <v>84</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7">
+        <v>84</v>
+      </c>
+      <c r="K5" s="7">
+        <v>84</v>
+      </c>
+      <c r="L5" s="7">
+        <v>84</v>
+      </c>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7">
+        <v>84</v>
+      </c>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7">
+        <v>84</v>
+      </c>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7">
+        <v>84</v>
+      </c>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7">
+        <v>84</v>
+      </c>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="L6" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="8"/>
+      <c r="C7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="R7" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="S7" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="T7" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="V7" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y7" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="12"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="14"/>
+      <c r="X8" s="59"/>
+      <c r="Y8" s="15"/>
+    </row>
+    <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="60"/>
+      <c r="Y9" s="20"/>
+    </row>
+    <row r="10" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="60"/>
+      <c r="Y10" s="20"/>
+    </row>
+    <row r="11" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="16"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="60"/>
+      <c r="Y11" s="20"/>
+    </row>
+    <row r="12" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="60"/>
+      <c r="Y12" s="20"/>
+    </row>
+    <row r="13" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="60"/>
+      <c r="Y13" s="20"/>
+    </row>
+    <row r="14" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="16"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="19"/>
+      <c r="V14" s="19"/>
+      <c r="W14" s="19"/>
+      <c r="X14" s="60"/>
+      <c r="Y14" s="20"/>
+    </row>
+    <row r="15" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="T15" s="23"/>
+      <c r="U15" s="23"/>
+      <c r="V15" s="23"/>
+      <c r="W15" s="23"/>
+      <c r="X15" s="61"/>
+      <c r="Y15" s="24"/>
+    </row>
+    <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="57"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28"/>
+      <c r="U16" s="28"/>
+      <c r="V16" s="28"/>
+      <c r="W16" s="56"/>
+      <c r="X16" s="62"/>
+      <c r="Y16" s="29"/>
+    </row>
+    <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="32"/>
+    </row>
+    <row r="18" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="34">
+        <f>[1]DSSR!B24</f>
+        <v>544</v>
+      </c>
+      <c r="D18" s="34">
+        <f>[1]DSSR!C24</f>
+        <v>1127</v>
+      </c>
+      <c r="E18" s="34">
+        <f>[1]DSSR!D24</f>
+        <v>853</v>
+      </c>
+      <c r="F18" s="34">
+        <f>[1]DSSR!E24</f>
+        <v>563</v>
+      </c>
+      <c r="G18" s="34">
+        <f>[1]DSSR!F24</f>
+        <v>575</v>
+      </c>
+      <c r="H18" s="34">
+        <f>[1]DSSR!G24</f>
+        <v>1175</v>
+      </c>
+      <c r="I18" s="34">
+        <f>[1]DSSR!H24</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="34">
+        <f>[1]DSSR!I24</f>
+        <v>791</v>
+      </c>
+      <c r="K18" s="34">
+        <f>[1]DSSR!J24</f>
+        <v>1102</v>
+      </c>
+      <c r="L18" s="34">
+        <f>[1]DSSR!K24</f>
+        <v>520</v>
+      </c>
+      <c r="M18" s="34">
+        <f>[1]DSSR!L24</f>
+        <v>1142</v>
+      </c>
+      <c r="N18" s="34">
+        <f>[1]DSSR!M24</f>
+        <v>205</v>
+      </c>
+      <c r="O18" s="34">
+        <f>[1]DSSR!N24</f>
+        <v>205</v>
+      </c>
+      <c r="P18" s="34">
+        <f>[1]DSSR!O24</f>
+        <v>205</v>
+      </c>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="34"/>
+      <c r="S18" s="34"/>
+      <c r="T18" s="34">
+        <f>[1]DSSR!P24</f>
+        <v>500</v>
+      </c>
+      <c r="U18" s="34">
+        <f>[1]DSSR!Q24</f>
+        <v>650</v>
+      </c>
+      <c r="V18" s="34">
+        <f>[1]DSSR!R24</f>
+        <v>650</v>
+      </c>
+      <c r="W18" s="34">
+        <f>[1]DSSR!S24</f>
+        <v>500</v>
+      </c>
+      <c r="X18" s="34"/>
+      <c r="Y18" s="35">
+        <f>[1]DSSR!T24</f>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="34">
+        <f>[1]DSSR!B25</f>
+        <v>111</v>
+      </c>
+      <c r="D19" s="34">
+        <f>[1]DSSR!C25</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="34">
+        <f>[1]DSSR!D25</f>
+        <v>120</v>
+      </c>
+      <c r="F19" s="34">
+        <f>[1]DSSR!E25</f>
+        <v>111</v>
+      </c>
+      <c r="G19" s="34">
+        <f>[1]DSSR!F25</f>
+        <v>111</v>
+      </c>
+      <c r="H19" s="34">
+        <f>[1]DSSR!G25</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="34">
+        <f>[1]DSSR!H25</f>
+        <v>111</v>
+      </c>
+      <c r="J19" s="34">
+        <f>[1]DSSR!I25</f>
+        <v>120</v>
+      </c>
+      <c r="K19" s="34">
+        <f>[1]DSSR!J25</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="34">
+        <f>[1]DSSR!K25</f>
+        <v>111</v>
+      </c>
+      <c r="M19" s="34">
+        <f>[1]DSSR!L25</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="34">
+        <f>[1]DSSR!M25</f>
+        <v>78</v>
+      </c>
+      <c r="O19" s="34">
+        <f>[1]DSSR!N25</f>
+        <v>78</v>
+      </c>
+      <c r="P19" s="34">
+        <f>[1]DSSR!O25</f>
+        <v>78</v>
+      </c>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+      <c r="S19" s="34"/>
+      <c r="T19" s="34">
+        <f>[1]DSSR!P25</f>
+        <v>120</v>
+      </c>
+      <c r="U19" s="34">
+        <f>[1]DSSR!Q25</f>
+        <v>0</v>
+      </c>
+      <c r="V19" s="34">
+        <f>[1]DSSR!R25</f>
+        <v>0</v>
+      </c>
+      <c r="W19" s="34">
+        <f>[1]DSSR!S25</f>
+        <v>120</v>
+      </c>
+      <c r="X19" s="34"/>
+      <c r="Y19" s="35">
+        <f>[1]DSSR!T25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="34">
+        <v>84</v>
+      </c>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34">
+        <v>84</v>
+      </c>
+      <c r="F20" s="34">
+        <v>84</v>
+      </c>
+      <c r="G20" s="34">
+        <v>84</v>
+      </c>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34">
+        <v>84</v>
+      </c>
+      <c r="J20" s="34">
+        <v>84</v>
+      </c>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34">
+        <v>84</v>
+      </c>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34">
+        <v>42</v>
+      </c>
+      <c r="O20" s="34">
+        <v>42</v>
+      </c>
+      <c r="P20" s="34">
+        <v>42</v>
+      </c>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="34"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="34">
+        <v>84</v>
+      </c>
+      <c r="U20" s="34"/>
+      <c r="V20" s="34"/>
+      <c r="W20" s="34">
+        <v>84</v>
+      </c>
+      <c r="X20" s="34"/>
+      <c r="Y20" s="35"/>
+    </row>
+    <row r="21" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="F21" s="36">
+        <f>4.5/2</f>
+        <v>2.25</v>
+      </c>
+      <c r="G21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="J21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="O21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="P21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+      <c r="S21" s="34"/>
+      <c r="T21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="U21" s="34"/>
+      <c r="V21" s="34"/>
+      <c r="W21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="X21" s="34"/>
+      <c r="Y21" s="35"/>
+    </row>
+    <row r="22" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="33"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="34"/>
+      <c r="S22" s="34"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="34"/>
+      <c r="V22" s="34"/>
+      <c r="W22" s="34"/>
+      <c r="X22" s="34"/>
+      <c r="Y22" s="35"/>
+    </row>
+    <row r="23" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="37"/>
+      <c r="C23" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O23" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P23" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q23" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="R23" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="V23" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="11"/>
+    </row>
+    <row r="24" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="14"/>
+      <c r="Y24" s="15"/>
+    </row>
+    <row r="25" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="17"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="19"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="19"/>
+      <c r="X25" s="60"/>
+      <c r="Y25" s="20"/>
+    </row>
+    <row r="26" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="16"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="19"/>
+      <c r="U26" s="19"/>
+      <c r="V26" s="19"/>
+      <c r="W26" s="19"/>
+      <c r="X26" s="60"/>
+      <c r="Y26" s="20"/>
+    </row>
+    <row r="27" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="16"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="19"/>
+      <c r="U27" s="19"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="19"/>
+      <c r="X27" s="60"/>
+      <c r="Y27" s="20"/>
+    </row>
+    <row r="28" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="16"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="19"/>
+      <c r="X28" s="60"/>
+      <c r="Y28" s="20"/>
+    </row>
+    <row r="29" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="16"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="19"/>
+      <c r="W29" s="19"/>
+      <c r="X29" s="60"/>
+      <c r="Y29" s="20"/>
+    </row>
+    <row r="30" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="16"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="19"/>
+      <c r="U30" s="19"/>
+      <c r="V30" s="19"/>
+      <c r="W30" s="19"/>
+      <c r="X30" s="60"/>
+      <c r="Y30" s="20"/>
+    </row>
+    <row r="31" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
+      <c r="M31" s="23"/>
+      <c r="N31" s="23"/>
+      <c r="O31" s="23"/>
+      <c r="P31" s="23"/>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="23"/>
+      <c r="S31" s="23"/>
+      <c r="T31" s="23"/>
+      <c r="U31" s="23"/>
+      <c r="V31" s="23"/>
+      <c r="W31" s="23"/>
+      <c r="X31" s="61"/>
+      <c r="Y31" s="24"/>
+    </row>
+    <row r="32" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="26"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="23"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="28"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="63"/>
+      <c r="Y32" s="29"/>
+    </row>
+    <row r="33" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="30"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="68"/>
+      <c r="S33" s="68"/>
+      <c r="T33" s="68"/>
+      <c r="U33" s="68"/>
+      <c r="V33" s="31"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="31"/>
+      <c r="Y33" s="31"/>
+    </row>
+    <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="90" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="92" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
+        <v>46</v>
+      </c>
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
+        <v>47</v>
+      </c>
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
+        <v>48</v>
+      </c>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
+      <c r="V34" s="66"/>
+      <c r="W34" s="3"/>
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
+    </row>
+    <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="91"/>
+      <c r="C35" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="G35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="J35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="K35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="L35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="M35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="N35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="O35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="P35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q35" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="R35" s="69"/>
+      <c r="S35" s="70"/>
+      <c r="T35" s="70"/>
+      <c r="U35" s="71"/>
+      <c r="V35" s="84"/>
+      <c r="W35" s="84"/>
+      <c r="X35" s="84"/>
+      <c r="Y35" s="84"/>
+    </row>
+    <row r="36" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="46"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="42"/>
+      <c r="L36" s="42"/>
+      <c r="M36" s="42"/>
+      <c r="N36" s="42"/>
+      <c r="O36" s="42"/>
+      <c r="P36" s="42"/>
+      <c r="Q36" s="43"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="44"/>
+      <c r="T36" s="44"/>
+      <c r="U36" s="84"/>
+      <c r="V36" s="84"/>
+      <c r="W36" s="84"/>
+      <c r="X36" s="84"/>
+      <c r="Y36" s="84"/>
+    </row>
+    <row r="37" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="53"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="48"/>
+      <c r="M37" s="48"/>
+      <c r="N37" s="48"/>
+      <c r="O37" s="48"/>
+      <c r="P37" s="48"/>
+      <c r="Q37" s="64"/>
+      <c r="R37" s="72"/>
+      <c r="S37" s="44"/>
+      <c r="T37" s="44"/>
+      <c r="U37" s="84"/>
+      <c r="V37" s="84"/>
+      <c r="W37" s="84"/>
+      <c r="X37" s="84"/>
+      <c r="Y37" s="84"/>
+    </row>
+    <row r="38" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="53"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="19"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="20"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="44"/>
+      <c r="T38" s="44"/>
+      <c r="U38" s="84"/>
+      <c r="V38" s="84"/>
+      <c r="W38" s="84"/>
+      <c r="X38" s="84"/>
+      <c r="Y38" s="84"/>
+    </row>
+    <row r="39" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="53"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="44"/>
+      <c r="T39" s="44"/>
+      <c r="U39" s="84"/>
+      <c r="V39" s="84"/>
+      <c r="W39" s="84"/>
+      <c r="X39" s="84"/>
+      <c r="Y39" s="84"/>
+    </row>
+    <row r="40" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="53"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="72"/>
+      <c r="S40" s="44"/>
+      <c r="T40" s="44"/>
+      <c r="U40" s="84"/>
+      <c r="V40" s="84"/>
+      <c r="W40" s="84"/>
+      <c r="X40" s="84"/>
+      <c r="Y40" s="84"/>
+    </row>
+    <row r="41" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="54"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="40"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="40"/>
+      <c r="M41" s="40"/>
+      <c r="N41" s="40"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="65"/>
+      <c r="R41" s="73"/>
+      <c r="S41" s="74"/>
+      <c r="T41" s="74"/>
+      <c r="U41" s="75"/>
+      <c r="V41" s="84"/>
+      <c r="W41" s="84"/>
+      <c r="X41" s="84"/>
+      <c r="Y41" s="84"/>
+    </row>
+    <row r="42" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="46"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="42"/>
+      <c r="I42" s="42"/>
+      <c r="J42" s="42"/>
+      <c r="K42" s="42"/>
+      <c r="L42" s="42"/>
+      <c r="M42" s="42"/>
+      <c r="N42" s="42"/>
+      <c r="O42" s="42"/>
+      <c r="P42" s="42"/>
+      <c r="Q42" s="43"/>
+      <c r="R42" s="88" t="s">
+        <v>54</v>
+      </c>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3"/>
+    </row>
+    <row r="43" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="3"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+      <c r="L43" s="44"/>
+      <c r="M43" s="44"/>
+      <c r="N43" s="44"/>
+      <c r="O43" s="44"/>
+      <c r="P43" s="44"/>
+      <c r="Q43" s="44"/>
+      <c r="R43" s="44"/>
+      <c r="S43" s="44"/>
+      <c r="T43" s="44"/>
+      <c r="U43" s="84"/>
+      <c r="V43" s="84"/>
+      <c r="W43" s="84"/>
+      <c r="X43" s="84"/>
+      <c r="Y43" s="84"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="R34:U34"/>
+    <mergeCell ref="R42:U42"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="O34:Q34"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="83" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48E91782-0E6F-470A-9CCB-BB7B6DD4454F}">
+  <dimension ref="B1:AA45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
+    <col min="3" max="5" width="5.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.140625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.140625" style="2" customWidth="1"/>
+    <col min="20" max="21" width="5.7109375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="29" width="5.7109375" style="2" customWidth="1"/>
+    <col min="30" max="16384" width="8.7109375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="3"/>
+    </row>
+    <row r="2" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6">
+        <f>[1]DSSR!B4</f>
+        <v>1300</v>
+      </c>
+      <c r="D3" s="6">
+        <f>[1]DSSR!C4</f>
+        <v>1534</v>
+      </c>
+      <c r="E3" s="6">
+        <f>[1]DSSR!D4</f>
+        <v>1728</v>
+      </c>
+      <c r="F3" s="6">
+        <f>[1]DSSR!E4</f>
+        <v>1728</v>
+      </c>
+      <c r="G3" s="6">
+        <f>[1]DSSR!F4</f>
+        <v>1452</v>
+      </c>
+      <c r="H3" s="6">
+        <f>[1]DSSR!G4</f>
+        <v>1240</v>
+      </c>
+      <c r="I3" s="6">
+        <f>[1]DSSR!H4</f>
+        <v>1520</v>
+      </c>
+      <c r="J3" s="6">
+        <f>[1]DSSR!I4</f>
+        <v>978</v>
+      </c>
+      <c r="K3" s="6">
+        <f>[1]DSSR!J4</f>
+        <v>945</v>
+      </c>
+      <c r="L3" s="6">
+        <f>[1]DSSR!K4</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="6">
+        <f>[1]DSSR!L4</f>
+        <v>1127</v>
+      </c>
+      <c r="N3" s="6">
+        <f>[1]DSSR!M4</f>
+        <v>773</v>
+      </c>
+      <c r="O3" s="6">
+        <f>[1]DSSR!N4</f>
+        <v>1038</v>
+      </c>
+      <c r="P3" s="6">
+        <f>[1]DSSR!O4</f>
+        <v>773</v>
+      </c>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6">
+        <f>[1]DSSR!P4</f>
+        <v>1038</v>
+      </c>
+      <c r="U3" s="6">
+        <f>[1]DSSR!Q4</f>
+        <v>773</v>
+      </c>
+      <c r="V3" s="6">
+        <f>[1]DSSR!R4</f>
+        <v>1038</v>
+      </c>
+      <c r="W3" s="6">
+        <f>[1]DSSR!S4</f>
+        <v>792</v>
+      </c>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6">
+        <f>[1]DSSR!T4</f>
+        <v>948</v>
+      </c>
+    </row>
+    <row r="4" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6">
+        <f>[1]DSSR!B5</f>
+        <v>120</v>
+      </c>
+      <c r="D4" s="6">
+        <f>[1]DSSR!C5</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="6">
+        <f>[1]DSSR!D5</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <f>[1]DSSR!E5</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="6">
+        <f>[1]DSSR!F5</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
+        <f>[1]DSSR!G5</f>
+        <v>120</v>
+      </c>
+      <c r="I4" s="6">
+        <f>[1]DSSR!H5</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <f>[1]DSSR!I5</f>
+        <v>120</v>
+      </c>
+      <c r="K4" s="6">
+        <f>[1]DSSR!J5</f>
+        <v>120</v>
+      </c>
+      <c r="L4" s="6">
+        <f>[1]DSSR!K5</f>
+        <v>111</v>
+      </c>
+      <c r="M4" s="6">
+        <f>[1]DSSR!L5</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="6">
+        <f>[1]DSSR!M5</f>
+        <v>120</v>
+      </c>
+      <c r="O4" s="6">
+        <f>[1]DSSR!N5</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="6">
+        <f>[1]DSSR!O5</f>
+        <v>120</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6">
+        <f>[1]DSSR!P5</f>
+        <v>0</v>
+      </c>
+      <c r="U4" s="6">
+        <f>[1]DSSR!Q5</f>
+        <v>120</v>
+      </c>
+      <c r="V4" s="6">
+        <f>[1]DSSR!R5</f>
+        <v>0</v>
+      </c>
+      <c r="W4" s="6">
+        <f>[1]DSSR!S5</f>
+        <v>120</v>
+      </c>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6">
+        <f>[1]DSSR!T5</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="7">
+        <v>84</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7">
+        <v>84</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7">
+        <v>84</v>
+      </c>
+      <c r="K5" s="7">
+        <v>84</v>
+      </c>
+      <c r="L5" s="7">
+        <v>84</v>
+      </c>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7">
+        <v>84</v>
+      </c>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7">
+        <v>84</v>
+      </c>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7">
+        <v>84</v>
+      </c>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7">
+        <v>84</v>
+      </c>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="L6" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="R7" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="S7" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="T7" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="V7" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y7" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="12"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14">
+        <v>1</v>
+      </c>
+      <c r="E8" s="14">
+        <v>1</v>
+      </c>
+      <c r="F8" s="14">
+        <v>1</v>
+      </c>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14">
+        <v>2</v>
+      </c>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="14">
+        <v>2</v>
+      </c>
+      <c r="X8" s="59">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="15"/>
+    </row>
+    <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="60"/>
+      <c r="Y9" s="20"/>
+    </row>
+    <row r="10" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="60"/>
+      <c r="Y10" s="20"/>
+    </row>
+    <row r="11" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="16"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="60"/>
+      <c r="Y11" s="20"/>
+    </row>
+    <row r="12" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="60"/>
+      <c r="Y12" s="20"/>
+    </row>
+    <row r="13" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="60"/>
+      <c r="Y13" s="20"/>
+    </row>
+    <row r="14" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="16"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="19"/>
+      <c r="V14" s="19"/>
+      <c r="W14" s="19"/>
+      <c r="X14" s="60"/>
+      <c r="Y14" s="20"/>
+    </row>
+    <row r="15" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23">
+        <v>1</v>
+      </c>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
+      <c r="F15" s="23">
+        <v>0</v>
+      </c>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="T15" s="23">
+        <v>1</v>
+      </c>
+      <c r="U15" s="23"/>
+      <c r="V15" s="23"/>
+      <c r="W15" s="23">
+        <v>1</v>
+      </c>
+      <c r="X15" s="61">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="24"/>
+    </row>
+    <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="57"/>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
+      <c r="E16" s="27">
+        <v>1</v>
+      </c>
+      <c r="F16" s="27">
+        <v>1</v>
+      </c>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28">
+        <v>10</v>
+      </c>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28">
+        <v>1</v>
+      </c>
+      <c r="U16" s="28"/>
+      <c r="V16" s="28"/>
+      <c r="W16" s="56">
+        <v>1</v>
+      </c>
+      <c r="X16" s="62">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="29"/>
+    </row>
+    <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="32"/>
+    </row>
+    <row r="18" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="34">
+        <f>[1]DSSR!B24</f>
+        <v>544</v>
+      </c>
+      <c r="D18" s="34">
+        <f>[1]DSSR!C24</f>
+        <v>1127</v>
+      </c>
+      <c r="E18" s="34">
+        <f>[1]DSSR!D24</f>
+        <v>853</v>
+      </c>
+      <c r="F18" s="34">
+        <f>[1]DSSR!E24</f>
+        <v>563</v>
+      </c>
+      <c r="G18" s="34">
+        <f>[1]DSSR!F24</f>
+        <v>575</v>
+      </c>
+      <c r="H18" s="34">
+        <f>[1]DSSR!G24</f>
+        <v>1175</v>
+      </c>
+      <c r="I18" s="34">
+        <f>[1]DSSR!H24</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="34">
+        <f>[1]DSSR!I24</f>
+        <v>791</v>
+      </c>
+      <c r="K18" s="34">
+        <f>[1]DSSR!J24</f>
+        <v>1102</v>
+      </c>
+      <c r="L18" s="34">
+        <f>[1]DSSR!K24</f>
+        <v>520</v>
+      </c>
+      <c r="M18" s="34">
+        <f>[1]DSSR!L24</f>
+        <v>1142</v>
+      </c>
+      <c r="N18" s="34">
+        <f>[1]DSSR!M24</f>
+        <v>205</v>
+      </c>
+      <c r="O18" s="34">
+        <f>[1]DSSR!N24</f>
+        <v>205</v>
+      </c>
+      <c r="P18" s="34">
+        <f>[1]DSSR!O24</f>
+        <v>205</v>
+      </c>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="34"/>
+      <c r="S18" s="34"/>
+      <c r="T18" s="34">
+        <f>[1]DSSR!P24</f>
+        <v>500</v>
+      </c>
+      <c r="U18" s="34">
+        <f>[1]DSSR!Q24</f>
+        <v>650</v>
+      </c>
+      <c r="V18" s="34">
+        <f>[1]DSSR!R24</f>
+        <v>650</v>
+      </c>
+      <c r="W18" s="34">
+        <f>[1]DSSR!S24</f>
+        <v>500</v>
+      </c>
+      <c r="X18" s="34"/>
+      <c r="Y18" s="35">
+        <f>[1]DSSR!T24</f>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="34">
+        <f>[1]DSSR!B25</f>
+        <v>111</v>
+      </c>
+      <c r="D19" s="34">
+        <f>[1]DSSR!C25</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="34">
+        <f>[1]DSSR!D25</f>
+        <v>120</v>
+      </c>
+      <c r="F19" s="34">
+        <f>[1]DSSR!E25</f>
+        <v>111</v>
+      </c>
+      <c r="G19" s="34">
+        <f>[1]DSSR!F25</f>
+        <v>111</v>
+      </c>
+      <c r="H19" s="34">
+        <f>[1]DSSR!G25</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="34">
+        <f>[1]DSSR!H25</f>
+        <v>111</v>
+      </c>
+      <c r="J19" s="34">
+        <f>[1]DSSR!I25</f>
+        <v>120</v>
+      </c>
+      <c r="K19" s="34">
+        <f>[1]DSSR!J25</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="34">
+        <f>[1]DSSR!K25</f>
+        <v>111</v>
+      </c>
+      <c r="M19" s="34">
+        <f>[1]DSSR!L25</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="34">
+        <f>[1]DSSR!M25</f>
+        <v>78</v>
+      </c>
+      <c r="O19" s="34">
+        <f>[1]DSSR!N25</f>
+        <v>78</v>
+      </c>
+      <c r="P19" s="34">
+        <f>[1]DSSR!O25</f>
+        <v>78</v>
+      </c>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+      <c r="S19" s="34"/>
+      <c r="T19" s="34">
+        <f>[1]DSSR!P25</f>
+        <v>120</v>
+      </c>
+      <c r="U19" s="34">
+        <f>[1]DSSR!Q25</f>
+        <v>0</v>
+      </c>
+      <c r="V19" s="34">
+        <f>[1]DSSR!R25</f>
+        <v>0</v>
+      </c>
+      <c r="W19" s="34">
+        <f>[1]DSSR!S25</f>
+        <v>120</v>
+      </c>
+      <c r="X19" s="34"/>
+      <c r="Y19" s="35">
+        <f>[1]DSSR!T25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="34">
+        <v>84</v>
+      </c>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34">
+        <v>84</v>
+      </c>
+      <c r="F20" s="34">
+        <v>84</v>
+      </c>
+      <c r="G20" s="34">
+        <v>84</v>
+      </c>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34">
+        <v>84</v>
+      </c>
+      <c r="J20" s="34">
+        <v>84</v>
+      </c>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34">
+        <v>84</v>
+      </c>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34">
+        <v>42</v>
+      </c>
+      <c r="O20" s="34">
+        <v>42</v>
+      </c>
+      <c r="P20" s="34">
+        <v>42</v>
+      </c>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="34"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="34">
+        <v>84</v>
+      </c>
+      <c r="U20" s="34"/>
+      <c r="V20" s="34"/>
+      <c r="W20" s="34">
+        <v>84</v>
+      </c>
+      <c r="X20" s="34"/>
+      <c r="Y20" s="35"/>
+    </row>
+    <row r="21" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="F21" s="36">
+        <f>4.5/2</f>
+        <v>2.25</v>
+      </c>
+      <c r="G21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="J21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="O21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="P21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+      <c r="S21" s="34"/>
+      <c r="T21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="U21" s="34"/>
+      <c r="V21" s="34"/>
+      <c r="W21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="X21" s="34"/>
+      <c r="Y21" s="35"/>
+    </row>
+    <row r="22" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="33"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="34"/>
+      <c r="S22" s="34"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="34"/>
+      <c r="V22" s="34"/>
+      <c r="W22" s="34"/>
+      <c r="X22" s="34"/>
+      <c r="Y22" s="35"/>
+    </row>
+    <row r="23" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="37"/>
+      <c r="C23" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O23" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P23" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q23" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="R23" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="V23" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="11"/>
+    </row>
+    <row r="24" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14">
+        <v>20</v>
+      </c>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14">
+        <v>363</v>
+      </c>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="14"/>
+      <c r="Y24" s="15"/>
+    </row>
+    <row r="25" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="17"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="19"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="19"/>
+      <c r="X25" s="60"/>
+      <c r="Y25" s="20"/>
+    </row>
+    <row r="26" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="16"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="19"/>
+      <c r="U26" s="19"/>
+      <c r="V26" s="19"/>
+      <c r="W26" s="19"/>
+      <c r="X26" s="60"/>
+      <c r="Y26" s="20"/>
+    </row>
+    <row r="27" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="16"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="19"/>
+      <c r="U27" s="19"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="19"/>
+      <c r="X27" s="60"/>
+      <c r="Y27" s="20"/>
+    </row>
+    <row r="28" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="16"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="19"/>
+      <c r="X28" s="60"/>
+      <c r="Y28" s="20"/>
+    </row>
+    <row r="29" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="16"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="19"/>
+      <c r="W29" s="19"/>
+      <c r="X29" s="60"/>
+      <c r="Y29" s="20"/>
+    </row>
+    <row r="30" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="16"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="19"/>
+      <c r="U30" s="19"/>
+      <c r="V30" s="19"/>
+      <c r="W30" s="19"/>
+      <c r="X30" s="60"/>
+      <c r="Y30" s="20"/>
+    </row>
+    <row r="31" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23">
+        <v>1</v>
+      </c>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23">
+        <v>0</v>
+      </c>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
+      <c r="M31" s="23">
+        <v>7</v>
+      </c>
+      <c r="N31" s="23"/>
+      <c r="O31" s="23"/>
+      <c r="P31" s="23">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="23"/>
+      <c r="S31" s="23"/>
+      <c r="T31" s="23"/>
+      <c r="U31" s="23"/>
+      <c r="V31" s="23"/>
+      <c r="W31" s="23"/>
+      <c r="X31" s="61"/>
+      <c r="Y31" s="24"/>
+    </row>
+    <row r="32" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="26"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27">
+        <v>1</v>
+      </c>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28">
+        <v>20</v>
+      </c>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28">
+        <v>356</v>
+      </c>
+      <c r="N32" s="28"/>
+      <c r="O32" s="23"/>
+      <c r="P32" s="28">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="28"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="63"/>
+      <c r="Y32" s="29"/>
+    </row>
+    <row r="33" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="30"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="68"/>
+      <c r="S33" s="68"/>
+      <c r="T33" s="68"/>
+      <c r="U33" s="68"/>
+      <c r="V33" s="31"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="31"/>
+      <c r="Y33" s="31"/>
+    </row>
+    <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="90" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="92" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
+        <v>46</v>
+      </c>
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
+        <v>47</v>
+      </c>
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
+        <v>48</v>
+      </c>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
+      <c r="V34" s="66"/>
+      <c r="W34" s="3"/>
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
+    </row>
+    <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="91"/>
+      <c r="C35" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="G35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="J35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="K35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="L35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="M35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="N35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="O35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="P35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q35" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="R35" s="69"/>
+      <c r="S35" s="70"/>
+      <c r="T35" s="70"/>
+      <c r="U35" s="71"/>
+      <c r="V35" s="84"/>
+      <c r="W35" s="84"/>
+      <c r="X35" s="84"/>
+      <c r="Y35" s="84"/>
+    </row>
+    <row r="36" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="46">
+        <v>1</v>
+      </c>
+      <c r="D36" s="41"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42">
+        <v>378</v>
+      </c>
+      <c r="G36" s="42">
+        <v>6</v>
+      </c>
+      <c r="H36" s="42">
+        <v>1</v>
+      </c>
+      <c r="I36" s="42">
+        <v>1</v>
+      </c>
+      <c r="J36" s="42">
+        <v>4</v>
+      </c>
+      <c r="K36" s="42"/>
+      <c r="L36" s="42">
+        <v>1</v>
+      </c>
+      <c r="M36" s="42">
+        <v>1</v>
+      </c>
+      <c r="N36" s="42">
+        <v>5</v>
+      </c>
+      <c r="O36" s="42">
+        <v>8</v>
+      </c>
+      <c r="P36" s="42">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>1</v>
+      </c>
+      <c r="R36" s="72"/>
+      <c r="S36" s="44"/>
+      <c r="T36" s="44"/>
+      <c r="U36" s="84"/>
+      <c r="V36" s="84"/>
+      <c r="W36" s="84"/>
+      <c r="X36" s="84"/>
+      <c r="Y36" s="84"/>
+    </row>
+    <row r="37" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="53"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="48"/>
+      <c r="M37" s="48"/>
+      <c r="N37" s="48"/>
+      <c r="O37" s="48"/>
+      <c r="P37" s="48"/>
+      <c r="Q37" s="64"/>
+      <c r="R37" s="72"/>
+      <c r="S37" s="44"/>
+      <c r="T37" s="44"/>
+      <c r="U37" s="84"/>
+      <c r="V37" s="84"/>
+      <c r="W37" s="84"/>
+      <c r="X37" s="84"/>
+      <c r="Y37" s="84"/>
+    </row>
+    <row r="38" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="53"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="19"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="20"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="44"/>
+      <c r="T38" s="44"/>
+      <c r="U38" s="84"/>
+      <c r="V38" s="84"/>
+      <c r="W38" s="84"/>
+      <c r="X38" s="84"/>
+      <c r="Y38" s="84"/>
+    </row>
+    <row r="39" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="53"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="44"/>
+      <c r="T39" s="44"/>
+      <c r="U39" s="84"/>
+      <c r="V39" s="84"/>
+      <c r="W39" s="84"/>
+      <c r="X39" s="84"/>
+      <c r="Y39" s="84"/>
+    </row>
+    <row r="40" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="53"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="72"/>
+      <c r="S40" s="44"/>
+      <c r="T40" s="44"/>
+      <c r="U40" s="84"/>
+      <c r="V40" s="84"/>
+      <c r="W40" s="84"/>
+      <c r="X40" s="84"/>
+      <c r="Y40" s="84"/>
+    </row>
+    <row r="41" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="54"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="40"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="40"/>
+      <c r="M41" s="40"/>
+      <c r="N41" s="40"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="65"/>
+      <c r="R41" s="73"/>
+      <c r="S41" s="74"/>
+      <c r="T41" s="74"/>
+      <c r="U41" s="75"/>
+      <c r="V41" s="84"/>
+      <c r="W41" s="84"/>
+      <c r="X41" s="84"/>
+      <c r="Y41" s="84"/>
+    </row>
+    <row r="42" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="46">
+        <v>1</v>
+      </c>
+      <c r="D42" s="41"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42">
+        <v>378</v>
+      </c>
+      <c r="G42" s="42">
+        <v>6</v>
+      </c>
+      <c r="H42" s="42">
+        <v>1</v>
+      </c>
+      <c r="I42" s="42">
+        <v>1</v>
+      </c>
+      <c r="J42" s="42">
+        <v>4</v>
+      </c>
+      <c r="K42" s="42"/>
+      <c r="L42" s="42">
+        <v>1</v>
+      </c>
+      <c r="M42" s="42">
+        <v>1</v>
+      </c>
+      <c r="N42" s="42">
+        <v>5</v>
+      </c>
+      <c r="O42" s="42">
+        <v>8</v>
+      </c>
+      <c r="P42" s="42">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>1</v>
+      </c>
+      <c r="R42" s="88" t="s">
+        <v>54</v>
+      </c>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3"/>
+    </row>
+    <row r="43" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="3"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+      <c r="L43" s="44"/>
+      <c r="M43" s="44"/>
+      <c r="N43" s="44"/>
+      <c r="O43" s="44"/>
+      <c r="P43" s="44"/>
+      <c r="Q43" s="44"/>
+      <c r="R43" s="44"/>
+      <c r="S43" s="44"/>
+      <c r="T43" s="44"/>
+      <c r="U43" s="84"/>
+      <c r="V43" s="84"/>
+      <c r="W43" s="84"/>
+      <c r="X43" s="84"/>
+      <c r="Y43" s="84"/>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B44" s="76" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" s="96">
+        <f>1+1+10+1+1+1+20+356+3</f>
+        <v>394</v>
+      </c>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B45" s="76" t="s">
+        <v>69</v>
+      </c>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="R34:U34"/>
+    <mergeCell ref="R42:U42"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="O34:Q34"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="83" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB061B5-D21D-4C41-A919-A7D4603E9923}">
+  <dimension ref="B1:AA45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.140625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.140625" style="2" customWidth="1"/>
+    <col min="20" max="21" width="5.7109375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="29" width="5.7109375" style="2" customWidth="1"/>
+    <col min="30" max="16384" width="8.7109375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="3"/>
+    </row>
+    <row r="2" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6">
+        <f>[1]DSSR!B4</f>
+        <v>1300</v>
+      </c>
+      <c r="D3" s="6">
+        <f>[1]DSSR!C4</f>
+        <v>1534</v>
+      </c>
+      <c r="E3" s="6">
+        <f>[1]DSSR!D4</f>
+        <v>1728</v>
+      </c>
+      <c r="F3" s="6">
+        <f>[1]DSSR!E4</f>
+        <v>1728</v>
+      </c>
+      <c r="G3" s="6">
+        <f>[1]DSSR!F4</f>
+        <v>1452</v>
+      </c>
+      <c r="H3" s="6">
+        <f>[1]DSSR!G4</f>
+        <v>1240</v>
+      </c>
+      <c r="I3" s="6">
+        <f>[1]DSSR!H4</f>
+        <v>1520</v>
+      </c>
+      <c r="J3" s="6">
+        <f>[1]DSSR!I4</f>
+        <v>978</v>
+      </c>
+      <c r="K3" s="6">
+        <f>[1]DSSR!J4</f>
+        <v>945</v>
+      </c>
+      <c r="L3" s="6">
+        <f>[1]DSSR!K4</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="6">
+        <f>[1]DSSR!L4</f>
+        <v>1127</v>
+      </c>
+      <c r="N3" s="6">
+        <f>[1]DSSR!M4</f>
+        <v>773</v>
+      </c>
+      <c r="O3" s="6">
+        <f>[1]DSSR!N4</f>
+        <v>1038</v>
+      </c>
+      <c r="P3" s="6">
+        <f>[1]DSSR!O4</f>
+        <v>773</v>
+      </c>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6">
+        <f>[1]DSSR!P4</f>
+        <v>1038</v>
+      </c>
+      <c r="U3" s="6">
+        <f>[1]DSSR!Q4</f>
+        <v>773</v>
+      </c>
+      <c r="V3" s="6">
+        <f>[1]DSSR!R4</f>
+        <v>1038</v>
+      </c>
+      <c r="W3" s="6">
+        <f>[1]DSSR!S4</f>
+        <v>792</v>
+      </c>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6">
+        <f>[1]DSSR!T4</f>
+        <v>948</v>
+      </c>
+    </row>
+    <row r="4" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6">
+        <f>[1]DSSR!B5</f>
+        <v>120</v>
+      </c>
+      <c r="D4" s="6">
+        <f>[1]DSSR!C5</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="6">
+        <f>[1]DSSR!D5</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <f>[1]DSSR!E5</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="6">
+        <f>[1]DSSR!F5</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
+        <f>[1]DSSR!G5</f>
+        <v>120</v>
+      </c>
+      <c r="I4" s="6">
+        <f>[1]DSSR!H5</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <f>[1]DSSR!I5</f>
+        <v>120</v>
+      </c>
+      <c r="K4" s="6">
+        <f>[1]DSSR!J5</f>
+        <v>120</v>
+      </c>
+      <c r="L4" s="6">
+        <f>[1]DSSR!K5</f>
+        <v>111</v>
+      </c>
+      <c r="M4" s="6">
+        <f>[1]DSSR!L5</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="6">
+        <f>[1]DSSR!M5</f>
+        <v>120</v>
+      </c>
+      <c r="O4" s="6">
+        <f>[1]DSSR!N5</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="6">
+        <f>[1]DSSR!O5</f>
+        <v>120</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6">
+        <f>[1]DSSR!P5</f>
+        <v>0</v>
+      </c>
+      <c r="U4" s="6">
+        <f>[1]DSSR!Q5</f>
+        <v>120</v>
+      </c>
+      <c r="V4" s="6">
+        <f>[1]DSSR!R5</f>
+        <v>0</v>
+      </c>
+      <c r="W4" s="6">
+        <f>[1]DSSR!S5</f>
+        <v>120</v>
+      </c>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6">
+        <f>[1]DSSR!T5</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="7">
+        <v>84</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7">
+        <v>84</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7">
+        <v>84</v>
+      </c>
+      <c r="K5" s="7">
+        <v>84</v>
+      </c>
+      <c r="L5" s="7">
+        <v>84</v>
+      </c>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7">
+        <v>84</v>
+      </c>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7">
+        <v>84</v>
+      </c>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7">
+        <v>84</v>
+      </c>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7">
+        <v>84</v>
+      </c>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="L6" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="R7" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="S7" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="T7" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="V7" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y7" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="12"/>
+      <c r="C8" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14">
+        <v>2</v>
+      </c>
+      <c r="F8" s="14">
+        <v>2</v>
+      </c>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14">
+        <v>13</v>
+      </c>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14">
+        <v>1</v>
+      </c>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="14">
+        <v>3</v>
+      </c>
+      <c r="X8" s="59"/>
+      <c r="Y8" s="15"/>
+    </row>
+    <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="60"/>
+      <c r="Y9" s="20"/>
+    </row>
+    <row r="10" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="60"/>
+      <c r="Y10" s="20"/>
+    </row>
+    <row r="11" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="16"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="60"/>
+      <c r="Y11" s="20"/>
+    </row>
+    <row r="12" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="60"/>
+      <c r="Y12" s="20"/>
+    </row>
+    <row r="13" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="60"/>
+      <c r="Y13" s="20"/>
+    </row>
+    <row r="14" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="16"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="19"/>
+      <c r="V14" s="19"/>
+      <c r="W14" s="19"/>
+      <c r="X14" s="60"/>
+      <c r="Y14" s="20"/>
+    </row>
+    <row r="15" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23">
+        <v>2</v>
+      </c>
+      <c r="F15" s="23">
+        <v>2</v>
+      </c>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23">
+        <v>5</v>
+      </c>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="T15" s="23">
+        <v>1</v>
+      </c>
+      <c r="U15" s="23"/>
+      <c r="V15" s="23"/>
+      <c r="W15" s="23">
+        <v>2</v>
+      </c>
+      <c r="X15" s="61"/>
+      <c r="Y15" s="24"/>
+    </row>
+    <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+      <c r="D16" s="58"/>
+      <c r="E16" s="27">
+        <v>0</v>
+      </c>
+      <c r="F16" s="27">
+        <v>0</v>
+      </c>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28">
+        <v>8</v>
+      </c>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
+      <c r="U16" s="28"/>
+      <c r="V16" s="28"/>
+      <c r="W16" s="56">
+        <v>1</v>
+      </c>
+      <c r="X16" s="62"/>
+      <c r="Y16" s="29"/>
+    </row>
+    <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="32"/>
+    </row>
+    <row r="18" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="34">
+        <f>[1]DSSR!B24</f>
+        <v>544</v>
+      </c>
+      <c r="D18" s="34">
+        <f>[1]DSSR!C24</f>
+        <v>1127</v>
+      </c>
+      <c r="E18" s="34">
+        <f>[1]DSSR!D24</f>
+        <v>853</v>
+      </c>
+      <c r="F18" s="34">
+        <f>[1]DSSR!E24</f>
+        <v>563</v>
+      </c>
+      <c r="G18" s="34">
+        <f>[1]DSSR!F24</f>
+        <v>575</v>
+      </c>
+      <c r="H18" s="34">
+        <f>[1]DSSR!G24</f>
+        <v>1175</v>
+      </c>
+      <c r="I18" s="34">
+        <f>[1]DSSR!H24</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="34">
+        <f>[1]DSSR!I24</f>
+        <v>791</v>
+      </c>
+      <c r="K18" s="34">
+        <f>[1]DSSR!J24</f>
+        <v>1102</v>
+      </c>
+      <c r="L18" s="34">
+        <f>[1]DSSR!K24</f>
+        <v>520</v>
+      </c>
+      <c r="M18" s="34">
+        <f>[1]DSSR!L24</f>
+        <v>1142</v>
+      </c>
+      <c r="N18" s="34">
+        <f>[1]DSSR!M24</f>
+        <v>205</v>
+      </c>
+      <c r="O18" s="34">
+        <f>[1]DSSR!N24</f>
+        <v>205</v>
+      </c>
+      <c r="P18" s="34">
+        <f>[1]DSSR!O24</f>
+        <v>205</v>
+      </c>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="34"/>
+      <c r="S18" s="34"/>
+      <c r="T18" s="34">
+        <f>[1]DSSR!P24</f>
+        <v>500</v>
+      </c>
+      <c r="U18" s="34">
+        <f>[1]DSSR!Q24</f>
+        <v>650</v>
+      </c>
+      <c r="V18" s="34">
+        <f>[1]DSSR!R24</f>
+        <v>650</v>
+      </c>
+      <c r="W18" s="34">
+        <f>[1]DSSR!S24</f>
+        <v>500</v>
+      </c>
+      <c r="X18" s="34"/>
+      <c r="Y18" s="35">
+        <f>[1]DSSR!T24</f>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="34">
+        <f>[1]DSSR!B25</f>
+        <v>111</v>
+      </c>
+      <c r="D19" s="34">
+        <f>[1]DSSR!C25</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="34">
+        <f>[1]DSSR!D25</f>
+        <v>120</v>
+      </c>
+      <c r="F19" s="34">
+        <f>[1]DSSR!E25</f>
+        <v>111</v>
+      </c>
+      <c r="G19" s="34">
+        <f>[1]DSSR!F25</f>
+        <v>111</v>
+      </c>
+      <c r="H19" s="34">
+        <f>[1]DSSR!G25</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="34">
+        <f>[1]DSSR!H25</f>
+        <v>111</v>
+      </c>
+      <c r="J19" s="34">
+        <f>[1]DSSR!I25</f>
+        <v>120</v>
+      </c>
+      <c r="K19" s="34">
+        <f>[1]DSSR!J25</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="34">
+        <f>[1]DSSR!K25</f>
+        <v>111</v>
+      </c>
+      <c r="M19" s="34">
+        <f>[1]DSSR!L25</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="34">
+        <f>[1]DSSR!M25</f>
+        <v>78</v>
+      </c>
+      <c r="O19" s="34">
+        <f>[1]DSSR!N25</f>
+        <v>78</v>
+      </c>
+      <c r="P19" s="34">
+        <f>[1]DSSR!O25</f>
+        <v>78</v>
+      </c>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+      <c r="S19" s="34"/>
+      <c r="T19" s="34">
+        <f>[1]DSSR!P25</f>
+        <v>120</v>
+      </c>
+      <c r="U19" s="34">
+        <f>[1]DSSR!Q25</f>
+        <v>0</v>
+      </c>
+      <c r="V19" s="34">
+        <f>[1]DSSR!R25</f>
+        <v>0</v>
+      </c>
+      <c r="W19" s="34">
+        <f>[1]DSSR!S25</f>
+        <v>120</v>
+      </c>
+      <c r="X19" s="34"/>
+      <c r="Y19" s="35">
+        <f>[1]DSSR!T25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="34">
+        <v>84</v>
+      </c>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34">
+        <v>84</v>
+      </c>
+      <c r="F20" s="34">
+        <v>84</v>
+      </c>
+      <c r="G20" s="34">
+        <v>84</v>
+      </c>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34">
+        <v>84</v>
+      </c>
+      <c r="J20" s="34">
+        <v>84</v>
+      </c>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34">
+        <v>84</v>
+      </c>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34">
+        <v>42</v>
+      </c>
+      <c r="O20" s="34">
+        <v>42</v>
+      </c>
+      <c r="P20" s="34">
+        <v>42</v>
+      </c>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="34"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="34">
+        <v>84</v>
+      </c>
+      <c r="U20" s="34"/>
+      <c r="V20" s="34"/>
+      <c r="W20" s="34">
+        <v>84</v>
+      </c>
+      <c r="X20" s="34"/>
+      <c r="Y20" s="35"/>
+    </row>
+    <row r="21" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="F21" s="36">
+        <f>4.5/2</f>
+        <v>2.25</v>
+      </c>
+      <c r="G21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="J21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="O21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="P21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+      <c r="S21" s="34"/>
+      <c r="T21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="U21" s="34"/>
+      <c r="V21" s="34"/>
+      <c r="W21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="X21" s="34"/>
+      <c r="Y21" s="35"/>
+    </row>
+    <row r="22" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="33"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="34"/>
+      <c r="S22" s="34"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="34"/>
+      <c r="V22" s="34"/>
+      <c r="W22" s="34"/>
+      <c r="X22" s="34"/>
+      <c r="Y22" s="35"/>
+    </row>
+    <row r="23" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="37"/>
+      <c r="C23" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O23" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P23" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q23" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="R23" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="V23" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="11"/>
+    </row>
+    <row r="24" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="79" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14">
+        <v>38</v>
+      </c>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14">
+        <v>406</v>
+      </c>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14">
+        <v>1</v>
+      </c>
+      <c r="P24" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="14"/>
+      <c r="Y24" s="15"/>
+    </row>
+    <row r="25" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="17"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="19"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="19"/>
+      <c r="X25" s="60"/>
+      <c r="Y25" s="20"/>
+    </row>
+    <row r="26" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="16"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="19"/>
+      <c r="U26" s="19"/>
+      <c r="V26" s="19"/>
+      <c r="W26" s="19"/>
+      <c r="X26" s="60"/>
+      <c r="Y26" s="20"/>
+    </row>
+    <row r="27" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="16"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="19"/>
+      <c r="U27" s="19"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="19"/>
+      <c r="X27" s="60"/>
+      <c r="Y27" s="20"/>
+    </row>
+    <row r="28" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="16"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="19"/>
+      <c r="X28" s="60"/>
+      <c r="Y28" s="20"/>
+    </row>
+    <row r="29" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="16"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="19"/>
+      <c r="W29" s="19"/>
+      <c r="X29" s="60"/>
+      <c r="Y29" s="20"/>
+    </row>
+    <row r="30" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="16"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="19"/>
+      <c r="U30" s="19"/>
+      <c r="V30" s="19"/>
+      <c r="W30" s="19"/>
+      <c r="X30" s="60"/>
+      <c r="Y30" s="20"/>
+    </row>
+    <row r="31" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23">
+        <v>12</v>
+      </c>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="23">
+        <v>1</v>
+      </c>
+      <c r="L31" s="23"/>
+      <c r="M31" s="23">
+        <v>152</v>
+      </c>
+      <c r="N31" s="23"/>
+      <c r="O31" s="23">
+        <v>1</v>
+      </c>
+      <c r="P31" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="23"/>
+      <c r="S31" s="23"/>
+      <c r="T31" s="23"/>
+      <c r="U31" s="23"/>
+      <c r="V31" s="23"/>
+      <c r="W31" s="23"/>
+      <c r="X31" s="61"/>
+      <c r="Y31" s="24"/>
+    </row>
+    <row r="32" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="26"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27">
+        <v>1</v>
+      </c>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28">
+        <v>26</v>
+      </c>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28">
+        <v>1</v>
+      </c>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28">
+        <v>254</v>
+      </c>
+      <c r="N32" s="28"/>
+      <c r="O32" s="23">
+        <v>0</v>
+      </c>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="28"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="63"/>
+      <c r="Y32" s="29"/>
+    </row>
+    <row r="33" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="30"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="68"/>
+      <c r="S33" s="68"/>
+      <c r="T33" s="68"/>
+      <c r="U33" s="68"/>
+      <c r="V33" s="31"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="31"/>
+      <c r="Y33" s="31"/>
+    </row>
+    <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="90" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="92" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
+        <v>46</v>
+      </c>
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
+        <v>47</v>
+      </c>
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
+        <v>48</v>
+      </c>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
+      <c r="V34" s="66"/>
+      <c r="W34" s="3"/>
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
+    </row>
+    <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="91"/>
+      <c r="C35" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="G35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="J35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="K35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="L35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="M35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="N35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="O35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="P35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q35" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="R35" s="69"/>
+      <c r="S35" s="70"/>
+      <c r="T35" s="70"/>
+      <c r="U35" s="71"/>
+      <c r="V35" s="84"/>
+      <c r="W35" s="84"/>
+      <c r="X35" s="84"/>
+      <c r="Y35" s="84"/>
+    </row>
+    <row r="36" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="46"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42">
+        <v>364</v>
+      </c>
+      <c r="G36" s="42">
+        <v>6</v>
+      </c>
+      <c r="H36" s="42">
+        <v>1</v>
+      </c>
+      <c r="I36" s="42">
+        <v>5</v>
+      </c>
+      <c r="J36" s="42"/>
+      <c r="K36" s="42"/>
+      <c r="L36" s="42">
+        <v>3</v>
+      </c>
+      <c r="M36" s="42"/>
+      <c r="N36" s="42"/>
+      <c r="O36" s="42">
+        <v>3</v>
+      </c>
+      <c r="P36" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>5</v>
+      </c>
+      <c r="R36" s="72"/>
+      <c r="S36" s="44"/>
+      <c r="T36" s="44"/>
+      <c r="U36" s="84"/>
+      <c r="V36" s="84"/>
+      <c r="W36" s="84"/>
+      <c r="X36" s="84"/>
+      <c r="Y36" s="84"/>
+    </row>
+    <row r="37" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="53"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="48"/>
+      <c r="M37" s="48"/>
+      <c r="N37" s="48"/>
+      <c r="O37" s="48"/>
+      <c r="P37" s="48"/>
+      <c r="Q37" s="64"/>
+      <c r="R37" s="72"/>
+      <c r="S37" s="44"/>
+      <c r="T37" s="44"/>
+      <c r="U37" s="84"/>
+      <c r="V37" s="84"/>
+      <c r="W37" s="84"/>
+      <c r="X37" s="84"/>
+      <c r="Y37" s="84"/>
+    </row>
+    <row r="38" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="53"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="19"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="20"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="44"/>
+      <c r="T38" s="44"/>
+      <c r="U38" s="84"/>
+      <c r="V38" s="84"/>
+      <c r="W38" s="84"/>
+      <c r="X38" s="84"/>
+      <c r="Y38" s="84"/>
+    </row>
+    <row r="39" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="53"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="44"/>
+      <c r="T39" s="44"/>
+      <c r="U39" s="84"/>
+      <c r="V39" s="84"/>
+      <c r="W39" s="84"/>
+      <c r="X39" s="84"/>
+      <c r="Y39" s="84"/>
+    </row>
+    <row r="40" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="53"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="72"/>
+      <c r="S40" s="44"/>
+      <c r="T40" s="44"/>
+      <c r="U40" s="84"/>
+      <c r="V40" s="84"/>
+      <c r="W40" s="84"/>
+      <c r="X40" s="84"/>
+      <c r="Y40" s="84"/>
+    </row>
+    <row r="41" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="54"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="40"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="40"/>
+      <c r="M41" s="40"/>
+      <c r="N41" s="40"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="65"/>
+      <c r="R41" s="73"/>
+      <c r="S41" s="74"/>
+      <c r="T41" s="74"/>
+      <c r="U41" s="75"/>
+      <c r="V41" s="84"/>
+      <c r="W41" s="84"/>
+      <c r="X41" s="84"/>
+      <c r="Y41" s="84"/>
+    </row>
+    <row r="42" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="46"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42">
+        <v>364</v>
+      </c>
+      <c r="G42" s="42">
+        <v>6</v>
+      </c>
+      <c r="H42" s="42">
+        <v>1</v>
+      </c>
+      <c r="I42" s="42">
+        <v>5</v>
+      </c>
+      <c r="J42" s="42"/>
+      <c r="K42" s="42"/>
+      <c r="L42" s="42">
+        <v>3</v>
+      </c>
+      <c r="M42" s="42"/>
+      <c r="N42" s="42"/>
+      <c r="O42" s="42">
+        <v>3</v>
+      </c>
+      <c r="P42" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>5</v>
+      </c>
+      <c r="R42" s="88" t="s">
+        <v>54</v>
+      </c>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3"/>
+    </row>
+    <row r="43" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="3"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+      <c r="L43" s="44"/>
+      <c r="M43" s="44"/>
+      <c r="N43" s="44"/>
+      <c r="O43" s="44"/>
+      <c r="P43" s="44"/>
+      <c r="Q43" s="44"/>
+      <c r="R43" s="44"/>
+      <c r="S43" s="44"/>
+      <c r="T43" s="44"/>
+      <c r="U43" s="84"/>
+      <c r="V43" s="84"/>
+      <c r="W43" s="84"/>
+      <c r="X43" s="84"/>
+      <c r="Y43" s="84"/>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B44" s="76" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" s="96">
+        <f>8+1+1+26+1+254</f>
+        <v>291</v>
+      </c>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B45" s="76" t="s">
+        <v>69</v>
+      </c>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="R34:U34"/>
+    <mergeCell ref="R42:U42"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="O34:Q34"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="90" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95239002-C6C6-4606-92B9-853EA4FA1F78}">
+  <dimension ref="B1:AA45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.140625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.140625" style="2" customWidth="1"/>
+    <col min="20" max="21" width="5.7109375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="29" width="5.7109375" style="2" customWidth="1"/>
+    <col min="30" max="16384" width="8.7109375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="3"/>
+    </row>
+    <row r="2" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6">
+        <f>[1]DSSR!B4</f>
+        <v>1300</v>
+      </c>
+      <c r="D3" s="6">
+        <f>[1]DSSR!C4</f>
+        <v>1534</v>
+      </c>
+      <c r="E3" s="6">
+        <f>[1]DSSR!D4</f>
+        <v>1728</v>
+      </c>
+      <c r="F3" s="6">
+        <f>[1]DSSR!E4</f>
+        <v>1728</v>
+      </c>
+      <c r="G3" s="6">
+        <f>[1]DSSR!F4</f>
+        <v>1452</v>
+      </c>
+      <c r="H3" s="6">
+        <f>[1]DSSR!G4</f>
+        <v>1240</v>
+      </c>
+      <c r="I3" s="6">
+        <f>[1]DSSR!H4</f>
+        <v>1520</v>
+      </c>
+      <c r="J3" s="6">
+        <f>[1]DSSR!I4</f>
+        <v>978</v>
+      </c>
+      <c r="K3" s="6">
+        <f>[1]DSSR!J4</f>
+        <v>945</v>
+      </c>
+      <c r="L3" s="6">
+        <f>[1]DSSR!K4</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="6">
+        <f>[1]DSSR!L4</f>
+        <v>1127</v>
+      </c>
+      <c r="N3" s="6">
+        <f>[1]DSSR!M4</f>
+        <v>773</v>
+      </c>
+      <c r="O3" s="6">
+        <f>[1]DSSR!N4</f>
+        <v>1038</v>
+      </c>
+      <c r="P3" s="6">
+        <f>[1]DSSR!O4</f>
+        <v>773</v>
+      </c>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6">
+        <f>[1]DSSR!P4</f>
+        <v>1038</v>
+      </c>
+      <c r="U3" s="6">
+        <f>[1]DSSR!Q4</f>
+        <v>773</v>
+      </c>
+      <c r="V3" s="6">
+        <f>[1]DSSR!R4</f>
+        <v>1038</v>
+      </c>
+      <c r="W3" s="6">
+        <f>[1]DSSR!S4</f>
+        <v>792</v>
+      </c>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6">
+        <f>[1]DSSR!T4</f>
+        <v>948</v>
+      </c>
+    </row>
+    <row r="4" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6">
+        <f>[1]DSSR!B5</f>
+        <v>120</v>
+      </c>
+      <c r="D4" s="6">
+        <f>[1]DSSR!C5</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="6">
+        <f>[1]DSSR!D5</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <f>[1]DSSR!E5</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="6">
+        <f>[1]DSSR!F5</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
+        <f>[1]DSSR!G5</f>
+        <v>120</v>
+      </c>
+      <c r="I4" s="6">
+        <f>[1]DSSR!H5</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <f>[1]DSSR!I5</f>
+        <v>120</v>
+      </c>
+      <c r="K4" s="6">
+        <f>[1]DSSR!J5</f>
+        <v>120</v>
+      </c>
+      <c r="L4" s="6">
+        <f>[1]DSSR!K5</f>
+        <v>111</v>
+      </c>
+      <c r="M4" s="6">
+        <f>[1]DSSR!L5</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="6">
+        <f>[1]DSSR!M5</f>
+        <v>120</v>
+      </c>
+      <c r="O4" s="6">
+        <f>[1]DSSR!N5</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="6">
+        <f>[1]DSSR!O5</f>
+        <v>120</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6">
+        <f>[1]DSSR!P5</f>
+        <v>0</v>
+      </c>
+      <c r="U4" s="6">
+        <f>[1]DSSR!Q5</f>
+        <v>120</v>
+      </c>
+      <c r="V4" s="6">
+        <f>[1]DSSR!R5</f>
+        <v>0</v>
+      </c>
+      <c r="W4" s="6">
+        <f>[1]DSSR!S5</f>
+        <v>120</v>
+      </c>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6">
+        <f>[1]DSSR!T5</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="7">
+        <v>84</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7">
+        <v>84</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7">
+        <v>84</v>
+      </c>
+      <c r="K5" s="7">
+        <v>84</v>
+      </c>
+      <c r="L5" s="7">
+        <v>84</v>
+      </c>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7">
+        <v>84</v>
+      </c>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7">
+        <v>84</v>
+      </c>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7">
+        <v>84</v>
+      </c>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7">
+        <v>84</v>
+      </c>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="L6" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="R7" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="S7" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="T7" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="V7" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y7" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="12"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14">
+        <v>2</v>
+      </c>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14">
+        <v>20</v>
+      </c>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14">
+        <v>2</v>
+      </c>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="14">
+        <v>4</v>
+      </c>
+      <c r="X8" s="59">
+        <v>2</v>
+      </c>
+      <c r="Y8" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="60"/>
+      <c r="Y9" s="20"/>
+    </row>
+    <row r="10" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="60"/>
+      <c r="Y10" s="20"/>
+    </row>
+    <row r="11" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="16"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="60"/>
+      <c r="Y11" s="20"/>
+    </row>
+    <row r="12" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="60"/>
+      <c r="Y12" s="20"/>
+    </row>
+    <row r="13" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="60"/>
+      <c r="Y13" s="20"/>
+    </row>
+    <row r="14" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="16"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="19"/>
+      <c r="V14" s="19"/>
+      <c r="W14" s="19"/>
+      <c r="X14" s="60"/>
+      <c r="Y14" s="20"/>
+    </row>
+    <row r="15" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23">
+        <v>2</v>
+      </c>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="T15" s="23">
+        <v>2</v>
+      </c>
+      <c r="U15" s="23"/>
+      <c r="V15" s="23"/>
+      <c r="W15" s="23">
+        <v>0</v>
+      </c>
+      <c r="X15" s="61">
+        <v>2</v>
+      </c>
+      <c r="Y15" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="57"/>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
+      <c r="U16" s="28"/>
+      <c r="V16" s="28"/>
+      <c r="W16" s="56">
+        <v>4</v>
+      </c>
+      <c r="X16" s="62">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="32"/>
+    </row>
+    <row r="18" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="34">
+        <f>[1]DSSR!B24</f>
+        <v>544</v>
+      </c>
+      <c r="D18" s="34">
+        <f>[1]DSSR!C24</f>
+        <v>1127</v>
+      </c>
+      <c r="E18" s="34">
+        <f>[1]DSSR!D24</f>
+        <v>853</v>
+      </c>
+      <c r="F18" s="34">
+        <f>[1]DSSR!E24</f>
+        <v>563</v>
+      </c>
+      <c r="G18" s="34">
+        <f>[1]DSSR!F24</f>
+        <v>575</v>
+      </c>
+      <c r="H18" s="34">
+        <f>[1]DSSR!G24</f>
+        <v>1175</v>
+      </c>
+      <c r="I18" s="34">
+        <f>[1]DSSR!H24</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="34">
+        <f>[1]DSSR!I24</f>
+        <v>791</v>
+      </c>
+      <c r="K18" s="34">
+        <f>[1]DSSR!J24</f>
+        <v>1102</v>
+      </c>
+      <c r="L18" s="34">
+        <f>[1]DSSR!K24</f>
+        <v>520</v>
+      </c>
+      <c r="M18" s="34">
+        <f>[1]DSSR!L24</f>
+        <v>1142</v>
+      </c>
+      <c r="N18" s="34">
+        <f>[1]DSSR!M24</f>
+        <v>205</v>
+      </c>
+      <c r="O18" s="34">
+        <f>[1]DSSR!N24</f>
+        <v>205</v>
+      </c>
+      <c r="P18" s="34">
+        <f>[1]DSSR!O24</f>
+        <v>205</v>
+      </c>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="34"/>
+      <c r="S18" s="34"/>
+      <c r="T18" s="34">
+        <f>[1]DSSR!P24</f>
+        <v>500</v>
+      </c>
+      <c r="U18" s="34">
+        <f>[1]DSSR!Q24</f>
+        <v>650</v>
+      </c>
+      <c r="V18" s="34">
+        <f>[1]DSSR!R24</f>
+        <v>650</v>
+      </c>
+      <c r="W18" s="34">
+        <f>[1]DSSR!S24</f>
+        <v>500</v>
+      </c>
+      <c r="X18" s="34"/>
+      <c r="Y18" s="35">
+        <f>[1]DSSR!T24</f>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="34">
+        <f>[1]DSSR!B25</f>
+        <v>111</v>
+      </c>
+      <c r="D19" s="34">
+        <f>[1]DSSR!C25</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="34">
+        <f>[1]DSSR!D25</f>
+        <v>120</v>
+      </c>
+      <c r="F19" s="34">
+        <f>[1]DSSR!E25</f>
+        <v>111</v>
+      </c>
+      <c r="G19" s="34">
+        <f>[1]DSSR!F25</f>
+        <v>111</v>
+      </c>
+      <c r="H19" s="34">
+        <f>[1]DSSR!G25</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="34">
+        <f>[1]DSSR!H25</f>
+        <v>111</v>
+      </c>
+      <c r="J19" s="34">
+        <f>[1]DSSR!I25</f>
+        <v>120</v>
+      </c>
+      <c r="K19" s="34">
+        <f>[1]DSSR!J25</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="34">
+        <f>[1]DSSR!K25</f>
+        <v>111</v>
+      </c>
+      <c r="M19" s="34">
+        <f>[1]DSSR!L25</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="34">
+        <f>[1]DSSR!M25</f>
+        <v>78</v>
+      </c>
+      <c r="O19" s="34">
+        <f>[1]DSSR!N25</f>
+        <v>78</v>
+      </c>
+      <c r="P19" s="34">
+        <f>[1]DSSR!O25</f>
+        <v>78</v>
+      </c>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+      <c r="S19" s="34"/>
+      <c r="T19" s="34">
+        <f>[1]DSSR!P25</f>
+        <v>120</v>
+      </c>
+      <c r="U19" s="34">
+        <f>[1]DSSR!Q25</f>
+        <v>0</v>
+      </c>
+      <c r="V19" s="34">
+        <f>[1]DSSR!R25</f>
+        <v>0</v>
+      </c>
+      <c r="W19" s="34">
+        <f>[1]DSSR!S25</f>
+        <v>120</v>
+      </c>
+      <c r="X19" s="34"/>
+      <c r="Y19" s="35">
+        <f>[1]DSSR!T25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="34">
+        <v>84</v>
+      </c>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34">
+        <v>84</v>
+      </c>
+      <c r="F20" s="34">
+        <v>84</v>
+      </c>
+      <c r="G20" s="34">
+        <v>84</v>
+      </c>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34">
+        <v>84</v>
+      </c>
+      <c r="J20" s="34">
+        <v>84</v>
+      </c>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34">
+        <v>84</v>
+      </c>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34">
+        <v>42</v>
+      </c>
+      <c r="O20" s="34">
+        <v>42</v>
+      </c>
+      <c r="P20" s="34">
+        <v>42</v>
+      </c>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="34"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="34">
+        <v>84</v>
+      </c>
+      <c r="U20" s="34"/>
+      <c r="V20" s="34"/>
+      <c r="W20" s="34">
+        <v>84</v>
+      </c>
+      <c r="X20" s="34"/>
+      <c r="Y20" s="35"/>
+    </row>
+    <row r="21" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="F21" s="36">
+        <f>4.5/2</f>
+        <v>2.25</v>
+      </c>
+      <c r="G21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="J21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="O21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="P21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+      <c r="S21" s="34"/>
+      <c r="T21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="U21" s="34"/>
+      <c r="V21" s="34"/>
+      <c r="W21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="X21" s="34"/>
+      <c r="Y21" s="35"/>
+    </row>
+    <row r="22" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="33"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="34"/>
+      <c r="S22" s="34"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="34"/>
+      <c r="V22" s="34"/>
+      <c r="W22" s="34"/>
+      <c r="X22" s="34"/>
+      <c r="Y22" s="35"/>
+    </row>
+    <row r="23" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="37"/>
+      <c r="C23" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O23" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P23" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q23" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="R23" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="V23" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="11"/>
+    </row>
+    <row r="24" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14">
+        <v>3</v>
+      </c>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14">
+        <v>34</v>
+      </c>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14">
+        <v>421</v>
+      </c>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="14"/>
+      <c r="Y24" s="15"/>
+    </row>
+    <row r="25" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="17"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="19"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="19"/>
+      <c r="X25" s="60"/>
+      <c r="Y25" s="20"/>
+    </row>
+    <row r="26" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="16"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="19"/>
+      <c r="U26" s="19"/>
+      <c r="V26" s="19"/>
+      <c r="W26" s="19"/>
+      <c r="X26" s="60"/>
+      <c r="Y26" s="20"/>
+    </row>
+    <row r="27" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="16"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="19"/>
+      <c r="U27" s="19"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="19"/>
+      <c r="X27" s="60"/>
+      <c r="Y27" s="20"/>
+    </row>
+    <row r="28" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="16"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="19"/>
+      <c r="X28" s="60"/>
+      <c r="Y28" s="20"/>
+    </row>
+    <row r="29" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="16"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="19"/>
+      <c r="W29" s="19"/>
+      <c r="X29" s="60"/>
+      <c r="Y29" s="20"/>
+    </row>
+    <row r="30" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="16"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="19"/>
+      <c r="U30" s="19"/>
+      <c r="V30" s="19"/>
+      <c r="W30" s="19"/>
+      <c r="X30" s="60"/>
+      <c r="Y30" s="20"/>
+    </row>
+    <row r="31" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23">
+        <v>3</v>
+      </c>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23">
+        <v>25</v>
+      </c>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="23">
+        <v>2</v>
+      </c>
+      <c r="L31" s="23"/>
+      <c r="M31" s="23">
+        <v>288</v>
+      </c>
+      <c r="N31" s="23"/>
+      <c r="O31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="23"/>
+      <c r="S31" s="23"/>
+      <c r="T31" s="23"/>
+      <c r="U31" s="23"/>
+      <c r="V31" s="23"/>
+      <c r="W31" s="23"/>
+      <c r="X31" s="61"/>
+      <c r="Y31" s="24"/>
+    </row>
+    <row r="32" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="26"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28">
+        <v>9</v>
+      </c>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28">
+        <v>133</v>
+      </c>
+      <c r="N32" s="28"/>
+      <c r="O32" s="23"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="28"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="63"/>
+      <c r="Y32" s="29"/>
+    </row>
+    <row r="33" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="30"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="68"/>
+      <c r="S33" s="68"/>
+      <c r="T33" s="68"/>
+      <c r="U33" s="68"/>
+      <c r="V33" s="31"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="31"/>
+      <c r="Y33" s="31"/>
+    </row>
+    <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="90" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="92" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
+        <v>46</v>
+      </c>
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
+        <v>47</v>
+      </c>
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
+        <v>48</v>
+      </c>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
+      <c r="V34" s="66"/>
+      <c r="W34" s="3"/>
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
+    </row>
+    <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="91"/>
+      <c r="C35" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="G35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="J35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="K35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="L35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="M35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="N35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="O35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="P35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q35" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="R35" s="69"/>
+      <c r="S35" s="70"/>
+      <c r="T35" s="70"/>
+      <c r="U35" s="71"/>
+      <c r="V35" s="84"/>
+      <c r="W35" s="84"/>
+      <c r="X35" s="84"/>
+      <c r="Y35" s="84"/>
+    </row>
+    <row r="36" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="46"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42">
+        <v>154</v>
+      </c>
+      <c r="G36" s="42">
+        <v>1</v>
+      </c>
+      <c r="H36" s="42">
+        <v>2</v>
+      </c>
+      <c r="I36" s="42">
+        <v>2</v>
+      </c>
+      <c r="J36" s="42"/>
+      <c r="K36" s="42">
+        <v>8</v>
+      </c>
+      <c r="L36" s="42">
+        <v>4</v>
+      </c>
+      <c r="M36" s="42"/>
+      <c r="N36" s="42"/>
+      <c r="O36" s="42">
+        <v>3</v>
+      </c>
+      <c r="P36" s="42">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>7</v>
+      </c>
+      <c r="R36" s="72"/>
+      <c r="S36" s="44"/>
+      <c r="T36" s="44"/>
+      <c r="U36" s="84"/>
+      <c r="V36" s="84"/>
+      <c r="W36" s="84"/>
+      <c r="X36" s="84"/>
+      <c r="Y36" s="84"/>
+    </row>
+    <row r="37" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="53"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="48"/>
+      <c r="M37" s="48"/>
+      <c r="N37" s="48"/>
+      <c r="O37" s="48"/>
+      <c r="P37" s="48"/>
+      <c r="Q37" s="64"/>
+      <c r="R37" s="72"/>
+      <c r="S37" s="44"/>
+      <c r="T37" s="44"/>
+      <c r="U37" s="84"/>
+      <c r="V37" s="84"/>
+      <c r="W37" s="84"/>
+      <c r="X37" s="84"/>
+      <c r="Y37" s="84"/>
+    </row>
+    <row r="38" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="53"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="19"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="20"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="44"/>
+      <c r="T38" s="44"/>
+      <c r="U38" s="84"/>
+      <c r="V38" s="84"/>
+      <c r="W38" s="84"/>
+      <c r="X38" s="84"/>
+      <c r="Y38" s="84"/>
+    </row>
+    <row r="39" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="53"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="44"/>
+      <c r="T39" s="44"/>
+      <c r="U39" s="84"/>
+      <c r="V39" s="84"/>
+      <c r="W39" s="84"/>
+      <c r="X39" s="84"/>
+      <c r="Y39" s="84"/>
+    </row>
+    <row r="40" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="53"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="72"/>
+      <c r="S40" s="44"/>
+      <c r="T40" s="44"/>
+      <c r="U40" s="84"/>
+      <c r="V40" s="84"/>
+      <c r="W40" s="84"/>
+      <c r="X40" s="84"/>
+      <c r="Y40" s="84"/>
+    </row>
+    <row r="41" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="54"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="40"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="40"/>
+      <c r="M41" s="40"/>
+      <c r="N41" s="40"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="65"/>
+      <c r="R41" s="73"/>
+      <c r="S41" s="74"/>
+      <c r="T41" s="74"/>
+      <c r="U41" s="75"/>
+      <c r="V41" s="84"/>
+      <c r="W41" s="84"/>
+      <c r="X41" s="84"/>
+      <c r="Y41" s="84"/>
+    </row>
+    <row r="42" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="46"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42">
+        <v>154</v>
+      </c>
+      <c r="G42" s="42">
+        <v>1</v>
+      </c>
+      <c r="H42" s="42">
+        <v>2</v>
+      </c>
+      <c r="I42" s="42">
+        <v>2</v>
+      </c>
+      <c r="J42" s="42"/>
+      <c r="K42" s="42">
+        <v>8</v>
+      </c>
+      <c r="L42" s="42">
+        <v>4</v>
+      </c>
+      <c r="M42" s="42"/>
+      <c r="N42" s="42"/>
+      <c r="O42" s="42">
+        <v>3</v>
+      </c>
+      <c r="P42" s="42">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>7</v>
+      </c>
+      <c r="R42" s="88" t="s">
+        <v>54</v>
+      </c>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3"/>
+    </row>
+    <row r="43" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="3"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+      <c r="L43" s="44"/>
+      <c r="M43" s="44"/>
+      <c r="N43" s="44"/>
+      <c r="O43" s="44"/>
+      <c r="P43" s="44"/>
+      <c r="Q43" s="44"/>
+      <c r="R43" s="44"/>
+      <c r="S43" s="44"/>
+      <c r="T43" s="44"/>
+      <c r="U43" s="84"/>
+      <c r="V43" s="84"/>
+      <c r="W43" s="84"/>
+      <c r="X43" s="84"/>
+      <c r="Y43" s="84"/>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B44" s="76" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" s="96">
+        <f>3+4+9+133</f>
+        <v>149</v>
+      </c>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B45" s="76" t="s">
+        <v>69</v>
+      </c>
+      <c r="C45" s="96">
+        <v>12</v>
+      </c>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -31762,47 +38578,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -32034,12 +38850,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -32075,17 +38891,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="C44" s="96"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -33463,47 +40279,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -33771,12 +40587,12 @@
       <c r="Q42" s="43">
         <v>9</v>
       </c>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -33812,22 +40628,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95">
+      <c r="C44" s="96">
         <f>10+5+1+54+8+256</f>
         <v>334</v>
       </c>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95">
+      <c r="C45" s="96">
         <v>12</v>
       </c>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -35205,47 +42021,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -35509,12 +42325,12 @@
       <c r="Q42" s="43">
         <v>1</v>
       </c>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -35550,22 +42366,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95">
+      <c r="C44" s="96">
         <f>12+5+2+378</f>
         <v>397</v>
       </c>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95">
+      <c r="C45" s="96">
         <v>12</v>
       </c>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -36862,47 +43678,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -37134,12 +43950,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -38469,47 +45285,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -38741,12 +45557,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -38782,17 +45598,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="C44" s="96"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -40158,47 +46974,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -40478,12 +47294,12 @@
       <c r="Q42" s="43">
         <v>16</v>
       </c>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -40519,20 +47335,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95">
+      <c r="C44" s="96">
         <f>2+5+1+2+1+25+46+10+282</f>
         <v>374</v>
       </c>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -41904,47 +48720,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93" t="s">
+      <c r="D34" s="92"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="91"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="93" t="s">
+      <c r="G34" s="92"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93" t="s">
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="94" t="s">
+      <c r="M34" s="92"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="84" t="s">
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
-      <c r="U34" s="86"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="87"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -42200,12 +49016,12 @@
       <c r="Q42" s="43">
         <v>17</v>
       </c>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
-      <c r="U42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="89"/>
+      <c r="U42" s="89"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -42241,20 +49057,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95">
+      <c r="C44" s="96">
         <f>8+1+53+6+271</f>
         <v>339</v>
       </c>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/GBDS JULY FILES 2026/CSR MONTH OF JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/CSR MONTH OF JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46010C4F-F820-4F25-BFBC-EB2697145DA3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{971D65E5-86FB-4A8E-B690-7BE3FD979448}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="24" activeTab="26" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="24" activeTab="32" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | JULY" sheetId="902" r:id="rId1"/>
@@ -43,8 +43,8 @@
     <sheet name="07-09 R2" sheetId="1817" r:id="rId28"/>
     <sheet name="07-09 R3" sheetId="1818" r:id="rId29"/>
     <sheet name="(10)" sheetId="1819" r:id="rId30"/>
-    <sheet name="07-10 R1" sheetId="1820" r:id="rId31"/>
-    <sheet name="07-10 R2" sheetId="1821" r:id="rId32"/>
+    <sheet name="07-10 R1 NO TRIP" sheetId="1820" r:id="rId31"/>
+    <sheet name="07-10 R2 NO TRIP" sheetId="1821" r:id="rId32"/>
     <sheet name="07-10 R3" sheetId="1822" r:id="rId33"/>
     <sheet name="(11)" sheetId="1823" r:id="rId34"/>
     <sheet name="07-11 R1" sheetId="1824" r:id="rId35"/>
@@ -85,8 +85,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="26">'07-09 R1'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="27">'07-09 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="28">'07-09 R3'!$A$1:$V$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="30">'07-10 R1'!$A$1:$Z$43</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="31">'07-10 R2'!$A$1:$V$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="30">'07-10 R1 NO TRIP'!$A$1:$Z$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="31">'07-10 R2 NO TRIP'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="32">'07-10 R3'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="34">'07-11 R1'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="35">'07-11 R2'!$A$1:$V$44</definedName>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3242" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3246" uniqueCount="95">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -387,6 +387,12 @@
   </si>
   <si>
     <t>DATE ___________07/11/2026___________</t>
+  </si>
+  <si>
+    <t>4/12B</t>
+  </si>
+  <si>
+    <t>13/12B</t>
   </si>
 </sst>
 </file>
@@ -44177,11 +44183,15 @@
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
       <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="D8" s="14">
+        <v>2</v>
+      </c>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>94</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -44193,12 +44203,20 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>2</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="W8" s="14">
+        <v>3</v>
+      </c>
+      <c r="X8" s="59">
+        <v>2</v>
+      </c>
+      <c r="Y8" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -44365,11 +44383,15 @@
         <v>25</v>
       </c>
       <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
+      <c r="D15" s="23">
+        <v>1</v>
+      </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>12</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -44381,23 +44403,35 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>2</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="W15" s="23">
+        <v>2</v>
+      </c>
+      <c r="X15" s="61">
+        <v>2</v>
+      </c>
+      <c r="Y15" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
       <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="D16" s="58">
+        <v>1</v>
+      </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>93</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -44409,12 +44443,20 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="29"/>
+      <c r="W16" s="56">
+        <v>1</v>
+      </c>
+      <c r="X16" s="62">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -44816,17 +44858,27 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>3</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>54</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
       <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="M24" s="14">
+        <v>396</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -45002,17 +45054,27 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>2</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>8</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
+      <c r="K31" s="23">
+        <v>0</v>
+      </c>
       <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="M31" s="23">
+        <v>120</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>79</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -45030,17 +45092,27 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>1</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>46</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
+      <c r="K32" s="28">
+        <v>2</v>
+      </c>
       <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="M32" s="28">
+        <v>276</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -45177,21 +45249,43 @@
       <c r="B36" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="46"/>
+      <c r="C36" s="46">
+        <v>1</v>
+      </c>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
+      <c r="F36" s="42">
+        <v>315</v>
+      </c>
+      <c r="G36" s="42">
+        <v>7</v>
+      </c>
+      <c r="H36" s="42">
+        <v>1</v>
+      </c>
+      <c r="I36" s="42">
+        <v>3</v>
+      </c>
+      <c r="J36" s="42">
+        <v>1</v>
+      </c>
+      <c r="K36" s="42">
+        <v>7</v>
+      </c>
+      <c r="L36" s="42">
+        <v>4</v>
+      </c>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="O36" s="42">
+        <v>7</v>
+      </c>
+      <c r="P36" s="42">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>10</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -45335,21 +45429,43 @@
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
+      <c r="C42" s="46">
+        <v>1</v>
+      </c>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
+      <c r="F42" s="42">
+        <v>315</v>
+      </c>
+      <c r="G42" s="42">
+        <v>7</v>
+      </c>
+      <c r="H42" s="42">
+        <v>1</v>
+      </c>
+      <c r="I42" s="42">
+        <v>3</v>
+      </c>
+      <c r="J42" s="42">
+        <v>1</v>
+      </c>
+      <c r="K42" s="42">
+        <v>7</v>
+      </c>
+      <c r="L42" s="42">
+        <v>4</v>
+      </c>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="O42" s="42">
+        <v>7</v>
+      </c>
+      <c r="P42" s="42">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>10</v>
+      </c>
       <c r="R42" s="89" t="s">
         <v>54</v>
       </c>
@@ -45391,7 +45507,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="97"/>
+      <c r="C44" s="97">
+        <f>1+4+1+1+46+2+276</f>
+        <v>331</v>
+      </c>
       <c r="D44" s="97"/>
       <c r="E44" s="97"/>
     </row>
@@ -45399,7 +45518,9 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="97"/>
+      <c r="C45" s="97">
+        <v>12</v>
+      </c>
       <c r="D45" s="97"/>
       <c r="E45" s="97"/>
     </row>

--- a/GBDS JULY FILES 2026/CSR MONTH OF JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/CSR MONTH OF JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41445D87-459D-4C42-9F92-7CDD71F2AE18}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB5440F-142C-450A-885A-A757194D8830}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="32" activeTab="40" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
@@ -58,9 +58,10 @@
     <sheet name="07-14 R1" sheetId="1832" r:id="rId43"/>
     <sheet name="07-14 R2" sheetId="1833" r:id="rId44"/>
     <sheet name="07-14 R3" sheetId="1834" r:id="rId45"/>
+    <sheet name="(15)" sheetId="1835" r:id="rId46"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId46"/>
+    <externalReference r:id="rId47"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'(1)'!$A$1:$Z$44</definedName>
@@ -68,6 +69,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="33">'(11)'!$A$1:$Z$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="37">'(13)'!$A$1:$Z$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="41">'(14)'!$A$1:$Z$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="45">'(15)'!$A$1:$Z$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'(2)'!$A$1:$Z$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'(3)'!$A$1:$Z$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'(6)'!$A$1:$Z$44</definedName>
@@ -124,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3967" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4053" uniqueCount="99">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -1041,7 +1043,7 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1296,6 +1298,9 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3172,47 +3177,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -3444,12 +3449,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -4833,47 +4838,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -5145,12 +5150,12 @@
       <c r="Q42" s="43">
         <v>3</v>
       </c>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -5186,22 +5191,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98">
+      <c r="C44" s="99">
         <f>1+1+6+1+8+1+16+404</f>
         <v>438</v>
       </c>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98">
+      <c r="C45" s="99">
         <v>12</v>
       </c>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -6573,47 +6578,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -6861,12 +6866,12 @@
       <c r="Q42" s="43">
         <v>11</v>
       </c>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -6902,22 +6907,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98">
+      <c r="C44" s="99">
         <f>8+1+30+2+322</f>
         <v>363</v>
       </c>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98">
+      <c r="C45" s="99">
         <v>12</v>
       </c>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -8295,47 +8300,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -8593,12 +8598,12 @@
       <c r="Q42" s="43">
         <v>16</v>
       </c>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -8634,17 +8639,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98"/>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98"/>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -9941,47 +9946,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -10213,12 +10218,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -11596,47 +11601,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -11920,12 +11925,12 @@
       <c r="Q42" s="43">
         <v>19</v>
       </c>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -11961,20 +11966,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98">
+      <c r="C44" s="99">
         <f>1+1+5+5+3+293</f>
         <v>308</v>
       </c>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98"/>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -13338,47 +13343,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -13634,12 +13639,12 @@
         <v>8</v>
       </c>
       <c r="Q42" s="43"/>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -13675,22 +13680,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98">
+      <c r="C44" s="99">
         <f>1+10+25+306</f>
         <v>342</v>
       </c>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98">
+      <c r="C45" s="99">
         <v>12</v>
       </c>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -15062,47 +15067,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -15354,12 +15359,12 @@
       <c r="Q42" s="43">
         <v>3</v>
       </c>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -15395,20 +15400,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98">
+      <c r="C44" s="99">
         <f>14+2+20+266</f>
         <v>302</v>
       </c>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98"/>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -16705,47 +16710,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -16977,12 +16982,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -18348,47 +18353,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -18644,12 +18649,12 @@
       <c r="Q42" s="43">
         <v>21</v>
       </c>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -18685,20 +18690,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98">
+      <c r="C44" s="99">
         <f>12+11+324</f>
         <v>347</v>
       </c>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98"/>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -19995,47 +20000,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -20267,12 +20272,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -21660,47 +21665,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -21956,12 +21961,12 @@
       <c r="Q42" s="43">
         <v>2</v>
       </c>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -21997,20 +22002,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98">
+      <c r="C44" s="99">
         <f>12+70+356</f>
         <v>438</v>
       </c>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98"/>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -23382,47 +23387,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -23710,12 +23715,12 @@
       <c r="Q42" s="43">
         <v>11</v>
       </c>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -23751,20 +23756,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98">
+      <c r="C44" s="99">
         <f>9+4+2+89+1+279</f>
         <v>384</v>
       </c>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98"/>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -25061,47 +25066,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -25333,12 +25338,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -26716,47 +26721,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -27020,12 +27025,12 @@
       <c r="Q42" s="43">
         <v>4</v>
       </c>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -27061,22 +27066,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98">
+      <c r="C44" s="99">
         <f>5+20+45+289</f>
         <v>359</v>
       </c>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98">
+      <c r="C45" s="99">
         <v>12</v>
       </c>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -28448,47 +28453,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -28752,12 +28757,12 @@
       <c r="Q42" s="43">
         <v>5</v>
       </c>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -28793,20 +28798,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98">
+      <c r="C44" s="99">
         <f>8+1+1+26+1+254</f>
         <v>291</v>
       </c>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98"/>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -30178,47 +30183,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -30482,12 +30487,12 @@
       <c r="Q42" s="43">
         <v>21</v>
       </c>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -30523,20 +30528,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98">
+      <c r="C44" s="99">
         <f>15+17+12+55+374</f>
         <v>473</v>
       </c>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98"/>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -31833,47 +31838,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -32105,12 +32110,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -33506,47 +33511,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -33826,12 +33831,12 @@
       <c r="Q42" s="43">
         <v>1</v>
       </c>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -33867,20 +33872,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98">
+      <c r="C44" s="99">
         <f>1+1+10+1+1+1+20+356+3</f>
         <v>394</v>
       </c>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98"/>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -35252,47 +35257,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -35556,12 +35561,12 @@
       <c r="Q42" s="43">
         <v>5</v>
       </c>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -35597,20 +35602,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98">
+      <c r="C44" s="99">
         <f>8+1+1+26+1+254</f>
         <v>291</v>
       </c>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98"/>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -36976,47 +36981,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -37284,12 +37289,12 @@
       <c r="Q42" s="43">
         <v>7</v>
       </c>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -37325,22 +37330,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98">
+      <c r="C44" s="99">
         <f>3+4+9+133</f>
         <v>149</v>
       </c>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98">
+      <c r="C45" s="99">
         <v>12</v>
       </c>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -38642,47 +38647,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -38914,12 +38919,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -38955,17 +38960,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98"/>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98"/>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -40262,47 +40267,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -40534,12 +40539,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -41869,47 +41874,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -42141,12 +42146,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -42182,17 +42187,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98"/>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98"/>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -43492,47 +43497,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -43764,12 +43769,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -43805,17 +43810,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98"/>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98"/>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -45181,47 +45186,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -45497,12 +45502,12 @@
       <c r="Q42" s="43">
         <v>10</v>
       </c>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -45538,22 +45543,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98">
+      <c r="C44" s="99">
         <f>1+4+1+1+46+2+276</f>
         <v>331</v>
       </c>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98">
+      <c r="C45" s="99">
         <v>12</v>
       </c>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -46850,47 +46855,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -47122,12 +47127,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -48457,47 +48462,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -48729,12 +48734,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -48770,17 +48775,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98"/>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98"/>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -50080,47 +50085,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -50352,12 +50357,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -50393,17 +50398,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98"/>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98"/>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -51703,47 +51708,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -51975,12 +51980,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -52016,17 +52021,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98"/>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98"/>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -53323,47 +53328,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -53595,12 +53600,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -54990,47 +54995,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -55310,12 +55315,12 @@
       <c r="Q42" s="43">
         <v>3</v>
       </c>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -55351,23 +55356,23 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98">
+      <c r="C44" s="99">
         <f>1+2+5+10+10+321</f>
         <v>349</v>
       </c>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98">
+      <c r="C45" s="99">
         <f>12</f>
         <v>12</v>
       </c>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -56745,47 +56750,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -57053,12 +57058,12 @@
       <c r="Q42" s="43">
         <v>9</v>
       </c>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -57094,22 +57099,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98">
+      <c r="C44" s="99">
         <f>10+5+1+54+8+256</f>
         <v>334</v>
       </c>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98">
+      <c r="C45" s="99">
         <v>12</v>
       </c>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -58487,47 +58492,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -58799,12 +58804,12 @@
         <v>5</v>
       </c>
       <c r="Q42" s="43"/>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -58840,23 +58845,23 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98">
+      <c r="C44" s="99">
         <f>9+27+317</f>
         <v>353</v>
       </c>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98">
+      <c r="C45" s="99">
         <f>12+12</f>
         <v>24</v>
       </c>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -60228,47 +60233,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -60536,12 +60541,12 @@
       </c>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -60577,23 +60582,23 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98">
+      <c r="C44" s="99">
         <f>17+3+59+438</f>
         <v>517</v>
       </c>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98">
+      <c r="C45" s="99">
         <f>12</f>
         <v>12</v>
       </c>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -61890,47 +61895,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -62162,12 +62167,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -63497,47 +63502,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -63769,12 +63774,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -63810,17 +63815,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98"/>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98"/>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -65120,47 +65125,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -65392,12 +65397,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -65433,17 +65438,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98"/>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98"/>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -66743,47 +66748,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -67015,12 +67020,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -67056,17 +67061,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98"/>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98"/>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -67084,6 +67089,1608 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="90" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1ADE195-D50D-4620-9E3C-5DF2483EE145}">
+  <dimension ref="B1:AA43"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
+    <col min="3" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.140625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.140625" style="2" customWidth="1"/>
+    <col min="20" max="21" width="5.7109375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="29" width="5.7109375" style="2" customWidth="1"/>
+    <col min="30" max="16384" width="8.7109375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="3"/>
+    </row>
+    <row r="2" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6">
+        <f>[1]DSSR!B4</f>
+        <v>1300</v>
+      </c>
+      <c r="D3" s="6">
+        <f>[1]DSSR!C4</f>
+        <v>1534</v>
+      </c>
+      <c r="E3" s="6">
+        <f>[1]DSSR!D4</f>
+        <v>1728</v>
+      </c>
+      <c r="F3" s="6">
+        <f>[1]DSSR!E4</f>
+        <v>1728</v>
+      </c>
+      <c r="G3" s="6">
+        <f>[1]DSSR!F4</f>
+        <v>1452</v>
+      </c>
+      <c r="H3" s="6">
+        <f>[1]DSSR!G4</f>
+        <v>1240</v>
+      </c>
+      <c r="I3" s="6">
+        <f>[1]DSSR!H4</f>
+        <v>1520</v>
+      </c>
+      <c r="J3" s="6">
+        <f>[1]DSSR!I4</f>
+        <v>978</v>
+      </c>
+      <c r="K3" s="6">
+        <f>[1]DSSR!J4</f>
+        <v>945</v>
+      </c>
+      <c r="L3" s="6">
+        <f>[1]DSSR!K4</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="6">
+        <f>[1]DSSR!L4</f>
+        <v>1127</v>
+      </c>
+      <c r="N3" s="6">
+        <f>[1]DSSR!M4</f>
+        <v>773</v>
+      </c>
+      <c r="O3" s="6">
+        <f>[1]DSSR!N4</f>
+        <v>1038</v>
+      </c>
+      <c r="P3" s="6">
+        <f>[1]DSSR!O4</f>
+        <v>773</v>
+      </c>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6">
+        <f>[1]DSSR!P4</f>
+        <v>1038</v>
+      </c>
+      <c r="U3" s="6">
+        <f>[1]DSSR!Q4</f>
+        <v>773</v>
+      </c>
+      <c r="V3" s="6">
+        <f>[1]DSSR!R4</f>
+        <v>1038</v>
+      </c>
+      <c r="W3" s="6">
+        <f>[1]DSSR!S4</f>
+        <v>792</v>
+      </c>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6">
+        <f>[1]DSSR!T4</f>
+        <v>948</v>
+      </c>
+    </row>
+    <row r="4" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6">
+        <f>[1]DSSR!B5</f>
+        <v>120</v>
+      </c>
+      <c r="D4" s="6">
+        <f>[1]DSSR!C5</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="6">
+        <f>[1]DSSR!D5</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <f>[1]DSSR!E5</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="6">
+        <f>[1]DSSR!F5</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
+        <f>[1]DSSR!G5</f>
+        <v>120</v>
+      </c>
+      <c r="I4" s="6">
+        <f>[1]DSSR!H5</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <f>[1]DSSR!I5</f>
+        <v>120</v>
+      </c>
+      <c r="K4" s="6">
+        <f>[1]DSSR!J5</f>
+        <v>120</v>
+      </c>
+      <c r="L4" s="6">
+        <f>[1]DSSR!K5</f>
+        <v>111</v>
+      </c>
+      <c r="M4" s="6">
+        <f>[1]DSSR!L5</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="6">
+        <f>[1]DSSR!M5</f>
+        <v>120</v>
+      </c>
+      <c r="O4" s="6">
+        <f>[1]DSSR!N5</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="6">
+        <f>[1]DSSR!O5</f>
+        <v>120</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6">
+        <f>[1]DSSR!P5</f>
+        <v>0</v>
+      </c>
+      <c r="U4" s="6">
+        <f>[1]DSSR!Q5</f>
+        <v>120</v>
+      </c>
+      <c r="V4" s="6">
+        <f>[1]DSSR!R5</f>
+        <v>0</v>
+      </c>
+      <c r="W4" s="6">
+        <f>[1]DSSR!S5</f>
+        <v>120</v>
+      </c>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6">
+        <f>[1]DSSR!T5</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="7">
+        <v>84</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7">
+        <v>84</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7">
+        <v>84</v>
+      </c>
+      <c r="K5" s="7">
+        <v>84</v>
+      </c>
+      <c r="L5" s="7">
+        <v>84</v>
+      </c>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7">
+        <v>84</v>
+      </c>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7">
+        <v>84</v>
+      </c>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7">
+        <v>84</v>
+      </c>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7">
+        <v>84</v>
+      </c>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="L6" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="8"/>
+      <c r="C7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="R7" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="S7" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="T7" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="V7" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y7" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="12"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="14"/>
+      <c r="X8" s="59"/>
+      <c r="Y8" s="15"/>
+    </row>
+    <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="60"/>
+      <c r="Y9" s="20"/>
+    </row>
+    <row r="10" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="60"/>
+      <c r="Y10" s="20"/>
+    </row>
+    <row r="11" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="16"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="60"/>
+      <c r="Y11" s="20"/>
+    </row>
+    <row r="12" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="60"/>
+      <c r="Y12" s="20"/>
+    </row>
+    <row r="13" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="60"/>
+      <c r="Y13" s="20"/>
+    </row>
+    <row r="14" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="16"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="19"/>
+      <c r="V14" s="19"/>
+      <c r="W14" s="19"/>
+      <c r="X14" s="60"/>
+      <c r="Y14" s="20"/>
+    </row>
+    <row r="15" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="T15" s="23"/>
+      <c r="U15" s="23"/>
+      <c r="V15" s="23"/>
+      <c r="W15" s="23"/>
+      <c r="X15" s="61"/>
+      <c r="Y15" s="24"/>
+    </row>
+    <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="57"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28"/>
+      <c r="U16" s="28"/>
+      <c r="V16" s="28"/>
+      <c r="W16" s="56"/>
+      <c r="X16" s="62"/>
+      <c r="Y16" s="29"/>
+    </row>
+    <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="32"/>
+    </row>
+    <row r="18" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="34">
+        <f>[1]DSSR!B24</f>
+        <v>544</v>
+      </c>
+      <c r="D18" s="34">
+        <f>[1]DSSR!C24</f>
+        <v>1127</v>
+      </c>
+      <c r="E18" s="34">
+        <f>[1]DSSR!D24</f>
+        <v>853</v>
+      </c>
+      <c r="F18" s="34">
+        <f>[1]DSSR!E24</f>
+        <v>563</v>
+      </c>
+      <c r="G18" s="34">
+        <f>[1]DSSR!F24</f>
+        <v>575</v>
+      </c>
+      <c r="H18" s="34">
+        <f>[1]DSSR!G24</f>
+        <v>1175</v>
+      </c>
+      <c r="I18" s="34">
+        <f>[1]DSSR!H24</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="34">
+        <f>[1]DSSR!I24</f>
+        <v>791</v>
+      </c>
+      <c r="K18" s="34">
+        <f>[1]DSSR!J24</f>
+        <v>1102</v>
+      </c>
+      <c r="L18" s="34">
+        <f>[1]DSSR!K24</f>
+        <v>520</v>
+      </c>
+      <c r="M18" s="34">
+        <f>[1]DSSR!L24</f>
+        <v>1142</v>
+      </c>
+      <c r="N18" s="34">
+        <f>[1]DSSR!M24</f>
+        <v>205</v>
+      </c>
+      <c r="O18" s="34">
+        <f>[1]DSSR!N24</f>
+        <v>205</v>
+      </c>
+      <c r="P18" s="34">
+        <f>[1]DSSR!O24</f>
+        <v>205</v>
+      </c>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="34"/>
+      <c r="S18" s="34"/>
+      <c r="T18" s="34">
+        <f>[1]DSSR!P24</f>
+        <v>500</v>
+      </c>
+      <c r="U18" s="34">
+        <f>[1]DSSR!Q24</f>
+        <v>650</v>
+      </c>
+      <c r="V18" s="34">
+        <f>[1]DSSR!R24</f>
+        <v>650</v>
+      </c>
+      <c r="W18" s="34">
+        <f>[1]DSSR!S24</f>
+        <v>500</v>
+      </c>
+      <c r="X18" s="34"/>
+      <c r="Y18" s="35">
+        <f>[1]DSSR!T24</f>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="34">
+        <f>[1]DSSR!B25</f>
+        <v>111</v>
+      </c>
+      <c r="D19" s="34">
+        <f>[1]DSSR!C25</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="34">
+        <f>[1]DSSR!D25</f>
+        <v>120</v>
+      </c>
+      <c r="F19" s="34">
+        <f>[1]DSSR!E25</f>
+        <v>111</v>
+      </c>
+      <c r="G19" s="34">
+        <f>[1]DSSR!F25</f>
+        <v>111</v>
+      </c>
+      <c r="H19" s="34">
+        <f>[1]DSSR!G25</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="34">
+        <f>[1]DSSR!H25</f>
+        <v>111</v>
+      </c>
+      <c r="J19" s="34">
+        <f>[1]DSSR!I25</f>
+        <v>120</v>
+      </c>
+      <c r="K19" s="34">
+        <f>[1]DSSR!J25</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="34">
+        <f>[1]DSSR!K25</f>
+        <v>111</v>
+      </c>
+      <c r="M19" s="34">
+        <f>[1]DSSR!L25</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="34">
+        <f>[1]DSSR!M25</f>
+        <v>78</v>
+      </c>
+      <c r="O19" s="34">
+        <f>[1]DSSR!N25</f>
+        <v>78</v>
+      </c>
+      <c r="P19" s="34">
+        <f>[1]DSSR!O25</f>
+        <v>78</v>
+      </c>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+      <c r="S19" s="34"/>
+      <c r="T19" s="34">
+        <f>[1]DSSR!P25</f>
+        <v>120</v>
+      </c>
+      <c r="U19" s="34">
+        <f>[1]DSSR!Q25</f>
+        <v>0</v>
+      </c>
+      <c r="V19" s="34">
+        <f>[1]DSSR!R25</f>
+        <v>0</v>
+      </c>
+      <c r="W19" s="34">
+        <f>[1]DSSR!S25</f>
+        <v>120</v>
+      </c>
+      <c r="X19" s="34"/>
+      <c r="Y19" s="35">
+        <f>[1]DSSR!T25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="34">
+        <v>84</v>
+      </c>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34">
+        <v>84</v>
+      </c>
+      <c r="F20" s="34">
+        <v>84</v>
+      </c>
+      <c r="G20" s="34">
+        <v>84</v>
+      </c>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34">
+        <v>84</v>
+      </c>
+      <c r="J20" s="34">
+        <v>84</v>
+      </c>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34">
+        <v>84</v>
+      </c>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34">
+        <v>42</v>
+      </c>
+      <c r="O20" s="34">
+        <v>42</v>
+      </c>
+      <c r="P20" s="34">
+        <v>42</v>
+      </c>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="34"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="34">
+        <v>84</v>
+      </c>
+      <c r="U20" s="34"/>
+      <c r="V20" s="34"/>
+      <c r="W20" s="34">
+        <v>84</v>
+      </c>
+      <c r="X20" s="34"/>
+      <c r="Y20" s="35"/>
+    </row>
+    <row r="21" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="F21" s="36">
+        <f>4.5/2</f>
+        <v>2.25</v>
+      </c>
+      <c r="G21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="J21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="O21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="P21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+      <c r="S21" s="34"/>
+      <c r="T21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="U21" s="34"/>
+      <c r="V21" s="34"/>
+      <c r="W21" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="X21" s="34"/>
+      <c r="Y21" s="35"/>
+    </row>
+    <row r="22" spans="2:25" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="33"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="34"/>
+      <c r="S22" s="34"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="34"/>
+      <c r="V22" s="34"/>
+      <c r="W22" s="34"/>
+      <c r="X22" s="34"/>
+      <c r="Y22" s="35"/>
+    </row>
+    <row r="23" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="37"/>
+      <c r="C23" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O23" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P23" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q23" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="R23" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="V23" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="11"/>
+    </row>
+    <row r="24" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="14"/>
+      <c r="Y24" s="15"/>
+    </row>
+    <row r="25" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="17"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="19"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="19"/>
+      <c r="X25" s="60"/>
+      <c r="Y25" s="20"/>
+    </row>
+    <row r="26" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="16"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="19"/>
+      <c r="U26" s="19"/>
+      <c r="V26" s="19"/>
+      <c r="W26" s="19"/>
+      <c r="X26" s="60"/>
+      <c r="Y26" s="20"/>
+    </row>
+    <row r="27" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="16"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="19"/>
+      <c r="U27" s="19"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="19"/>
+      <c r="X27" s="60"/>
+      <c r="Y27" s="20"/>
+    </row>
+    <row r="28" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="16"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="19"/>
+      <c r="X28" s="60"/>
+      <c r="Y28" s="20"/>
+    </row>
+    <row r="29" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="16"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="19"/>
+      <c r="W29" s="19"/>
+      <c r="X29" s="60"/>
+      <c r="Y29" s="20"/>
+    </row>
+    <row r="30" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="16"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="19"/>
+      <c r="U30" s="19"/>
+      <c r="V30" s="19"/>
+      <c r="W30" s="19"/>
+      <c r="X30" s="60"/>
+      <c r="Y30" s="20"/>
+    </row>
+    <row r="31" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
+      <c r="M31" s="23"/>
+      <c r="N31" s="23"/>
+      <c r="O31" s="23"/>
+      <c r="P31" s="23"/>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="23"/>
+      <c r="S31" s="23"/>
+      <c r="T31" s="23"/>
+      <c r="U31" s="23"/>
+      <c r="V31" s="23"/>
+      <c r="W31" s="23"/>
+      <c r="X31" s="61"/>
+      <c r="Y31" s="24"/>
+    </row>
+    <row r="32" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="26"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="23"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="28"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="63"/>
+      <c r="Y32" s="29"/>
+    </row>
+    <row r="33" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="30"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="68"/>
+      <c r="S33" s="68"/>
+      <c r="T33" s="68"/>
+      <c r="U33" s="68"/>
+      <c r="V33" s="31"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="31"/>
+      <c r="Y33" s="31"/>
+    </row>
+    <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="93" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="95" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
+        <v>46</v>
+      </c>
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
+        <v>47</v>
+      </c>
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
+        <v>48</v>
+      </c>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
+      <c r="V34" s="66"/>
+      <c r="W34" s="3"/>
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
+    </row>
+    <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="94"/>
+      <c r="C35" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="G35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="J35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="K35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="L35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="M35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="N35" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="O35" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="P35" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q35" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="R35" s="69"/>
+      <c r="S35" s="70"/>
+      <c r="T35" s="70"/>
+      <c r="U35" s="71"/>
+      <c r="V35" s="87"/>
+      <c r="W35" s="87"/>
+      <c r="X35" s="87"/>
+      <c r="Y35" s="87"/>
+    </row>
+    <row r="36" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="46"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="42"/>
+      <c r="L36" s="42"/>
+      <c r="M36" s="42"/>
+      <c r="N36" s="42"/>
+      <c r="O36" s="42"/>
+      <c r="P36" s="42"/>
+      <c r="Q36" s="43"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="44"/>
+      <c r="T36" s="44"/>
+      <c r="U36" s="87"/>
+      <c r="V36" s="87"/>
+      <c r="W36" s="87"/>
+      <c r="X36" s="87"/>
+      <c r="Y36" s="87"/>
+    </row>
+    <row r="37" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="53"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="48"/>
+      <c r="M37" s="48"/>
+      <c r="N37" s="48"/>
+      <c r="O37" s="48"/>
+      <c r="P37" s="48"/>
+      <c r="Q37" s="64"/>
+      <c r="R37" s="72"/>
+      <c r="S37" s="44"/>
+      <c r="T37" s="44"/>
+      <c r="U37" s="87"/>
+      <c r="V37" s="87"/>
+      <c r="W37" s="87"/>
+      <c r="X37" s="87"/>
+      <c r="Y37" s="87"/>
+    </row>
+    <row r="38" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="53"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="19"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="20"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="44"/>
+      <c r="T38" s="44"/>
+      <c r="U38" s="87"/>
+      <c r="V38" s="87"/>
+      <c r="W38" s="87"/>
+      <c r="X38" s="87"/>
+      <c r="Y38" s="87"/>
+    </row>
+    <row r="39" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="53"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="44"/>
+      <c r="T39" s="44"/>
+      <c r="U39" s="87"/>
+      <c r="V39" s="87"/>
+      <c r="W39" s="87"/>
+      <c r="X39" s="87"/>
+      <c r="Y39" s="87"/>
+    </row>
+    <row r="40" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="53"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="72"/>
+      <c r="S40" s="44"/>
+      <c r="T40" s="44"/>
+      <c r="U40" s="87"/>
+      <c r="V40" s="87"/>
+      <c r="W40" s="87"/>
+      <c r="X40" s="87"/>
+      <c r="Y40" s="87"/>
+    </row>
+    <row r="41" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="54"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="40"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="40"/>
+      <c r="M41" s="40"/>
+      <c r="N41" s="40"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="65"/>
+      <c r="R41" s="73"/>
+      <c r="S41" s="74"/>
+      <c r="T41" s="74"/>
+      <c r="U41" s="75"/>
+      <c r="V41" s="87"/>
+      <c r="W41" s="87"/>
+      <c r="X41" s="87"/>
+      <c r="Y41" s="87"/>
+    </row>
+    <row r="42" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="46"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="42"/>
+      <c r="I42" s="42"/>
+      <c r="J42" s="42"/>
+      <c r="K42" s="42"/>
+      <c r="L42" s="42"/>
+      <c r="M42" s="42"/>
+      <c r="N42" s="42"/>
+      <c r="O42" s="42"/>
+      <c r="P42" s="42"/>
+      <c r="Q42" s="43"/>
+      <c r="R42" s="91" t="s">
+        <v>54</v>
+      </c>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3"/>
+    </row>
+    <row r="43" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="3"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+      <c r="L43" s="44"/>
+      <c r="M43" s="44"/>
+      <c r="N43" s="44"/>
+      <c r="O43" s="44"/>
+      <c r="P43" s="44"/>
+      <c r="Q43" s="44"/>
+      <c r="R43" s="44"/>
+      <c r="S43" s="44"/>
+      <c r="T43" s="44"/>
+      <c r="U43" s="87"/>
+      <c r="V43" s="87"/>
+      <c r="W43" s="87"/>
+      <c r="X43" s="87"/>
+      <c r="Y43" s="87"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="R34:U34"/>
+    <mergeCell ref="R42:U42"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="O34:Q34"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="83" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -68444,47 +70051,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -68748,12 +70355,12 @@
       <c r="Q42" s="43">
         <v>1</v>
       </c>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -68789,22 +70396,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98">
+      <c r="C44" s="99">
         <f>12+5+2+378</f>
         <v>397</v>
       </c>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98">
+      <c r="C45" s="99">
         <v>12</v>
       </c>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -70101,47 +71708,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -70373,12 +71980,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -71708,47 +73315,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -71980,12 +73587,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -72021,17 +73628,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98"/>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98"/>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -73397,47 +75004,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -73717,12 +75324,12 @@
       <c r="Q42" s="43">
         <v>16</v>
       </c>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -73758,20 +75365,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98">
+      <c r="C44" s="99">
         <f>2+5+1+2+1+25+46+10+282</f>
         <v>374</v>
       </c>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98"/>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -75143,47 +76750,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="94"/>
-      <c r="N34" s="95"/>
-      <c r="O34" s="97" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -75439,12 +77046,12 @@
       <c r="Q42" s="43">
         <v>17</v>
       </c>
-      <c r="R42" s="90" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="91"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="91"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -75480,20 +77087,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="98">
+      <c r="C44" s="99">
         <f>8+1+53+6+271</f>
         <v>339</v>
       </c>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="98"/>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
